--- a/Manifest Description Conversion.xlsx
+++ b/Manifest Description Conversion.xlsx
@@ -35,19 +35,19 @@
       <text/>
       <mc:AlternateContent>
         <mc:Choice Requires="v2">
-          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="justify">
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>14</xdr:colOff>
-                <xdr:row>15</xdr:row>
-                <xdr:rowOff>22</xdr:rowOff>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>24</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>2</xdr:col>
-                <xdr:colOff>-105</xdr:colOff>
-                <xdr:row>44</xdr:row>
-                <xdr:rowOff>24</xdr:rowOff>
+                <xdr:colOff>-338</xdr:colOff>
+                <xdr:row>1</xdr:row>
+                <xdr:rowOff>-14</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -59,19 +59,19 @@
       <text/>
       <mc:AlternateContent>
         <mc:Choice Requires="v2">
-          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="true" textHAlign="justify" textVAlign="top">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="true" textHAlign="justify" textVAlign="justify">
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>17</xdr:colOff>
-                <xdr:row>18</xdr:row>
-                <xdr:rowOff>13</xdr:rowOff>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>7</xdr:row>
+                <xdr:rowOff>9</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>2</xdr:col>
-                <xdr:colOff>-203</xdr:colOff>
-                <xdr:row>87</xdr:row>
-                <xdr:rowOff>26</xdr:rowOff>
+                <xdr:colOff>-338</xdr:colOff>
+                <xdr:row>9</xdr:row>
+                <xdr:rowOff>19</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -83,19 +83,19 @@
       <text/>
       <mc:AlternateContent>
         <mc:Choice Requires="v2">
-          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="true" textHAlign="justify" textVAlign="top">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="true" textHAlign="justify" textVAlign="justify">
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>14</xdr:colOff>
-                <xdr:row>51</xdr:row>
-                <xdr:rowOff>22</xdr:rowOff>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>9</xdr:row>
+                <xdr:rowOff>9</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>2</xdr:col>
-                <xdr:colOff>1</xdr:colOff>
-                <xdr:row>90</xdr:row>
-                <xdr:rowOff>16</xdr:rowOff>
+                <xdr:colOff>-338</xdr:colOff>
+                <xdr:row>12</xdr:row>
+                <xdr:rowOff>19</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -107,19 +107,19 @@
       <text/>
       <mc:AlternateContent>
         <mc:Choice Requires="v2">
-          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="justify">
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>14</xdr:colOff>
-                <xdr:row>59</xdr:row>
-                <xdr:rowOff>22</xdr:rowOff>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>9</xdr:row>
+                <xdr:rowOff>9</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>2</xdr:col>
-                <xdr:colOff>-103</xdr:colOff>
-                <xdr:row>94</xdr:row>
-                <xdr:rowOff>28</xdr:rowOff>
+                <xdr:colOff>-338</xdr:colOff>
+                <xdr:row>12</xdr:row>
+                <xdr:rowOff>19</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -131,19 +131,19 @@
       <text/>
       <mc:AlternateContent>
         <mc:Choice Requires="v2">
-          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="true" textHAlign="justify" textVAlign="top">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="true" textHAlign="justify" textVAlign="justify">
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>14</xdr:colOff>
-                <xdr:row>85</xdr:row>
-                <xdr:rowOff>22</xdr:rowOff>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>12</xdr:row>
+                <xdr:rowOff>9</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>2</xdr:col>
-                <xdr:colOff>24</xdr:colOff>
-                <xdr:row>95</xdr:row>
-                <xdr:rowOff>5</xdr:rowOff>
+                <xdr:colOff>-338</xdr:colOff>
+                <xdr:row>15</xdr:row>
+                <xdr:rowOff>19</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -155,19 +155,19 @@
       <text/>
       <mc:AlternateContent>
         <mc:Choice Requires="v2">
-          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="justify">
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>14</xdr:colOff>
-                <xdr:row>86</xdr:row>
-                <xdr:rowOff>22</xdr:rowOff>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>12</xdr:row>
+                <xdr:rowOff>9</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>2</xdr:col>
-                <xdr:colOff>-79</xdr:colOff>
-                <xdr:row>96</xdr:row>
-                <xdr:rowOff>1</xdr:rowOff>
+                <xdr:colOff>-338</xdr:colOff>
+                <xdr:row>15</xdr:row>
+                <xdr:rowOff>19</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -179,19 +179,19 @@
       <text/>
       <mc:AlternateContent>
         <mc:Choice Requires="v2">
-          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="justify">
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>14</xdr:colOff>
-                <xdr:row>87</xdr:row>
-                <xdr:rowOff>22</xdr:rowOff>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>15</xdr:row>
+                <xdr:rowOff>9</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>2</xdr:col>
-                <xdr:colOff>-71</xdr:colOff>
-                <xdr:row>98</xdr:row>
-                <xdr:rowOff>20</xdr:rowOff>
+                <xdr:colOff>-338</xdr:colOff>
+                <xdr:row>17</xdr:row>
+                <xdr:rowOff>19</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -203,19 +203,19 @@
       <text/>
       <mc:AlternateContent>
         <mc:Choice Requires="v2">
-          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="true" textHAlign="justify" textVAlign="top">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="true" textHAlign="justify" textVAlign="justify">
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>14</xdr:colOff>
-                <xdr:row>92</xdr:row>
-                <xdr:rowOff>22</xdr:rowOff>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>18</xdr:row>
+                <xdr:rowOff>9</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>2</xdr:col>
-                <xdr:colOff>56</xdr:colOff>
-                <xdr:row>125</xdr:row>
-                <xdr:rowOff>32</xdr:rowOff>
+                <xdr:colOff>-338</xdr:colOff>
+                <xdr:row>19</xdr:row>
+                <xdr:rowOff>19</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -227,19 +227,19 @@
       <text/>
       <mc:AlternateContent>
         <mc:Choice Requires="v2">
-          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="true" textHAlign="justify" textVAlign="top">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="true" textHAlign="justify" textVAlign="justify">
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>14</xdr:colOff>
-                <xdr:row>98</xdr:row>
-                <xdr:rowOff>22</xdr:rowOff>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>18</xdr:row>
+                <xdr:rowOff>9</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>2</xdr:col>
-                <xdr:colOff>-111</xdr:colOff>
-                <xdr:row>131</xdr:row>
-                <xdr:rowOff>12</xdr:rowOff>
+                <xdr:colOff>-338</xdr:colOff>
+                <xdr:row>19</xdr:row>
+                <xdr:rowOff>19</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -251,19 +251,19 @@
       <text/>
       <mc:AlternateContent>
         <mc:Choice Requires="v2">
-          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="true" textHAlign="justify" textVAlign="top">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="true" textHAlign="justify" textVAlign="justify">
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>14</xdr:colOff>
-                <xdr:row>124</xdr:row>
-                <xdr:rowOff>22</xdr:rowOff>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>18</xdr:row>
+                <xdr:rowOff>9</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>2</xdr:col>
-                <xdr:colOff>21</xdr:colOff>
-                <xdr:row>141</xdr:row>
-                <xdr:rowOff>28</xdr:rowOff>
+                <xdr:colOff>-338</xdr:colOff>
+                <xdr:row>19</xdr:row>
+                <xdr:rowOff>19</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -275,19 +275,19 @@
       <text/>
       <mc:AlternateContent>
         <mc:Choice Requires="v2">
-          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="true" textHAlign="justify" textVAlign="top">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="true" textHAlign="justify" textVAlign="justify">
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>14</xdr:colOff>
-                <xdr:row>125</xdr:row>
-                <xdr:rowOff>22</xdr:rowOff>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>18</xdr:row>
+                <xdr:rowOff>9</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>2</xdr:col>
-                <xdr:colOff>29</xdr:colOff>
-                <xdr:row>142</xdr:row>
-                <xdr:rowOff>33</xdr:rowOff>
+                <xdr:colOff>-338</xdr:colOff>
+                <xdr:row>19</xdr:row>
+                <xdr:rowOff>19</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -299,19 +299,19 @@
       <text/>
       <mc:AlternateContent>
         <mc:Choice Requires="v2">
-          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="justify">
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>28</xdr:colOff>
-                <xdr:row>125</xdr:row>
-                <xdr:rowOff>8</xdr:rowOff>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>18</xdr:row>
+                <xdr:rowOff>9</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>2</xdr:col>
-                <xdr:colOff>211</xdr:colOff>
-                <xdr:row>154</xdr:row>
-                <xdr:rowOff>6</xdr:rowOff>
+                <xdr:colOff>-338</xdr:colOff>
+                <xdr:row>19</xdr:row>
+                <xdr:rowOff>19</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -323,19 +323,19 @@
       <text/>
       <mc:AlternateContent>
         <mc:Choice Requires="v2">
-          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="true" textHAlign="justify" textVAlign="top">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="true" textHAlign="justify" textVAlign="justify">
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>22</xdr:colOff>
-                <xdr:row>130</xdr:row>
-                <xdr:rowOff>25</xdr:rowOff>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>32</xdr:row>
+                <xdr:rowOff>9</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>2</xdr:col>
-                <xdr:colOff>332</xdr:colOff>
-                <xdr:row>335</xdr:row>
-                <xdr:rowOff>25</xdr:rowOff>
+                <xdr:colOff>-338</xdr:colOff>
+                <xdr:row>33</xdr:row>
+                <xdr:rowOff>19</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -347,19 +347,19 @@
       <text/>
       <mc:AlternateContent>
         <mc:Choice Requires="v2">
-          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="true" textHAlign="justify" textVAlign="top">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="true" textHAlign="justify" textVAlign="justify">
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>14</xdr:colOff>
-                <xdr:row>141</xdr:row>
-                <xdr:rowOff>22</xdr:rowOff>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>32</xdr:row>
+                <xdr:rowOff>9</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>2</xdr:col>
-                <xdr:colOff>-101</xdr:colOff>
-                <xdr:row>325</xdr:row>
-                <xdr:rowOff>2</xdr:rowOff>
+                <xdr:colOff>-338</xdr:colOff>
+                <xdr:row>33</xdr:row>
+                <xdr:rowOff>19</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -371,19 +371,19 @@
       <text/>
       <mc:AlternateContent>
         <mc:Choice Requires="v2">
-          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="true" textHAlign="justify" textVAlign="top">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="true" textHAlign="justify" textVAlign="justify">
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>14</xdr:colOff>
-                <xdr:row>142</xdr:row>
-                <xdr:rowOff>22</xdr:rowOff>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>32</xdr:row>
+                <xdr:rowOff>9</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>2</xdr:col>
-                <xdr:colOff>-67</xdr:colOff>
-                <xdr:row>335</xdr:row>
-                <xdr:rowOff>1</xdr:rowOff>
+                <xdr:colOff>-338</xdr:colOff>
+                <xdr:row>33</xdr:row>
+                <xdr:rowOff>19</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -395,19 +395,19 @@
       <text/>
       <mc:AlternateContent>
         <mc:Choice Requires="v2">
-          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="true" textHAlign="justify" textVAlign="top">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="true" textHAlign="justify" textVAlign="justify">
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>14</xdr:colOff>
-                <xdr:row>143</xdr:row>
-                <xdr:rowOff>22</xdr:rowOff>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>32</xdr:row>
+                <xdr:rowOff>9</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>2</xdr:col>
-                <xdr:colOff>29</xdr:colOff>
-                <xdr:row>336</xdr:row>
-                <xdr:rowOff>2</xdr:rowOff>
+                <xdr:colOff>-338</xdr:colOff>
+                <xdr:row>33</xdr:row>
+                <xdr:rowOff>19</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -419,19 +419,19 @@
       <text/>
       <mc:AlternateContent>
         <mc:Choice Requires="v2">
-          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="true" textHAlign="justify" textVAlign="top">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="true" textHAlign="justify" textVAlign="justify">
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>28</xdr:colOff>
-                <xdr:row>143</xdr:row>
-                <xdr:rowOff>8</xdr:rowOff>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>32</xdr:row>
+                <xdr:rowOff>9</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>2</xdr:col>
-                <xdr:colOff>167</xdr:colOff>
-                <xdr:row>338</xdr:row>
-                <xdr:rowOff>2</xdr:rowOff>
+                <xdr:colOff>-338</xdr:colOff>
+                <xdr:row>33</xdr:row>
+                <xdr:rowOff>19</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -443,19 +443,19 @@
       <text/>
       <mc:AlternateContent>
         <mc:Choice Requires="v2">
-          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="true" textHAlign="justify" textVAlign="top">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="true" textHAlign="justify" textVAlign="justify">
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>14</xdr:colOff>
-                <xdr:row>154</xdr:row>
-                <xdr:rowOff>22</xdr:rowOff>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>32</xdr:row>
+                <xdr:rowOff>9</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>2</xdr:col>
-                <xdr:colOff>32</xdr:colOff>
-                <xdr:row>340</xdr:row>
-                <xdr:rowOff>20</xdr:rowOff>
+                <xdr:colOff>-338</xdr:colOff>
+                <xdr:row>33</xdr:row>
+                <xdr:rowOff>19</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -467,19 +467,19 @@
       <text/>
       <mc:AlternateContent>
         <mc:Choice Requires="v2">
-          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="justify">
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>14</xdr:colOff>
-                <xdr:row>276</xdr:row>
-                <xdr:rowOff>22</xdr:rowOff>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>32</xdr:row>
+                <xdr:rowOff>9</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>2</xdr:col>
-                <xdr:colOff>73</xdr:colOff>
-                <xdr:row>344</xdr:row>
-                <xdr:rowOff>8</xdr:rowOff>
+                <xdr:colOff>-338</xdr:colOff>
+                <xdr:row>33</xdr:row>
+                <xdr:rowOff>19</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -491,19 +491,19 @@
       <text/>
       <mc:AlternateContent>
         <mc:Choice Requires="v2">
-          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="justify">
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>28</xdr:colOff>
-                <xdr:row>276</xdr:row>
-                <xdr:rowOff>21</xdr:rowOff>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>33</xdr:row>
+                <xdr:rowOff>9</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>2</xdr:col>
-                <xdr:colOff>350</xdr:colOff>
-                <xdr:row>340</xdr:row>
-                <xdr:rowOff>12</xdr:rowOff>
+                <xdr:colOff>-338</xdr:colOff>
+                <xdr:row>43</xdr:row>
+                <xdr:rowOff>19</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -515,19 +515,19 @@
       <text/>
       <mc:AlternateContent>
         <mc:Choice Requires="v2">
-          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="true" textHAlign="justify" textVAlign="top">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="true" textHAlign="justify" textVAlign="justify">
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>28</xdr:colOff>
-                <xdr:row>325</xdr:row>
-                <xdr:rowOff>8</xdr:rowOff>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>43</xdr:row>
+                <xdr:rowOff>9</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>2</xdr:col>
-                <xdr:colOff>36</xdr:colOff>
-                <xdr:row>346</xdr:row>
-                <xdr:rowOff>10</xdr:rowOff>
+                <xdr:colOff>-338</xdr:colOff>
+                <xdr:row>44</xdr:row>
+                <xdr:rowOff>19</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -539,19 +539,19 @@
       <text/>
       <mc:AlternateContent>
         <mc:Choice Requires="v2">
-          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="true" textHAlign="justify" textVAlign="top">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="true" textHAlign="justify" textVAlign="justify">
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>28</xdr:colOff>
-                <xdr:row>337</xdr:row>
-                <xdr:rowOff>21</xdr:rowOff>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>43</xdr:row>
+                <xdr:rowOff>9</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>2</xdr:col>
-                <xdr:colOff>268</xdr:colOff>
-                <xdr:row>346</xdr:row>
-                <xdr:rowOff>16</xdr:rowOff>
+                <xdr:colOff>-338</xdr:colOff>
+                <xdr:row>44</xdr:row>
+                <xdr:rowOff>19</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -563,19 +563,19 @@
       <text/>
       <mc:AlternateContent>
         <mc:Choice Requires="v2">
-          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="true" textHAlign="justify" textVAlign="top">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="true" textHAlign="justify" textVAlign="justify">
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>28</xdr:colOff>
-                <xdr:row>338</xdr:row>
-                <xdr:rowOff>21</xdr:rowOff>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>43</xdr:row>
+                <xdr:rowOff>9</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>2</xdr:col>
-                <xdr:colOff>195</xdr:colOff>
-                <xdr:row>350</xdr:row>
-                <xdr:rowOff>8</xdr:rowOff>
+                <xdr:colOff>-338</xdr:colOff>
+                <xdr:row>44</xdr:row>
+                <xdr:rowOff>19</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -587,19 +587,19 @@
       <text/>
       <mc:AlternateContent>
         <mc:Choice Requires="v2">
-          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="justify">
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>28</xdr:colOff>
-                <xdr:row>340</xdr:row>
-                <xdr:rowOff>8</xdr:rowOff>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>43</xdr:row>
+                <xdr:rowOff>9</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>2</xdr:col>
-                <xdr:colOff>74</xdr:colOff>
-                <xdr:row>350</xdr:row>
-                <xdr:rowOff>8</xdr:rowOff>
+                <xdr:colOff>-338</xdr:colOff>
+                <xdr:row>44</xdr:row>
+                <xdr:rowOff>19</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -611,19 +611,19 @@
       <text/>
       <mc:AlternateContent>
         <mc:Choice Requires="v2">
-          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="true" textHAlign="justify" textVAlign="top">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="true" textHAlign="justify" textVAlign="justify">
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>28</xdr:colOff>
-                <xdr:row>341</xdr:row>
-                <xdr:rowOff>21</xdr:rowOff>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>44</xdr:row>
+                <xdr:rowOff>9</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>2</xdr:col>
-                <xdr:colOff>175</xdr:colOff>
-                <xdr:row>352</xdr:row>
-                <xdr:rowOff>20</xdr:rowOff>
+                <xdr:colOff>-338</xdr:colOff>
+                <xdr:row>51</xdr:row>
+                <xdr:rowOff>19</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -635,19 +635,19 @@
       <text/>
       <mc:AlternateContent>
         <mc:Choice Requires="v2">
-          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="true" textHAlign="justify" textVAlign="top">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="true" textHAlign="justify" textVAlign="justify">
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>28</xdr:colOff>
-                <xdr:row>343</xdr:row>
-                <xdr:rowOff>8</xdr:rowOff>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>44</xdr:row>
+                <xdr:rowOff>9</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>2</xdr:col>
-                <xdr:colOff>-71</xdr:colOff>
-                <xdr:row>352</xdr:row>
-                <xdr:rowOff>32</xdr:rowOff>
+                <xdr:colOff>-338</xdr:colOff>
+                <xdr:row>51</xdr:row>
+                <xdr:rowOff>19</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -659,19 +659,19 @@
       <text/>
       <mc:AlternateContent>
         <mc:Choice Requires="v2">
-          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="true" textHAlign="justify" textVAlign="top">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="true" textHAlign="justify" textVAlign="justify">
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>28</xdr:colOff>
-                <xdr:row>345</xdr:row>
-                <xdr:rowOff>8</xdr:rowOff>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>44</xdr:row>
+                <xdr:rowOff>9</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>2</xdr:col>
-                <xdr:colOff>211</xdr:colOff>
-                <xdr:row>353</xdr:row>
-                <xdr:rowOff>18</xdr:rowOff>
+                <xdr:colOff>-338</xdr:colOff>
+                <xdr:row>51</xdr:row>
+                <xdr:rowOff>19</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -683,19 +683,19 @@
       <text/>
       <mc:AlternateContent>
         <mc:Choice Requires="v2">
-          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="true" textHAlign="justify" textVAlign="top">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="true" textHAlign="justify" textVAlign="justify">
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>14</xdr:colOff>
-                <xdr:row>348</xdr:row>
-                <xdr:rowOff>22</xdr:rowOff>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>44</xdr:row>
+                <xdr:rowOff>9</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>2</xdr:col>
-                <xdr:colOff>197</xdr:colOff>
-                <xdr:row>359</xdr:row>
-                <xdr:rowOff>9</xdr:rowOff>
+                <xdr:colOff>-338</xdr:colOff>
+                <xdr:row>51</xdr:row>
+                <xdr:rowOff>19</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -707,19 +707,19 @@
       <text/>
       <mc:AlternateContent>
         <mc:Choice Requires="v2">
-          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="justify">
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>29</xdr:colOff>
-                <xdr:row>348</xdr:row>
-                <xdr:rowOff>16</xdr:rowOff>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>44</xdr:row>
+                <xdr:rowOff>9</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>2</xdr:col>
-                <xdr:colOff>212</xdr:colOff>
-                <xdr:row>359</xdr:row>
-                <xdr:rowOff>4</xdr:rowOff>
+                <xdr:colOff>-338</xdr:colOff>
+                <xdr:row>51</xdr:row>
+                <xdr:rowOff>19</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -731,19 +731,19 @@
       <text/>
       <mc:AlternateContent>
         <mc:Choice Requires="v2">
-          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="true" textHAlign="justify" textVAlign="top">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="true" textHAlign="justify" textVAlign="justify">
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>28</xdr:colOff>
-                <xdr:row>349</xdr:row>
-                <xdr:rowOff>21</xdr:rowOff>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>51</xdr:row>
+                <xdr:rowOff>9</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>2</xdr:col>
-                <xdr:colOff>223</xdr:colOff>
-                <xdr:row>360</xdr:row>
-                <xdr:rowOff>32</xdr:rowOff>
+                <xdr:colOff>-338</xdr:colOff>
+                <xdr:row>59</xdr:row>
+                <xdr:rowOff>19</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -755,19 +755,19 @@
       <text/>
       <mc:AlternateContent>
         <mc:Choice Requires="v2">
-          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="true" textHAlign="justify" textVAlign="top">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="true" textHAlign="justify" textVAlign="justify">
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>28</xdr:colOff>
-                <xdr:row>351</xdr:row>
-                <xdr:rowOff>21</xdr:rowOff>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>51</xdr:row>
+                <xdr:rowOff>9</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>2</xdr:col>
-                <xdr:colOff>282</xdr:colOff>
-                <xdr:row>362</xdr:row>
-                <xdr:rowOff>1</xdr:rowOff>
+                <xdr:colOff>-338</xdr:colOff>
+                <xdr:row>59</xdr:row>
+                <xdr:rowOff>19</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -779,19 +779,19 @@
       <text/>
       <mc:AlternateContent>
         <mc:Choice Requires="v2">
-          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="true" textHAlign="justify" textVAlign="top">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="true" textHAlign="justify" textVAlign="justify">
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>28</xdr:colOff>
-                <xdr:row>353</xdr:row>
-                <xdr:rowOff>21</xdr:rowOff>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>51</xdr:row>
+                <xdr:rowOff>9</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>2</xdr:col>
-                <xdr:colOff>219</xdr:colOff>
-                <xdr:row>363</xdr:row>
-                <xdr:rowOff>1</xdr:rowOff>
+                <xdr:colOff>-338</xdr:colOff>
+                <xdr:row>59</xdr:row>
+                <xdr:rowOff>19</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -803,19 +803,19 @@
       <text/>
       <mc:AlternateContent>
         <mc:Choice Requires="v2">
-          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="true" textHAlign="justify" textVAlign="top">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="true" textHAlign="justify" textVAlign="justify">
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>28</xdr:colOff>
-                <xdr:row>355</xdr:row>
-                <xdr:rowOff>8</xdr:rowOff>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>51</xdr:row>
+                <xdr:rowOff>9</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>2</xdr:col>
-                <xdr:colOff>326</xdr:colOff>
-                <xdr:row>367</xdr:row>
-                <xdr:rowOff>8</xdr:rowOff>
+                <xdr:colOff>-338</xdr:colOff>
+                <xdr:row>59</xdr:row>
+                <xdr:rowOff>19</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -827,19 +827,19 @@
       <text/>
       <mc:AlternateContent>
         <mc:Choice Requires="v2">
-          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="true" textHAlign="justify" textVAlign="top">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="true" textHAlign="justify" textVAlign="justify">
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>28</xdr:colOff>
-                <xdr:row>357</xdr:row>
-                <xdr:rowOff>8</xdr:rowOff>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>51</xdr:row>
+                <xdr:rowOff>9</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>2</xdr:col>
-                <xdr:colOff>354</xdr:colOff>
-                <xdr:row>361</xdr:row>
-                <xdr:rowOff>8</xdr:rowOff>
+                <xdr:colOff>-338</xdr:colOff>
+                <xdr:row>59</xdr:row>
+                <xdr:rowOff>19</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -851,19 +851,19 @@
       <text/>
       <mc:AlternateContent>
         <mc:Choice Requires="v2">
-          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="true" textHAlign="justify" textVAlign="top">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="true" textHAlign="justify" textVAlign="justify">
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>20</xdr:colOff>
-                <xdr:row>359</xdr:row>
-                <xdr:rowOff>4</xdr:rowOff>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>51</xdr:row>
+                <xdr:rowOff>9</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>2</xdr:col>
-                <xdr:colOff>418</xdr:colOff>
-                <xdr:row>370</xdr:row>
-                <xdr:rowOff>24</xdr:rowOff>
+                <xdr:colOff>-338</xdr:colOff>
+                <xdr:row>59</xdr:row>
+                <xdr:rowOff>19</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -875,19 +875,19 @@
       <text/>
       <mc:AlternateContent>
         <mc:Choice Requires="v2">
-          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="true" textHAlign="justify" textVAlign="top">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="true" textHAlign="justify" textVAlign="justify">
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>28</xdr:colOff>
-                <xdr:row>360</xdr:row>
-                <xdr:rowOff>8</xdr:rowOff>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>51</xdr:row>
+                <xdr:rowOff>9</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>2</xdr:col>
-                <xdr:colOff>191</xdr:colOff>
-                <xdr:row>368</xdr:row>
-                <xdr:rowOff>20</xdr:rowOff>
+                <xdr:colOff>-338</xdr:colOff>
+                <xdr:row>59</xdr:row>
+                <xdr:rowOff>19</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -899,19 +899,19 @@
       <text/>
       <mc:AlternateContent>
         <mc:Choice Requires="v2">
-          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="true" textHAlign="justify" textVAlign="top">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="true" textHAlign="justify" textVAlign="justify">
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>28</xdr:colOff>
-                <xdr:row>362</xdr:row>
-                <xdr:rowOff>21</xdr:rowOff>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>51</xdr:row>
+                <xdr:rowOff>9</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>2</xdr:col>
-                <xdr:colOff>312</xdr:colOff>
-                <xdr:row>372</xdr:row>
-                <xdr:rowOff>20</xdr:rowOff>
+                <xdr:colOff>-338</xdr:colOff>
+                <xdr:row>59</xdr:row>
+                <xdr:rowOff>19</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -923,19 +923,19 @@
       <text/>
       <mc:AlternateContent>
         <mc:Choice Requires="v2">
-          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="true" textHAlign="justify" textVAlign="top">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="true" textHAlign="justify" textVAlign="justify">
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>28</xdr:colOff>
-                <xdr:row>364</xdr:row>
-                <xdr:rowOff>21</xdr:rowOff>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>51</xdr:row>
+                <xdr:rowOff>9</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>2</xdr:col>
-                <xdr:colOff>113</xdr:colOff>
-                <xdr:row>372</xdr:row>
-                <xdr:rowOff>16</xdr:rowOff>
+                <xdr:colOff>-338</xdr:colOff>
+                <xdr:row>59</xdr:row>
+                <xdr:rowOff>19</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -947,19 +947,19 @@
       <text/>
       <mc:AlternateContent>
         <mc:Choice Requires="v2">
-          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="true" textHAlign="justify" textVAlign="top">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="true" textHAlign="justify" textVAlign="justify">
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>28</xdr:colOff>
-                <xdr:row>366</xdr:row>
-                <xdr:rowOff>21</xdr:rowOff>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>51</xdr:row>
+                <xdr:rowOff>9</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>2</xdr:col>
-                <xdr:colOff>235</xdr:colOff>
-                <xdr:row>380</xdr:row>
-                <xdr:rowOff>12</xdr:rowOff>
+                <xdr:colOff>-338</xdr:colOff>
+                <xdr:row>59</xdr:row>
+                <xdr:rowOff>19</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -971,19 +971,19 @@
       <text/>
       <mc:AlternateContent>
         <mc:Choice Requires="v2">
-          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="true" textHAlign="justify" textVAlign="top">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="true" textHAlign="justify" textVAlign="justify">
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>14</xdr:colOff>
-                <xdr:row>369</xdr:row>
-                <xdr:rowOff>22</xdr:rowOff>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>51</xdr:row>
+                <xdr:rowOff>9</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>2</xdr:col>
-                <xdr:colOff>90</xdr:colOff>
-                <xdr:row>379</xdr:row>
-                <xdr:rowOff>12</xdr:rowOff>
+                <xdr:colOff>-338</xdr:colOff>
+                <xdr:row>59</xdr:row>
+                <xdr:rowOff>19</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -995,19 +995,19 @@
       <text/>
       <mc:AlternateContent>
         <mc:Choice Requires="v2">
-          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="true" textHAlign="justify" textVAlign="top">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="true" textHAlign="justify" textVAlign="justify">
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>28</xdr:colOff>
-                <xdr:row>369</xdr:row>
-                <xdr:rowOff>21</xdr:rowOff>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>51</xdr:row>
+                <xdr:rowOff>9</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>2</xdr:col>
-                <xdr:colOff>152</xdr:colOff>
-                <xdr:row>382</xdr:row>
-                <xdr:rowOff>6</xdr:rowOff>
+                <xdr:colOff>-338</xdr:colOff>
+                <xdr:row>59</xdr:row>
+                <xdr:rowOff>19</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -1019,19 +1019,19 @@
       <text/>
       <mc:AlternateContent>
         <mc:Choice Requires="v2">
-          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="justify">
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>14</xdr:colOff>
-                <xdr:row>375</xdr:row>
-                <xdr:rowOff>22</xdr:rowOff>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>51</xdr:row>
+                <xdr:rowOff>9</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>2</xdr:col>
-                <xdr:colOff>64</xdr:colOff>
-                <xdr:row>383</xdr:row>
-                <xdr:rowOff>24</xdr:rowOff>
+                <xdr:colOff>-338</xdr:colOff>
+                <xdr:row>59</xdr:row>
+                <xdr:rowOff>19</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -1043,19 +1043,19 @@
       <text/>
       <mc:AlternateContent>
         <mc:Choice Requires="v2">
-          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="justify">
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>14</xdr:colOff>
-                <xdr:row>376</xdr:row>
-                <xdr:rowOff>22</xdr:rowOff>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>59</xdr:row>
+                <xdr:rowOff>9</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>2</xdr:col>
-                <xdr:colOff>24</xdr:colOff>
-                <xdr:row>384</xdr:row>
-                <xdr:rowOff>4</xdr:rowOff>
+                <xdr:colOff>-338</xdr:colOff>
+                <xdr:row>85</xdr:row>
+                <xdr:rowOff>19</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -1067,19 +1067,19 @@
       <text/>
       <mc:AlternateContent>
         <mc:Choice Requires="v2">
-          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="justify">
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>14</xdr:colOff>
-                <xdr:row>377</xdr:row>
-                <xdr:rowOff>22</xdr:rowOff>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>85</xdr:row>
+                <xdr:rowOff>9</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>2</xdr:col>
-                <xdr:colOff>151</xdr:colOff>
-                <xdr:row>386</xdr:row>
-                <xdr:rowOff>13</xdr:rowOff>
+                <xdr:colOff>-338</xdr:colOff>
+                <xdr:row>86</xdr:row>
+                <xdr:rowOff>19</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -1091,19 +1091,19 @@
       <text/>
       <mc:AlternateContent>
         <mc:Choice Requires="v2">
-          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="justify">
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>14</xdr:colOff>
-                <xdr:row>378</xdr:row>
-                <xdr:rowOff>22</xdr:rowOff>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>86</xdr:row>
+                <xdr:rowOff>9</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>2</xdr:col>
-                <xdr:colOff>307</xdr:colOff>
-                <xdr:row>383</xdr:row>
-                <xdr:rowOff>18</xdr:rowOff>
+                <xdr:colOff>-338</xdr:colOff>
+                <xdr:row>87</xdr:row>
+                <xdr:rowOff>19</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -1115,19 +1115,19 @@
       <text/>
       <mc:AlternateContent>
         <mc:Choice Requires="v2">
-          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="justify">
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>14</xdr:colOff>
-                <xdr:row>379</xdr:row>
-                <xdr:rowOff>22</xdr:rowOff>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>87</xdr:row>
+                <xdr:rowOff>9</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>2</xdr:col>
-                <xdr:colOff>231</xdr:colOff>
-                <xdr:row>387</xdr:row>
-                <xdr:rowOff>25</xdr:rowOff>
+                <xdr:colOff>-338</xdr:colOff>
+                <xdr:row>88</xdr:row>
+                <xdr:rowOff>19</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -1139,19 +1139,19 @@
       <text/>
       <mc:AlternateContent>
         <mc:Choice Requires="v2">
-          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="justify">
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>14</xdr:colOff>
-                <xdr:row>380</xdr:row>
-                <xdr:rowOff>22</xdr:rowOff>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>88</xdr:row>
+                <xdr:rowOff>9</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>2</xdr:col>
-                <xdr:colOff>276</xdr:colOff>
-                <xdr:row>387</xdr:row>
-                <xdr:rowOff>28</xdr:rowOff>
+                <xdr:colOff>-338</xdr:colOff>
+                <xdr:row>89</xdr:row>
+                <xdr:rowOff>19</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -1163,19 +1163,19 @@
       <text/>
       <mc:AlternateContent>
         <mc:Choice Requires="v2">
-          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="justify">
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>16</xdr:colOff>
-                <xdr:row>381</xdr:row>
-                <xdr:rowOff>22</xdr:rowOff>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>89</xdr:row>
+                <xdr:rowOff>9</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>2</xdr:col>
-                <xdr:colOff>324</xdr:colOff>
-                <xdr:row>388</xdr:row>
-                <xdr:rowOff>9</xdr:rowOff>
+                <xdr:colOff>-338</xdr:colOff>
+                <xdr:row>90</xdr:row>
+                <xdr:rowOff>19</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -1187,19 +1187,19 @@
       <text/>
       <mc:AlternateContent>
         <mc:Choice Requires="v2">
-          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="justify">
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>14</xdr:colOff>
-                <xdr:row>382</xdr:row>
-                <xdr:rowOff>22</xdr:rowOff>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>90</xdr:row>
+                <xdr:rowOff>9</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>2</xdr:col>
-                <xdr:colOff>268</xdr:colOff>
-                <xdr:row>388</xdr:row>
-                <xdr:rowOff>8</xdr:rowOff>
+                <xdr:colOff>-338</xdr:colOff>
+                <xdr:row>91</xdr:row>
+                <xdr:rowOff>19</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -1211,19 +1211,19 @@
       <text/>
       <mc:AlternateContent>
         <mc:Choice Requires="v2">
-          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="true" textHAlign="justify" textVAlign="top">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="true" textHAlign="justify" textVAlign="justify">
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>14</xdr:colOff>
-                <xdr:row>383</xdr:row>
-                <xdr:rowOff>22</xdr:rowOff>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>91</xdr:row>
+                <xdr:rowOff>9</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>2</xdr:col>
-                <xdr:colOff>123</xdr:colOff>
-                <xdr:row>387</xdr:row>
-                <xdr:rowOff>16</xdr:rowOff>
+                <xdr:colOff>-338</xdr:colOff>
+                <xdr:row>92</xdr:row>
+                <xdr:rowOff>19</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -1235,19 +1235,19 @@
       <text/>
       <mc:AlternateContent>
         <mc:Choice Requires="v2">
-          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="justify">
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>4</xdr:colOff>
-                <xdr:row>384</xdr:row>
-                <xdr:rowOff>29</xdr:rowOff>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>91</xdr:row>
+                <xdr:rowOff>9</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>2</xdr:col>
-                <xdr:colOff>156</xdr:colOff>
-                <xdr:row>388</xdr:row>
-                <xdr:rowOff>25</xdr:rowOff>
+                <xdr:colOff>-338</xdr:colOff>
+                <xdr:row>92</xdr:row>
+                <xdr:rowOff>19</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -1259,19 +1259,19 @@
       <text/>
       <mc:AlternateContent>
         <mc:Choice Requires="v2">
-          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="justify">
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>14</xdr:colOff>
-                <xdr:row>385</xdr:row>
-                <xdr:rowOff>22</xdr:rowOff>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>92</xdr:row>
+                <xdr:rowOff>9</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>2</xdr:col>
-                <xdr:colOff>197</xdr:colOff>
-                <xdr:row>391</xdr:row>
-                <xdr:rowOff>32</xdr:rowOff>
+                <xdr:colOff>-338</xdr:colOff>
+                <xdr:row>94</xdr:row>
+                <xdr:rowOff>19</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -1283,19 +1283,19 @@
       <text/>
       <mc:AlternateContent>
         <mc:Choice Requires="v2">
-          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="justify">
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>14</xdr:colOff>
-                <xdr:row>386</xdr:row>
-                <xdr:rowOff>22</xdr:rowOff>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>94</xdr:row>
+                <xdr:rowOff>9</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>2</xdr:col>
-                <xdr:colOff>278</xdr:colOff>
-                <xdr:row>394</xdr:row>
-                <xdr:rowOff>16</xdr:rowOff>
+                <xdr:colOff>-338</xdr:colOff>
+                <xdr:row>95</xdr:row>
+                <xdr:rowOff>19</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -1307,19 +1307,19 @@
       <text/>
       <mc:AlternateContent>
         <mc:Choice Requires="v2">
-          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="justify">
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>10</xdr:colOff>
-                <xdr:row>388</xdr:row>
-                <xdr:rowOff>12</xdr:rowOff>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>95</xdr:row>
+                <xdr:rowOff>9</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>2</xdr:col>
-                <xdr:colOff>111</xdr:colOff>
-                <xdr:row>399</xdr:row>
-                <xdr:rowOff>1</xdr:rowOff>
+                <xdr:colOff>-338</xdr:colOff>
+                <xdr:row>96</xdr:row>
+                <xdr:rowOff>19</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -1331,19 +1331,19 @@
       <text/>
       <mc:AlternateContent>
         <mc:Choice Requires="v2">
-          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="true" textHAlign="justify" textVAlign="top">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="true" textHAlign="justify" textVAlign="justify">
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>14</xdr:colOff>
-                <xdr:row>389</xdr:row>
-                <xdr:rowOff>22</xdr:rowOff>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>96</xdr:row>
+                <xdr:rowOff>9</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>2</xdr:col>
-                <xdr:colOff>179</xdr:colOff>
-                <xdr:row>399</xdr:row>
-                <xdr:rowOff>4</xdr:rowOff>
+                <xdr:colOff>-338</xdr:colOff>
+                <xdr:row>98</xdr:row>
+                <xdr:rowOff>19</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -1355,19 +1355,19 @@
       <text/>
       <mc:AlternateContent>
         <mc:Choice Requires="v2">
-          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="true" textHAlign="justify" textVAlign="top">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="true" textHAlign="justify" textVAlign="justify">
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>14</xdr:colOff>
-                <xdr:row>400</xdr:row>
-                <xdr:rowOff>22</xdr:rowOff>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>96</xdr:row>
+                <xdr:rowOff>9</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>2</xdr:col>
-                <xdr:colOff>271</xdr:colOff>
-                <xdr:row>409</xdr:row>
-                <xdr:rowOff>1</xdr:rowOff>
+                <xdr:colOff>-338</xdr:colOff>
+                <xdr:row>98</xdr:row>
+                <xdr:rowOff>19</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -1379,19 +1379,19 @@
       <text/>
       <mc:AlternateContent>
         <mc:Choice Requires="v2">
-          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="true" textHAlign="justify" textVAlign="top">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="true" textHAlign="justify" textVAlign="justify">
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>14</xdr:colOff>
-                <xdr:row>402</xdr:row>
-                <xdr:rowOff>22</xdr:rowOff>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>96</xdr:row>
+                <xdr:rowOff>9</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>2</xdr:col>
-                <xdr:colOff>211</xdr:colOff>
-                <xdr:row>409</xdr:row>
-                <xdr:rowOff>16</xdr:rowOff>
+                <xdr:colOff>-338</xdr:colOff>
+                <xdr:row>98</xdr:row>
+                <xdr:rowOff>19</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -1403,19 +1403,19 @@
       <text/>
       <mc:AlternateContent>
         <mc:Choice Requires="v2">
-          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="true" textHAlign="justify" textVAlign="top">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="true" textHAlign="justify" textVAlign="justify">
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>14</xdr:colOff>
-                <xdr:row>405</xdr:row>
-                <xdr:rowOff>22</xdr:rowOff>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>96</xdr:row>
+                <xdr:rowOff>9</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>2</xdr:col>
-                <xdr:colOff>201</xdr:colOff>
-                <xdr:row>412</xdr:row>
-                <xdr:rowOff>13</xdr:rowOff>
+                <xdr:colOff>-338</xdr:colOff>
+                <xdr:row>98</xdr:row>
+                <xdr:rowOff>19</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -1427,19 +1427,19 @@
       <text/>
       <mc:AlternateContent>
         <mc:Choice Requires="v2">
-          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="true" textHAlign="justify" textVAlign="top">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="true" textHAlign="justify" textVAlign="justify">
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>14</xdr:colOff>
-                <xdr:row>407</xdr:row>
-                <xdr:rowOff>22</xdr:rowOff>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>96</xdr:row>
+                <xdr:rowOff>9</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>2</xdr:col>
-                <xdr:colOff>291</xdr:colOff>
-                <xdr:row>414</xdr:row>
-                <xdr:rowOff>14</xdr:rowOff>
+                <xdr:colOff>-338</xdr:colOff>
+                <xdr:row>98</xdr:row>
+                <xdr:rowOff>19</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -1451,19 +1451,19 @@
       <text/>
       <mc:AlternateContent>
         <mc:Choice Requires="v2">
-          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="true" textHAlign="justify" textVAlign="top">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="true" textHAlign="justify" textVAlign="justify">
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>14</xdr:colOff>
-                <xdr:row>408</xdr:row>
-                <xdr:rowOff>22</xdr:rowOff>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>96</xdr:row>
+                <xdr:rowOff>9</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>2</xdr:col>
-                <xdr:colOff>302</xdr:colOff>
-                <xdr:row>416</xdr:row>
-                <xdr:rowOff>32</xdr:rowOff>
+                <xdr:colOff>-338</xdr:colOff>
+                <xdr:row>98</xdr:row>
+                <xdr:rowOff>19</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -1475,19 +1475,19 @@
       <text/>
       <mc:AlternateContent>
         <mc:Choice Requires="v2">
-          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="justify">
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>14</xdr:colOff>
-                <xdr:row>410</xdr:row>
-                <xdr:rowOff>22</xdr:rowOff>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>96</xdr:row>
+                <xdr:rowOff>9</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>2</xdr:col>
-                <xdr:colOff>115</xdr:colOff>
-                <xdr:row>420</xdr:row>
-                <xdr:rowOff>20</xdr:rowOff>
+                <xdr:colOff>-338</xdr:colOff>
+                <xdr:row>98</xdr:row>
+                <xdr:rowOff>19</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -1499,19 +1499,19 @@
       <text/>
       <mc:AlternateContent>
         <mc:Choice Requires="v2">
-          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="true" textHAlign="justify" textVAlign="top">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="true" textHAlign="justify" textVAlign="justify">
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>14</xdr:colOff>
-                <xdr:row>411</xdr:row>
-                <xdr:rowOff>22</xdr:rowOff>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>98</xdr:row>
+                <xdr:rowOff>9</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>2</xdr:col>
-                <xdr:colOff>175</xdr:colOff>
-                <xdr:row>419</xdr:row>
-                <xdr:rowOff>29</xdr:rowOff>
+                <xdr:colOff>-338</xdr:colOff>
+                <xdr:row>120</xdr:row>
+                <xdr:rowOff>19</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -1523,19 +1523,19 @@
       <text/>
       <mc:AlternateContent>
         <mc:Choice Requires="v2">
-          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="justify">
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>14</xdr:colOff>
-                <xdr:row>412</xdr:row>
-                <xdr:rowOff>22</xdr:rowOff>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>98</xdr:row>
+                <xdr:rowOff>9</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>2</xdr:col>
-                <xdr:colOff>147</xdr:colOff>
-                <xdr:row>422</xdr:row>
-                <xdr:rowOff>33</xdr:rowOff>
+                <xdr:colOff>-338</xdr:colOff>
+                <xdr:row>120</xdr:row>
+                <xdr:rowOff>19</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -1547,19 +1547,19 @@
       <text/>
       <mc:AlternateContent>
         <mc:Choice Requires="v2">
-          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="true" textHAlign="justify" textVAlign="top">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="true" textHAlign="justify" textVAlign="justify">
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>28</xdr:colOff>
-                <xdr:row>427</xdr:row>
-                <xdr:rowOff>21</xdr:rowOff>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>131</xdr:row>
+                <xdr:rowOff>9</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>2</xdr:col>
-                <xdr:colOff>70</xdr:colOff>
-                <xdr:row>436</xdr:row>
-                <xdr:rowOff>28</xdr:rowOff>
+                <xdr:colOff>-338</xdr:colOff>
+                <xdr:row>137</xdr:row>
+                <xdr:rowOff>19</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -1571,19 +1571,19 @@
       <text/>
       <mc:AlternateContent>
         <mc:Choice Requires="v2">
-          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="justify">
             <anchor moveWithCells="false" sizeWithCells="false">
               <xdr:from>
                 <xdr:col>1</xdr:col>
-                <xdr:colOff>28</xdr:colOff>
-                <xdr:row>430</xdr:row>
-                <xdr:rowOff>8</xdr:rowOff>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>131</xdr:row>
+                <xdr:rowOff>9</xdr:rowOff>
               </xdr:from>
               <xdr:to>
                 <xdr:col>2</xdr:col>
-                <xdr:colOff>217</xdr:colOff>
-                <xdr:row>439</xdr:row>
-                <xdr:rowOff>14</xdr:rowOff>
+                <xdr:colOff>-338</xdr:colOff>
+                <xdr:row>137</xdr:row>
+                <xdr:rowOff>19</xdr:rowOff>
               </xdr:to>
             </anchor>
           </commentPr>
@@ -1596,7 +1596,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1175" uniqueCount="1134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1178" uniqueCount="1137">
   <si>
     <t xml:space="preserve">GENIUS #</t>
   </si>
@@ -4557,6 +4557,35 @@
   </si>
   <si>
     <t xml:space="preserve">ROD, 00.500ODx144.000, ALUMINUM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70-02188-0950</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SCALLOPED </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">T-TRIM@95</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">SCALLOPED T MOULDING 6063/T5</t>
   </si>
   <si>
     <t xml:space="preserve"> - PO </t>
@@ -5029,7 +5058,7 @@
     <numFmt numFmtId="165" formatCode="d\-mmm"/>
     <numFmt numFmtId="166" formatCode="0"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -5072,6 +5101,14 @@
       <sz val="14"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="14"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
@@ -5193,148 +5230,152 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="37">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5636,3664 +5677,3675 @@
   <sheetPr filterMode="true">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C335"/>
+  <dimension ref="A1:C336"/>
   <sheetFormatPr defaultColWidth="8.6171875" defaultRowHeight="24.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26.72"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="57.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="108.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16383" style="0" width="10.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="26.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="57.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="108.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16383" style="1" width="10.49"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="60.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="5" t="s">
+      <c r="B2" s="5"/>
+      <c r="C2" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="8" t="s">
+      <c r="B3" s="8"/>
+      <c r="C3" s="9" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="6" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="9" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="4"/>
-      <c r="C6" s="5" t="s">
+      <c r="B6" s="5"/>
+      <c r="C6" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="9" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="6" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="9" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="6" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="9" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="6" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="9" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="6" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="B15" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C15" s="9" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="6" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="6" t="s">
+      <c r="A17" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B17" s="7" t="s">
+      <c r="B17" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="C17" s="9" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="6" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="6" t="s">
+      <c r="A19" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B19" s="7" t="s">
+      <c r="B19" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="C19" s="8" t="s">
+      <c r="C19" s="9" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C20" s="6" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="6" t="s">
+      <c r="A21" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B21" s="7" t="s">
+      <c r="B21" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="C21" s="8" t="s">
+      <c r="C21" s="9" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="3" t="s">
+      <c r="A22" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="C22" s="6" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="6" t="s">
+      <c r="A23" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="B23" s="7" t="s">
+      <c r="B23" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="C23" s="8" t="s">
+      <c r="C23" s="9" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="3" t="s">
+      <c r="A24" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="B24" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="C24" s="6" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="6" t="s">
+      <c r="A25" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="B25" s="7" t="s">
+      <c r="B25" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="C25" s="8" t="s">
+      <c r="C25" s="9" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="3" t="s">
+      <c r="A26" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="B26" s="4" t="s">
+      <c r="B26" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="C26" s="5" t="s">
+      <c r="C26" s="6" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="6" t="s">
+      <c r="A27" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="B27" s="7" t="s">
+      <c r="B27" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="C27" s="8" t="s">
+      <c r="C27" s="9" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="3" t="s">
+      <c r="A28" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="B28" s="4" t="s">
+      <c r="B28" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="C28" s="5" t="s">
+      <c r="C28" s="6" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="6" t="s">
+      <c r="A29" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="B29" s="7" t="s">
+      <c r="B29" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="C29" s="8" t="s">
+      <c r="C29" s="9" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="3" t="s">
+      <c r="A30" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="B30" s="4" t="s">
+      <c r="B30" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="C30" s="5" t="s">
+      <c r="C30" s="6" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="6" t="s">
+      <c r="A31" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="B31" s="7" t="s">
+      <c r="B31" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="C31" s="8" t="s">
+      <c r="C31" s="9" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="3" t="s">
+      <c r="A32" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="B32" s="4" t="s">
+      <c r="B32" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="C32" s="5" t="s">
+      <c r="C32" s="6" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="6" t="s">
+      <c r="A33" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="B33" s="7" t="s">
+      <c r="B33" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="C33" s="8" t="s">
+      <c r="C33" s="9" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="3" t="s">
+      <c r="A34" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="B34" s="4" t="s">
+      <c r="B34" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="C34" s="5" t="s">
+      <c r="C34" s="6" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="6" t="s">
+      <c r="A35" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="B35" s="7" t="s">
+      <c r="B35" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="C35" s="8" t="s">
+      <c r="C35" s="9" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="3" t="s">
+      <c r="A36" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="B36" s="4" t="s">
+      <c r="B36" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="C36" s="5" t="s">
+      <c r="C36" s="6" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="3" t="s">
+      <c r="A37" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="B37" s="4" t="s">
+      <c r="B37" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="C37" s="5"/>
+      <c r="C37" s="6"/>
     </row>
     <row r="38" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="6" t="s">
+      <c r="A38" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="B38" s="7" t="s">
+      <c r="B38" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="C38" s="8" t="s">
+      <c r="C38" s="9" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="3" t="s">
+      <c r="A39" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="B39" s="4" t="s">
+      <c r="B39" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="C39" s="5" t="s">
+      <c r="C39" s="6" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="6" t="s">
+      <c r="A40" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="B40" s="7" t="s">
+      <c r="B40" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="C40" s="8" t="s">
+      <c r="C40" s="9" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="3" t="s">
+      <c r="A41" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="B41" s="4" t="s">
+      <c r="B41" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="C41" s="5" t="s">
+      <c r="C41" s="6" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="6" t="s">
+      <c r="A42" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="B42" s="7" t="s">
+      <c r="B42" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="C42" s="8" t="s">
+      <c r="C42" s="9" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="3" t="s">
+      <c r="A43" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B43" s="4" t="s">
+      <c r="B43" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="C43" s="5" t="s">
+      <c r="C43" s="6" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="6" t="s">
+      <c r="A44" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="B44" s="7" t="s">
+      <c r="B44" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="C44" s="8" t="s">
+      <c r="C44" s="9" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="3" t="s">
+      <c r="A45" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="B45" s="4" t="s">
+      <c r="B45" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="C45" s="5" t="s">
+      <c r="C45" s="6" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="6" t="s">
+      <c r="A46" s="7" t="s">
         <v>131</v>
       </c>
-      <c r="B46" s="7" t="s">
+      <c r="B46" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="C46" s="8" t="s">
+      <c r="C46" s="9" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="3" t="s">
+      <c r="A47" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="B47" s="4" t="s">
+      <c r="B47" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="C47" s="5" t="s">
+      <c r="C47" s="6" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="6" t="s">
+      <c r="A48" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="B48" s="7" t="s">
+      <c r="B48" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="C48" s="8" t="s">
+      <c r="C48" s="9" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="3" t="s">
+      <c r="A49" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="B49" s="4" t="s">
+      <c r="B49" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="C49" s="5" t="s">
+      <c r="C49" s="6" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="6" t="s">
+      <c r="A50" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B50" s="7" t="s">
+      <c r="B50" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="C50" s="8" t="s">
+      <c r="C50" s="9" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="3" t="s">
+      <c r="A51" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="B51" s="4" t="s">
+      <c r="B51" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="C51" s="5" t="s">
+      <c r="C51" s="6" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="6" t="s">
+      <c r="A52" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="B52" s="7" t="s">
+      <c r="B52" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="C52" s="8" t="s">
+      <c r="C52" s="9" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="3" t="s">
+      <c r="A53" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="B53" s="4" t="s">
+      <c r="B53" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="C53" s="5" t="s">
+      <c r="C53" s="6" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="6" t="s">
+      <c r="A54" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="B54" s="7" t="s">
+      <c r="B54" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="C54" s="8" t="s">
+      <c r="C54" s="9" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="3" t="s">
+      <c r="A55" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="B55" s="4" t="s">
+      <c r="B55" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="C55" s="5" t="s">
+      <c r="C55" s="6" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="6" t="s">
+      <c r="A56" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="B56" s="7" t="s">
+      <c r="B56" s="8" t="s">
         <v>162</v>
       </c>
-      <c r="C56" s="8" t="s">
+      <c r="C56" s="9" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="3" t="s">
+      <c r="A57" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="B57" s="4" t="s">
+      <c r="B57" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="C57" s="5" t="s">
+      <c r="C57" s="6" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="6" t="s">
+      <c r="A58" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="B58" s="7" t="s">
+      <c r="B58" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="C58" s="8" t="s">
+      <c r="C58" s="9" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="3" t="s">
+      <c r="A59" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="B59" s="4" t="s">
+      <c r="B59" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="C59" s="5" t="s">
+      <c r="C59" s="6" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="3" t="s">
+      <c r="A60" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="B60" s="4" t="s">
+      <c r="B60" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="C60" s="5" t="s">
+      <c r="C60" s="6" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="6" t="s">
+      <c r="A61" s="7" t="s">
         <v>176</v>
       </c>
-      <c r="B61" s="7" t="s">
+      <c r="B61" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="C61" s="8" t="s">
+      <c r="C61" s="9" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A62" s="3" t="s">
+      <c r="A62" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="B62" s="4" t="s">
+      <c r="B62" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="C62" s="5" t="s">
+      <c r="C62" s="6" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A63" s="6" t="s">
+      <c r="A63" s="7" t="s">
         <v>182</v>
       </c>
-      <c r="B63" s="7" t="s">
+      <c r="B63" s="8" t="s">
         <v>183</v>
       </c>
-      <c r="C63" s="8" t="s">
+      <c r="C63" s="9" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A64" s="3" t="s">
+      <c r="A64" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="B64" s="4" t="s">
+      <c r="B64" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="C64" s="5" t="s">
+      <c r="C64" s="6" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A65" s="6" t="s">
+      <c r="A65" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="B65" s="7" t="s">
+      <c r="B65" s="8" t="s">
         <v>189</v>
       </c>
-      <c r="C65" s="8" t="s">
+      <c r="C65" s="9" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A66" s="3" t="s">
+      <c r="A66" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="B66" s="4" t="s">
+      <c r="B66" s="5" t="s">
         <v>192</v>
       </c>
-      <c r="C66" s="5" t="s">
+      <c r="C66" s="6" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A67" s="6" t="s">
+      <c r="A67" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="B67" s="7" t="s">
+      <c r="B67" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="C67" s="8" t="s">
+      <c r="C67" s="9" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A68" s="3" t="s">
+      <c r="A68" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="B68" s="4" t="s">
+      <c r="B68" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="C68" s="5" t="s">
+      <c r="C68" s="6" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A69" s="6" t="s">
+      <c r="A69" s="7" t="s">
         <v>200</v>
       </c>
-      <c r="B69" s="7" t="s">
+      <c r="B69" s="8" t="s">
         <v>201</v>
       </c>
-      <c r="C69" s="8" t="s">
+      <c r="C69" s="9" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A70" s="3" t="s">
+      <c r="A70" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="B70" s="4" t="s">
+      <c r="B70" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="C70" s="5" t="s">
+      <c r="C70" s="6" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A71" s="6" t="s">
+      <c r="A71" s="7" t="s">
         <v>206</v>
       </c>
-      <c r="B71" s="7" t="s">
+      <c r="B71" s="8" t="s">
         <v>207</v>
       </c>
-      <c r="C71" s="8" t="s">
+      <c r="C71" s="9" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A72" s="3" t="s">
+      <c r="A72" s="4" t="s">
         <v>209</v>
       </c>
-      <c r="B72" s="4" t="s">
+      <c r="B72" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="C72" s="5" t="s">
+      <c r="C72" s="6" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A73" s="6" t="s">
+      <c r="A73" s="7" t="s">
         <v>212</v>
       </c>
-      <c r="B73" s="7" t="s">
+      <c r="B73" s="8" t="s">
         <v>213</v>
       </c>
-      <c r="C73" s="8" t="s">
+      <c r="C73" s="9" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A74" s="3" t="s">
+      <c r="A74" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="B74" s="4" t="s">
+      <c r="B74" s="5" t="s">
         <v>216</v>
       </c>
-      <c r="C74" s="5" t="s">
+      <c r="C74" s="6" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A75" s="6" t="s">
+      <c r="A75" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="B75" s="7" t="s">
+      <c r="B75" s="8" t="s">
         <v>219</v>
       </c>
-      <c r="C75" s="8" t="s">
+      <c r="C75" s="9" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A76" s="3" t="s">
+      <c r="A76" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="B76" s="4" t="s">
+      <c r="B76" s="5" t="s">
         <v>222</v>
       </c>
-      <c r="C76" s="5" t="s">
+      <c r="C76" s="6" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A77" s="6" t="s">
+      <c r="A77" s="7" t="s">
         <v>224</v>
       </c>
-      <c r="B77" s="7" t="s">
+      <c r="B77" s="8" t="s">
         <v>225</v>
       </c>
-      <c r="C77" s="8" t="s">
+      <c r="C77" s="9" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A78" s="3" t="s">
+      <c r="A78" s="4" t="s">
         <v>227</v>
       </c>
-      <c r="B78" s="4" t="s">
+      <c r="B78" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="C78" s="5" t="s">
+      <c r="C78" s="6" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A79" s="6" t="s">
+      <c r="A79" s="7" t="s">
         <v>230</v>
       </c>
-      <c r="B79" s="7" t="s">
+      <c r="B79" s="8" t="s">
         <v>231</v>
       </c>
-      <c r="C79" s="8" t="s">
+      <c r="C79" s="9" t="s">
         <v>232</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A80" s="3" t="s">
+      <c r="A80" s="4" t="s">
         <v>233</v>
       </c>
-      <c r="B80" s="4" t="s">
+      <c r="B80" s="5" t="s">
         <v>234</v>
       </c>
-      <c r="C80" s="5" t="s">
+      <c r="C80" s="6" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A81" s="6" t="s">
+      <c r="A81" s="7" t="s">
         <v>236</v>
       </c>
-      <c r="B81" s="7" t="s">
+      <c r="B81" s="8" t="s">
         <v>237</v>
       </c>
-      <c r="C81" s="8" t="s">
+      <c r="C81" s="9" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A82" s="6" t="s">
+      <c r="A82" s="7" t="s">
         <v>239</v>
       </c>
-      <c r="B82" s="7" t="s">
+      <c r="B82" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C82" s="8" t="s">
+      <c r="C82" s="9" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A83" s="3" t="s">
+      <c r="A83" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="B83" s="4"/>
-      <c r="C83" s="5" t="s">
+      <c r="B83" s="5"/>
+      <c r="C83" s="6" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A84" s="6" t="s">
+      <c r="A84" s="7" t="s">
         <v>244</v>
       </c>
-      <c r="B84" s="7" t="s">
+      <c r="B84" s="8" t="s">
         <v>245</v>
       </c>
-      <c r="C84" s="8" t="s">
+      <c r="C84" s="9" t="s">
         <v>246</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A85" s="3" t="s">
+      <c r="A85" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="B85" s="4" t="s">
+      <c r="B85" s="5" t="s">
         <v>248</v>
       </c>
-      <c r="C85" s="5" t="s">
+      <c r="C85" s="6" t="s">
         <v>249</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A86" s="6" t="s">
+      <c r="A86" s="7" t="s">
         <v>250</v>
       </c>
-      <c r="B86" s="7" t="s">
+      <c r="B86" s="8" t="s">
         <v>251</v>
       </c>
-      <c r="C86" s="8" t="s">
+      <c r="C86" s="9" t="s">
         <v>252</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A87" s="3" t="s">
+      <c r="A87" s="4" t="s">
         <v>253</v>
       </c>
-      <c r="B87" s="4" t="s">
+      <c r="B87" s="5" t="s">
         <v>254</v>
       </c>
-      <c r="C87" s="5" t="s">
+      <c r="C87" s="6" t="s">
         <v>255</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A88" s="6" t="s">
+      <c r="A88" s="7" t="s">
         <v>256</v>
       </c>
-      <c r="B88" s="7" t="s">
+      <c r="B88" s="8" t="s">
         <v>257</v>
       </c>
-      <c r="C88" s="8" t="s">
+      <c r="C88" s="9" t="s">
         <v>258</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A89" s="3" t="s">
+      <c r="A89" s="4" t="s">
         <v>259</v>
       </c>
-      <c r="B89" s="4" t="s">
+      <c r="B89" s="5" t="s">
         <v>260</v>
       </c>
-      <c r="C89" s="5" t="s">
+      <c r="C89" s="6" t="s">
         <v>261</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A90" s="6" t="s">
+      <c r="A90" s="7" t="s">
         <v>262</v>
       </c>
-      <c r="B90" s="7" t="s">
+      <c r="B90" s="8" t="s">
         <v>263</v>
       </c>
-      <c r="C90" s="8" t="s">
+      <c r="C90" s="9" t="s">
         <v>264</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A91" s="3" t="s">
+      <c r="A91" s="4" t="s">
         <v>265</v>
       </c>
-      <c r="B91" s="4" t="s">
+      <c r="B91" s="5" t="s">
         <v>266</v>
       </c>
-      <c r="C91" s="5" t="s">
+      <c r="C91" s="6" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A92" s="6" t="s">
+      <c r="A92" s="7" t="s">
         <v>268</v>
       </c>
-      <c r="B92" s="7" t="s">
+      <c r="B92" s="8" t="s">
         <v>269</v>
       </c>
-      <c r="C92" s="8" t="s">
+      <c r="C92" s="9" t="s">
         <v>270</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A93" s="6" t="s">
+      <c r="A93" s="7" t="s">
         <v>271</v>
       </c>
-      <c r="B93" s="7" t="s">
+      <c r="B93" s="8" t="s">
         <v>272</v>
       </c>
-      <c r="C93" s="8" t="s">
+      <c r="C93" s="9" t="s">
         <v>273</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A94" s="3" t="s">
+      <c r="A94" s="4" t="s">
         <v>274</v>
       </c>
-      <c r="B94" s="4" t="s">
+      <c r="B94" s="5" t="s">
         <v>275</v>
       </c>
-      <c r="C94" s="5" t="s">
+      <c r="C94" s="6" t="s">
         <v>276</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A95" s="6" t="s">
+      <c r="A95" s="7" t="s">
         <v>277</v>
       </c>
-      <c r="B95" s="7" t="s">
+      <c r="B95" s="8" t="s">
         <v>278</v>
       </c>
-      <c r="C95" s="8" t="s">
+      <c r="C95" s="9" t="s">
         <v>279</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A96" s="3" t="s">
+      <c r="A96" s="4" t="s">
         <v>280</v>
       </c>
-      <c r="B96" s="4" t="s">
+      <c r="B96" s="5" t="s">
         <v>281</v>
       </c>
-      <c r="C96" s="5" t="s">
+      <c r="C96" s="6" t="s">
         <v>282</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A97" s="6" t="s">
+      <c r="A97" s="7" t="s">
         <v>283</v>
       </c>
-      <c r="B97" s="7" t="s">
+      <c r="B97" s="8" t="s">
         <v>284</v>
       </c>
-      <c r="C97" s="8" t="s">
+      <c r="C97" s="9" t="s">
         <v>285</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A98" s="3" t="s">
+      <c r="A98" s="4" t="s">
         <v>286</v>
       </c>
-      <c r="B98" s="4" t="s">
+      <c r="B98" s="5" t="s">
         <v>287</v>
       </c>
-      <c r="C98" s="5" t="s">
+      <c r="C98" s="6" t="s">
         <v>288</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A99" s="6" t="s">
+      <c r="A99" s="7" t="s">
         <v>289</v>
       </c>
-      <c r="B99" s="7" t="s">
+      <c r="B99" s="8" t="s">
         <v>290</v>
       </c>
-      <c r="C99" s="8" t="s">
+      <c r="C99" s="9" t="s">
         <v>291</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A100" s="3" t="s">
+      <c r="A100" s="4" t="s">
         <v>292</v>
       </c>
-      <c r="B100" s="4" t="s">
+      <c r="B100" s="5" t="s">
         <v>293</v>
       </c>
-      <c r="C100" s="5" t="s">
+      <c r="C100" s="6" t="s">
         <v>294</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A101" s="6" t="s">
+      <c r="A101" s="7" t="s">
         <v>295</v>
       </c>
-      <c r="B101" s="7" t="s">
+      <c r="B101" s="8" t="s">
         <v>296</v>
       </c>
-      <c r="C101" s="8" t="s">
+      <c r="C101" s="9" t="s">
         <v>297</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A102" s="3" t="s">
+      <c r="A102" s="4" t="s">
         <v>298</v>
       </c>
-      <c r="B102" s="4" t="s">
+      <c r="B102" s="5" t="s">
         <v>299</v>
       </c>
-      <c r="C102" s="5" t="s">
+      <c r="C102" s="6" t="s">
         <v>300</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A103" s="6" t="s">
+      <c r="A103" s="7" t="s">
         <v>301</v>
       </c>
-      <c r="B103" s="7" t="s">
+      <c r="B103" s="8" t="s">
         <v>302</v>
       </c>
-      <c r="C103" s="8" t="s">
+      <c r="C103" s="9" t="s">
         <v>303</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A104" s="3" t="s">
+      <c r="A104" s="4" t="s">
         <v>304</v>
       </c>
-      <c r="B104" s="4" t="s">
+      <c r="B104" s="5" t="s">
         <v>305</v>
       </c>
-      <c r="C104" s="5" t="s">
+      <c r="C104" s="6" t="s">
         <v>306</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A105" s="6" t="s">
+      <c r="A105" s="7" t="s">
         <v>307</v>
       </c>
-      <c r="B105" s="7" t="s">
+      <c r="B105" s="8" t="s">
         <v>308</v>
       </c>
-      <c r="C105" s="8" t="s">
+      <c r="C105" s="9" t="s">
         <v>309</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A106" s="3" t="s">
+      <c r="A106" s="4" t="s">
         <v>310</v>
       </c>
-      <c r="B106" s="4" t="s">
+      <c r="B106" s="5" t="s">
         <v>311</v>
       </c>
-      <c r="C106" s="5" t="s">
+      <c r="C106" s="6" t="s">
         <v>312</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A107" s="6" t="s">
+      <c r="A107" s="7" t="s">
         <v>313</v>
       </c>
-      <c r="B107" s="7" t="s">
+      <c r="B107" s="8" t="s">
         <v>314</v>
       </c>
-      <c r="C107" s="8" t="s">
+      <c r="C107" s="9" t="s">
         <v>315</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A108" s="3" t="s">
+      <c r="A108" s="4" t="s">
         <v>316</v>
       </c>
-      <c r="B108" s="4" t="s">
+      <c r="B108" s="5" t="s">
         <v>317</v>
       </c>
-      <c r="C108" s="5" t="s">
+      <c r="C108" s="6" t="s">
         <v>318</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A109" s="6" t="s">
+      <c r="A109" s="7" t="s">
         <v>319</v>
       </c>
-      <c r="B109" s="7" t="s">
+      <c r="B109" s="8" t="s">
         <v>320</v>
       </c>
-      <c r="C109" s="8" t="s">
+      <c r="C109" s="9" t="s">
         <v>321</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A110" s="3" t="s">
+      <c r="A110" s="4" t="s">
         <v>322</v>
       </c>
-      <c r="B110" s="4" t="s">
+      <c r="B110" s="5" t="s">
         <v>323</v>
       </c>
-      <c r="C110" s="5" t="s">
+      <c r="C110" s="6" t="s">
         <v>324</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A111" s="6" t="s">
+      <c r="A111" s="7" t="s">
         <v>325</v>
       </c>
-      <c r="B111" s="7" t="s">
+      <c r="B111" s="8" t="s">
         <v>326</v>
       </c>
-      <c r="C111" s="8" t="s">
+      <c r="C111" s="9" t="s">
         <v>327</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A112" s="3" t="s">
+      <c r="A112" s="4" t="s">
         <v>328</v>
       </c>
-      <c r="B112" s="4" t="s">
+      <c r="B112" s="5" t="s">
         <v>329</v>
       </c>
-      <c r="C112" s="5" t="s">
+      <c r="C112" s="6" t="s">
         <v>330</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A113" s="6" t="s">
+      <c r="A113" s="7" t="s">
         <v>331</v>
       </c>
-      <c r="B113" s="7" t="s">
+      <c r="B113" s="8" t="s">
         <v>332</v>
       </c>
-      <c r="C113" s="8" t="s">
+      <c r="C113" s="9" t="s">
         <v>333</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A114" s="3" t="s">
+      <c r="A114" s="4" t="s">
         <v>334</v>
       </c>
-      <c r="B114" s="4" t="s">
+      <c r="B114" s="5" t="s">
         <v>335</v>
       </c>
-      <c r="C114" s="5" t="s">
+      <c r="C114" s="6" t="s">
         <v>336</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A115" s="6" t="s">
+      <c r="A115" s="7" t="s">
         <v>337</v>
       </c>
-      <c r="B115" s="7" t="s">
+      <c r="B115" s="8" t="s">
         <v>338</v>
       </c>
-      <c r="C115" s="8" t="s">
+      <c r="C115" s="9" t="s">
         <v>339</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A116" s="3" t="s">
+      <c r="A116" s="4" t="s">
         <v>340</v>
       </c>
-      <c r="B116" s="4" t="s">
+      <c r="B116" s="5" t="s">
         <v>341</v>
       </c>
-      <c r="C116" s="5" t="s">
+      <c r="C116" s="6" t="s">
         <v>342</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A117" s="6" t="s">
+      <c r="A117" s="7" t="s">
         <v>343</v>
       </c>
-      <c r="B117" s="7" t="s">
+      <c r="B117" s="8" t="s">
         <v>344</v>
       </c>
-      <c r="C117" s="8" t="s">
+      <c r="C117" s="9" t="s">
         <v>345</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A118" s="3" t="s">
+      <c r="A118" s="4" t="s">
         <v>346</v>
       </c>
-      <c r="B118" s="4" t="s">
+      <c r="B118" s="5" t="s">
         <v>347</v>
       </c>
-      <c r="C118" s="5" t="s">
+      <c r="C118" s="6" t="s">
         <v>348</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A119" s="6" t="s">
+      <c r="A119" s="7" t="s">
         <v>349</v>
       </c>
-      <c r="B119" s="7" t="s">
+      <c r="B119" s="8" t="s">
         <v>350</v>
       </c>
-      <c r="C119" s="8" t="s">
+      <c r="C119" s="9" t="s">
         <v>351</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A120" s="3" t="s">
+      <c r="A120" s="4" t="s">
         <v>352</v>
       </c>
-      <c r="B120" s="4" t="s">
+      <c r="B120" s="5" t="s">
         <v>353</v>
       </c>
-      <c r="C120" s="5" t="s">
+      <c r="C120" s="6" t="s">
         <v>354</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A121" s="6" t="s">
+      <c r="A121" s="7" t="s">
         <v>355</v>
       </c>
-      <c r="B121" s="7" t="s">
+      <c r="B121" s="8" t="s">
         <v>356</v>
       </c>
-      <c r="C121" s="8" t="s">
+      <c r="C121" s="9" t="s">
         <v>357</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A122" s="6" t="s">
+      <c r="A122" s="7" t="s">
         <v>358</v>
       </c>
-      <c r="B122" s="7" t="s">
+      <c r="B122" s="8" t="s">
         <v>359</v>
       </c>
-      <c r="C122" s="8" t="s">
+      <c r="C122" s="9" t="s">
         <v>360</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A123" s="3" t="s">
+      <c r="A123" s="4" t="s">
         <v>361</v>
       </c>
-      <c r="B123" s="4" t="s">
+      <c r="B123" s="5" t="s">
         <v>362</v>
       </c>
-      <c r="C123" s="5" t="s">
+      <c r="C123" s="6" t="s">
         <v>363</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A124" s="3" t="s">
+      <c r="A124" s="4" t="s">
         <v>364</v>
       </c>
-      <c r="B124" s="4" t="s">
+      <c r="B124" s="5" t="s">
         <v>365</v>
       </c>
-      <c r="C124" s="9" t="s">
+      <c r="C124" s="10" t="s">
         <v>365</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A125" s="6" t="s">
+      <c r="A125" s="7" t="s">
         <v>366</v>
       </c>
-      <c r="B125" s="7" t="s">
+      <c r="B125" s="8" t="s">
         <v>367</v>
       </c>
-      <c r="C125" s="8" t="s">
+      <c r="C125" s="9" t="s">
         <v>368</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A126" s="3" t="s">
+      <c r="A126" s="4" t="s">
         <v>369</v>
       </c>
-      <c r="B126" s="4" t="s">
+      <c r="B126" s="5" t="s">
         <v>370</v>
       </c>
-      <c r="C126" s="5" t="s">
+      <c r="C126" s="6" t="s">
         <v>371</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A127" s="6" t="s">
+      <c r="A127" s="7" t="s">
         <v>372</v>
       </c>
-      <c r="B127" s="7" t="s">
+      <c r="B127" s="8" t="s">
         <v>373</v>
       </c>
-      <c r="C127" s="8" t="s">
+      <c r="C127" s="9" t="s">
         <v>374</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A128" s="3" t="s">
+      <c r="A128" s="4" t="s">
         <v>375</v>
       </c>
-      <c r="B128" s="4" t="s">
+      <c r="B128" s="5" t="s">
         <v>376</v>
       </c>
-      <c r="C128" s="5" t="s">
+      <c r="C128" s="6" t="s">
         <v>377</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A129" s="6" t="s">
+      <c r="A129" s="7" t="s">
         <v>378</v>
       </c>
-      <c r="B129" s="7" t="s">
+      <c r="B129" s="8" t="s">
         <v>379</v>
       </c>
-      <c r="C129" s="8" t="s">
+      <c r="C129" s="9" t="s">
         <v>380</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A130" s="3" t="s">
+      <c r="A130" s="4" t="s">
         <v>381</v>
       </c>
-      <c r="B130" s="4" t="s">
+      <c r="B130" s="5" t="s">
         <v>382</v>
       </c>
-      <c r="C130" s="5" t="s">
+      <c r="C130" s="6" t="s">
         <v>383</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A131" s="6" t="s">
+      <c r="A131" s="7" t="s">
         <v>384</v>
       </c>
-      <c r="B131" s="7" t="s">
+      <c r="B131" s="8" t="s">
         <v>385</v>
       </c>
-      <c r="C131" s="8" t="s">
+      <c r="C131" s="9" t="s">
         <v>386</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A132" s="3" t="s">
+      <c r="A132" s="4" t="s">
         <v>387</v>
       </c>
-      <c r="B132" s="4" t="s">
+      <c r="B132" s="5" t="s">
         <v>388</v>
       </c>
-      <c r="C132" s="5" t="s">
+      <c r="C132" s="6" t="s">
         <v>389</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A133" s="6" t="s">
+      <c r="A133" s="7" t="s">
         <v>390</v>
       </c>
-      <c r="B133" s="7" t="s">
+      <c r="B133" s="8" t="s">
         <v>391</v>
       </c>
-      <c r="C133" s="8" t="s">
+      <c r="C133" s="9" t="s">
         <v>392</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A134" s="3" t="s">
+      <c r="A134" s="4" t="s">
         <v>393</v>
       </c>
-      <c r="B134" s="4" t="s">
+      <c r="B134" s="5" t="s">
         <v>394</v>
       </c>
-      <c r="C134" s="5" t="s">
+      <c r="C134" s="6" t="s">
         <v>395</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A135" s="6" t="s">
+      <c r="A135" s="7" t="s">
         <v>396</v>
       </c>
-      <c r="B135" s="7" t="s">
+      <c r="B135" s="8" t="s">
         <v>397</v>
       </c>
-      <c r="C135" s="8" t="s">
+      <c r="C135" s="9" t="s">
         <v>398</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A136" s="3" t="s">
+      <c r="A136" s="4" t="s">
         <v>399</v>
       </c>
-      <c r="B136" s="4" t="s">
+      <c r="B136" s="5" t="s">
         <v>400</v>
       </c>
-      <c r="C136" s="5" t="s">
+      <c r="C136" s="6" t="s">
         <v>401</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A137" s="6" t="s">
+      <c r="A137" s="7" t="s">
         <v>402</v>
       </c>
-      <c r="B137" s="7" t="s">
+      <c r="B137" s="8" t="s">
         <v>403</v>
       </c>
-      <c r="C137" s="8" t="s">
+      <c r="C137" s="9" t="s">
         <v>404</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A138" s="3" t="s">
+      <c r="A138" s="4" t="s">
         <v>405</v>
       </c>
-      <c r="B138" s="4" t="s">
+      <c r="B138" s="5" t="s">
         <v>406</v>
       </c>
-      <c r="C138" s="5" t="s">
+      <c r="C138" s="6" t="s">
         <v>407</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A139" s="6" t="s">
+      <c r="A139" s="7" t="s">
         <v>408</v>
       </c>
-      <c r="B139" s="7" t="s">
+      <c r="B139" s="8" t="s">
         <v>409</v>
       </c>
-      <c r="C139" s="8" t="s">
+      <c r="C139" s="9" t="s">
         <v>410</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A140" s="3" t="s">
+      <c r="A140" s="4" t="s">
         <v>411</v>
       </c>
-      <c r="B140" s="4" t="s">
+      <c r="B140" s="5" t="s">
         <v>412</v>
       </c>
-      <c r="C140" s="5" t="s">
+      <c r="C140" s="6" t="s">
         <v>413</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A141" s="6" t="s">
+      <c r="A141" s="7" t="s">
         <v>414</v>
       </c>
-      <c r="B141" s="7" t="s">
+      <c r="B141" s="8" t="s">
         <v>415</v>
       </c>
-      <c r="C141" s="8" t="s">
+      <c r="C141" s="9" t="s">
         <v>416</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A142" s="3" t="s">
+      <c r="A142" s="4" t="s">
         <v>417</v>
       </c>
-      <c r="B142" s="4" t="s">
+      <c r="B142" s="5" t="s">
         <v>418</v>
       </c>
-      <c r="C142" s="5" t="s">
+      <c r="C142" s="6" t="s">
         <v>419</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A143" s="6" t="s">
+      <c r="A143" s="7" t="s">
         <v>420</v>
       </c>
-      <c r="B143" s="7" t="s">
+      <c r="B143" s="8" t="s">
         <v>421</v>
       </c>
-      <c r="C143" s="8" t="s">
+      <c r="C143" s="9" t="s">
         <v>422</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A144" s="3" t="s">
+      <c r="A144" s="4" t="s">
         <v>423</v>
       </c>
-      <c r="B144" s="4" t="s">
+      <c r="B144" s="5" t="s">
         <v>424</v>
       </c>
-      <c r="C144" s="5" t="s">
+      <c r="C144" s="6" t="s">
         <v>425</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A145" s="6" t="s">
+      <c r="A145" s="7" t="s">
         <v>426</v>
       </c>
-      <c r="B145" s="7" t="s">
+      <c r="B145" s="8" t="s">
         <v>427</v>
       </c>
-      <c r="C145" s="8" t="s">
+      <c r="C145" s="9" t="s">
         <v>428</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A146" s="3" t="s">
+      <c r="A146" s="4" t="s">
         <v>429</v>
       </c>
-      <c r="B146" s="4" t="s">
+      <c r="B146" s="5" t="s">
         <v>430</v>
       </c>
-      <c r="C146" s="5" t="s">
+      <c r="C146" s="6" t="s">
         <v>431</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A147" s="6" t="s">
+      <c r="A147" s="7" t="s">
         <v>432</v>
       </c>
-      <c r="B147" s="7" t="s">
+      <c r="B147" s="8" t="s">
         <v>433</v>
       </c>
-      <c r="C147" s="8" t="s">
+      <c r="C147" s="9" t="s">
         <v>434</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A148" s="6" t="s">
+      <c r="A148" s="7" t="s">
         <v>435</v>
       </c>
-      <c r="B148" s="7" t="s">
+      <c r="B148" s="8" t="s">
         <v>436</v>
       </c>
-      <c r="C148" s="8" t="s">
+      <c r="C148" s="9" t="s">
         <v>437</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A149" s="6" t="s">
+      <c r="A149" s="7" t="s">
         <v>438</v>
       </c>
-      <c r="B149" s="7" t="s">
+      <c r="B149" s="8" t="s">
         <v>439</v>
       </c>
-      <c r="C149" s="8"/>
+      <c r="C149" s="9"/>
     </row>
     <row r="150" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A150" s="6" t="s">
+      <c r="A150" s="7" t="s">
         <v>440</v>
       </c>
-      <c r="B150" s="7" t="s">
+      <c r="B150" s="8" t="s">
         <v>441</v>
       </c>
-      <c r="C150" s="8"/>
+      <c r="C150" s="9"/>
     </row>
     <row r="151" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A151" s="3" t="s">
+      <c r="A151" s="4" t="s">
         <v>442</v>
       </c>
-      <c r="B151" s="4" t="s">
+      <c r="B151" s="5" t="s">
         <v>443</v>
       </c>
-      <c r="C151" s="5" t="s">
+      <c r="C151" s="6" t="s">
         <v>444</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A152" s="6" t="s">
+      <c r="A152" s="7" t="s">
         <v>445</v>
       </c>
-      <c r="B152" s="7" t="s">
+      <c r="B152" s="8" t="s">
         <v>446</v>
       </c>
-      <c r="C152" s="8" t="s">
+      <c r="C152" s="9" t="s">
         <v>447</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A153" s="3" t="s">
+      <c r="A153" s="4" t="s">
         <v>448</v>
       </c>
-      <c r="B153" s="4" t="s">
+      <c r="B153" s="5" t="s">
         <v>449</v>
       </c>
-      <c r="C153" s="5" t="s">
+      <c r="C153" s="6" t="s">
         <v>450</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A154" s="6" t="s">
+      <c r="A154" s="7" t="s">
         <v>451</v>
       </c>
-      <c r="B154" s="7" t="s">
+      <c r="B154" s="8" t="s">
         <v>452</v>
       </c>
-      <c r="C154" s="8" t="s">
+      <c r="C154" s="9" t="s">
         <v>453</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A155" s="3" t="s">
+      <c r="A155" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="B155" s="4" t="s">
+      <c r="B155" s="5" t="s">
         <v>455</v>
       </c>
-      <c r="C155" s="5" t="s">
+      <c r="C155" s="6" t="s">
         <v>456</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A156" s="6" t="s">
+      <c r="A156" s="7" t="s">
         <v>457</v>
       </c>
-      <c r="B156" s="7" t="s">
+      <c r="B156" s="8" t="s">
         <v>458</v>
       </c>
-      <c r="C156" s="8" t="s">
+      <c r="C156" s="9" t="s">
         <v>459</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A157" s="6" t="s">
+      <c r="A157" s="7" t="s">
         <v>460</v>
       </c>
-      <c r="B157" s="7" t="s">
+      <c r="B157" s="8" t="s">
         <v>461</v>
       </c>
-      <c r="C157" s="8" t="s">
+      <c r="C157" s="9" t="s">
         <v>462</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A158" s="3" t="s">
+      <c r="A158" s="4" t="s">
         <v>463</v>
       </c>
-      <c r="B158" s="4" t="s">
+      <c r="B158" s="5" t="s">
         <v>464</v>
       </c>
-      <c r="C158" s="5" t="s">
+      <c r="C158" s="6" t="s">
         <v>465</v>
       </c>
     </row>
     <row r="159" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A159" s="6" t="s">
+      <c r="A159" s="7" t="s">
         <v>466</v>
       </c>
-      <c r="B159" s="7" t="s">
+      <c r="B159" s="8" t="s">
         <v>467</v>
       </c>
-      <c r="C159" s="8" t="s">
+      <c r="C159" s="9" t="s">
         <v>468</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A160" s="6" t="s">
+      <c r="A160" s="7" t="s">
         <v>469</v>
       </c>
-      <c r="B160" s="7" t="s">
+      <c r="B160" s="8" t="s">
         <v>470</v>
       </c>
-      <c r="C160" s="8" t="s">
+      <c r="C160" s="9" t="s">
         <v>471</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A161" s="3" t="s">
+      <c r="A161" s="4" t="s">
         <v>472</v>
       </c>
-      <c r="B161" s="4" t="s">
+      <c r="B161" s="5" t="s">
         <v>473</v>
       </c>
-      <c r="C161" s="5" t="s">
+      <c r="C161" s="6" t="s">
         <v>474</v>
       </c>
     </row>
     <row r="162" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A162" s="6" t="s">
+      <c r="A162" s="7" t="s">
         <v>475</v>
       </c>
-      <c r="B162" s="7" t="s">
+      <c r="B162" s="8" t="s">
         <v>476</v>
       </c>
-      <c r="C162" s="8" t="s">
+      <c r="C162" s="9" t="s">
         <v>477</v>
       </c>
     </row>
     <row r="163" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A163" s="3" t="s">
+      <c r="A163" s="4" t="s">
         <v>478</v>
       </c>
-      <c r="B163" s="4" t="s">
+      <c r="B163" s="5" t="s">
         <v>479</v>
       </c>
-      <c r="C163" s="5" t="s">
+      <c r="C163" s="6" t="s">
         <v>480</v>
       </c>
     </row>
     <row r="164" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A164" s="6" t="s">
+      <c r="A164" s="7" t="s">
         <v>481</v>
       </c>
-      <c r="B164" s="7" t="s">
+      <c r="B164" s="8" t="s">
         <v>482</v>
       </c>
-      <c r="C164" s="8" t="s">
+      <c r="C164" s="9" t="s">
         <v>483</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A165" s="3" t="s">
+      <c r="A165" s="4" t="s">
         <v>484</v>
       </c>
-      <c r="B165" s="4" t="s">
+      <c r="B165" s="5" t="s">
         <v>485</v>
       </c>
-      <c r="C165" s="5" t="s">
+      <c r="C165" s="6" t="s">
         <v>486</v>
       </c>
     </row>
     <row r="166" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A166" s="6" t="s">
+      <c r="A166" s="7" t="s">
         <v>487</v>
       </c>
-      <c r="B166" s="7" t="s">
+      <c r="B166" s="8" t="s">
         <v>488</v>
       </c>
-      <c r="C166" s="8" t="s">
+      <c r="C166" s="9" t="s">
         <v>489</v>
       </c>
     </row>
     <row r="167" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A167" s="3" t="s">
+      <c r="A167" s="4" t="s">
         <v>490</v>
       </c>
-      <c r="B167" s="4" t="s">
+      <c r="B167" s="5" t="s">
         <v>491</v>
       </c>
-      <c r="C167" s="5" t="s">
+      <c r="C167" s="6" t="s">
         <v>492</v>
       </c>
     </row>
     <row r="168" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A168" s="6" t="s">
+      <c r="A168" s="7" t="s">
         <v>493</v>
       </c>
-      <c r="B168" s="7" t="s">
+      <c r="B168" s="8" t="s">
         <v>494</v>
       </c>
-      <c r="C168" s="8" t="s">
+      <c r="C168" s="9" t="s">
         <v>495</v>
       </c>
     </row>
     <row r="169" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A169" s="3" t="s">
+      <c r="A169" s="4" t="s">
         <v>496</v>
       </c>
-      <c r="B169" s="4" t="s">
+      <c r="B169" s="5" t="s">
         <v>497</v>
       </c>
-      <c r="C169" s="5" t="s">
+      <c r="C169" s="6" t="s">
         <v>498</v>
       </c>
     </row>
     <row r="170" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A170" s="6" t="s">
+      <c r="A170" s="7" t="s">
         <v>499</v>
       </c>
-      <c r="B170" s="7" t="s">
+      <c r="B170" s="8" t="s">
         <v>500</v>
       </c>
-      <c r="C170" s="8" t="s">
+      <c r="C170" s="9" t="s">
         <v>501</v>
       </c>
     </row>
     <row r="171" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A171" s="3" t="s">
+      <c r="A171" s="4" t="s">
         <v>502</v>
       </c>
-      <c r="B171" s="4" t="s">
+      <c r="B171" s="5" t="s">
         <v>503</v>
       </c>
-      <c r="C171" s="5" t="s">
+      <c r="C171" s="6" t="s">
         <v>504</v>
       </c>
     </row>
     <row r="172" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A172" s="6" t="s">
+      <c r="A172" s="7" t="s">
         <v>505</v>
       </c>
-      <c r="B172" s="7" t="s">
+      <c r="B172" s="8" t="s">
         <v>506</v>
       </c>
-      <c r="C172" s="8" t="s">
+      <c r="C172" s="9" t="s">
         <v>507</v>
       </c>
     </row>
     <row r="173" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A173" s="3" t="s">
+      <c r="A173" s="4" t="s">
         <v>508</v>
       </c>
-      <c r="B173" s="4" t="s">
+      <c r="B173" s="5" t="s">
         <v>509</v>
       </c>
-      <c r="C173" s="5" t="s">
+      <c r="C173" s="6" t="s">
         <v>510</v>
       </c>
     </row>
     <row r="174" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A174" s="6" t="s">
+      <c r="A174" s="7" t="s">
         <v>511</v>
       </c>
-      <c r="B174" s="7" t="s">
+      <c r="B174" s="8" t="s">
         <v>512</v>
       </c>
-      <c r="C174" s="8" t="s">
+      <c r="C174" s="9" t="s">
         <v>513</v>
       </c>
     </row>
     <row r="175" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A175" s="3" t="s">
+      <c r="A175" s="4" t="s">
         <v>514</v>
       </c>
-      <c r="B175" s="4" t="s">
+      <c r="B175" s="5" t="s">
         <v>515</v>
       </c>
-      <c r="C175" s="5" t="s">
+      <c r="C175" s="6" t="s">
         <v>516</v>
       </c>
     </row>
     <row r="176" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A176" s="6" t="s">
+      <c r="A176" s="7" t="s">
         <v>517</v>
       </c>
-      <c r="B176" s="7" t="s">
+      <c r="B176" s="8" t="s">
         <v>518</v>
       </c>
-      <c r="C176" s="8" t="s">
+      <c r="C176" s="9" t="s">
         <v>519</v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A177" s="3" t="s">
+      <c r="A177" s="4" t="s">
         <v>520</v>
       </c>
-      <c r="B177" s="4" t="s">
+      <c r="B177" s="5" t="s">
         <v>521</v>
       </c>
-      <c r="C177" s="5" t="s">
+      <c r="C177" s="6" t="s">
         <v>522</v>
       </c>
     </row>
     <row r="178" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A178" s="6" t="s">
+      <c r="A178" s="7" t="s">
         <v>523</v>
       </c>
-      <c r="B178" s="7" t="s">
+      <c r="B178" s="8" t="s">
         <v>524</v>
       </c>
-      <c r="C178" s="8" t="s">
+      <c r="C178" s="9" t="s">
         <v>525</v>
       </c>
     </row>
     <row r="179" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A179" s="3" t="s">
+      <c r="A179" s="4" t="s">
         <v>526</v>
       </c>
-      <c r="B179" s="4" t="s">
+      <c r="B179" s="5" t="s">
         <v>527</v>
       </c>
-      <c r="C179" s="5" t="s">
+      <c r="C179" s="6" t="s">
         <v>528</v>
       </c>
     </row>
     <row r="180" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A180" s="6" t="s">
+      <c r="A180" s="7" t="s">
         <v>529</v>
       </c>
-      <c r="B180" s="7" t="s">
+      <c r="B180" s="8" t="s">
         <v>530</v>
       </c>
-      <c r="C180" s="8" t="s">
+      <c r="C180" s="9" t="s">
         <v>531</v>
       </c>
     </row>
     <row r="181" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A181" s="3" t="s">
+      <c r="A181" s="4" t="s">
         <v>532</v>
       </c>
-      <c r="B181" s="4"/>
-      <c r="C181" s="5" t="s">
+      <c r="B181" s="5"/>
+      <c r="C181" s="6" t="s">
         <v>533</v>
       </c>
     </row>
     <row r="182" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A182" s="6" t="s">
+      <c r="A182" s="7" t="s">
         <v>534</v>
       </c>
-      <c r="B182" s="7"/>
-      <c r="C182" s="8" t="s">
+      <c r="B182" s="8"/>
+      <c r="C182" s="9" t="s">
         <v>535</v>
       </c>
     </row>
     <row r="183" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A183" s="3" t="s">
+      <c r="A183" s="4" t="s">
         <v>536</v>
       </c>
-      <c r="B183" s="4" t="s">
+      <c r="B183" s="5" t="s">
         <v>537</v>
       </c>
-      <c r="C183" s="5" t="s">
+      <c r="C183" s="6" t="s">
         <v>538</v>
       </c>
     </row>
     <row r="184" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A184" s="6" t="s">
+      <c r="A184" s="7" t="s">
         <v>539</v>
       </c>
-      <c r="B184" s="7" t="s">
+      <c r="B184" s="8" t="s">
         <v>540</v>
       </c>
-      <c r="C184" s="8" t="s">
+      <c r="C184" s="9" t="s">
         <v>541</v>
       </c>
     </row>
     <row r="185" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A185" s="3" t="s">
+      <c r="A185" s="4" t="s">
         <v>542</v>
       </c>
-      <c r="B185" s="4" t="s">
+      <c r="B185" s="5" t="s">
         <v>543</v>
       </c>
-      <c r="C185" s="5" t="s">
+      <c r="C185" s="6" t="s">
         <v>544</v>
       </c>
     </row>
     <row r="186" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A186" s="6" t="s">
+      <c r="A186" s="7" t="s">
         <v>545</v>
       </c>
-      <c r="B186" s="7" t="s">
+      <c r="B186" s="8" t="s">
         <v>546</v>
       </c>
-      <c r="C186" s="8" t="s">
+      <c r="C186" s="9" t="s">
         <v>547</v>
       </c>
     </row>
     <row r="187" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A187" s="3" t="s">
+      <c r="A187" s="4" t="s">
         <v>548</v>
       </c>
-      <c r="B187" s="4" t="s">
+      <c r="B187" s="5" t="s">
         <v>549</v>
       </c>
-      <c r="C187" s="5" t="s">
+      <c r="C187" s="6" t="s">
         <v>550</v>
       </c>
     </row>
     <row r="188" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A188" s="6" t="s">
+      <c r="A188" s="7" t="s">
         <v>551</v>
       </c>
-      <c r="B188" s="7" t="s">
+      <c r="B188" s="8" t="s">
         <v>552</v>
       </c>
-      <c r="C188" s="8" t="s">
+      <c r="C188" s="9" t="s">
         <v>553</v>
       </c>
     </row>
     <row r="189" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A189" s="3" t="s">
+      <c r="A189" s="4" t="s">
         <v>554</v>
       </c>
-      <c r="B189" s="4" t="s">
+      <c r="B189" s="5" t="s">
         <v>555</v>
       </c>
-      <c r="C189" s="5" t="s">
+      <c r="C189" s="6" t="s">
         <v>556</v>
       </c>
     </row>
     <row r="190" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A190" s="6" t="s">
+      <c r="A190" s="7" t="s">
         <v>557</v>
       </c>
-      <c r="B190" s="7" t="s">
+      <c r="B190" s="8" t="s">
         <v>558</v>
       </c>
-      <c r="C190" s="8" t="s">
+      <c r="C190" s="9" t="s">
         <v>559</v>
       </c>
     </row>
     <row r="191" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A191" s="6" t="s">
+      <c r="A191" s="7" t="s">
         <v>560</v>
       </c>
-      <c r="B191" s="7" t="s">
+      <c r="B191" s="8" t="s">
         <v>561</v>
       </c>
-      <c r="C191" s="8" t="s">
+      <c r="C191" s="9" t="s">
         <v>562</v>
       </c>
     </row>
     <row r="192" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A192" s="3" t="s">
+      <c r="A192" s="4" t="s">
         <v>563</v>
       </c>
-      <c r="B192" s="4" t="s">
+      <c r="B192" s="5" t="s">
         <v>564</v>
       </c>
-      <c r="C192" s="5" t="s">
+      <c r="C192" s="6" t="s">
         <v>565</v>
       </c>
     </row>
     <row r="193" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A193" s="6" t="s">
+      <c r="A193" s="7" t="s">
         <v>566</v>
       </c>
-      <c r="B193" s="7" t="s">
+      <c r="B193" s="8" t="s">
         <v>567</v>
       </c>
-      <c r="C193" s="8" t="s">
+      <c r="C193" s="9" t="s">
         <v>568</v>
       </c>
     </row>
     <row r="194" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A194" s="3" t="s">
+      <c r="A194" s="4" t="s">
         <v>569</v>
       </c>
-      <c r="B194" s="4" t="s">
+      <c r="B194" s="5" t="s">
         <v>570</v>
       </c>
-      <c r="C194" s="5" t="s">
+      <c r="C194" s="6" t="s">
         <v>571</v>
       </c>
     </row>
     <row r="195" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A195" s="6" t="s">
+      <c r="A195" s="7" t="s">
         <v>572</v>
       </c>
-      <c r="B195" s="7" t="s">
+      <c r="B195" s="8" t="s">
         <v>573</v>
       </c>
-      <c r="C195" s="8" t="s">
+      <c r="C195" s="9" t="s">
         <v>574</v>
       </c>
     </row>
     <row r="196" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A196" s="3" t="s">
+      <c r="A196" s="4" t="s">
         <v>575</v>
       </c>
-      <c r="B196" s="4" t="s">
+      <c r="B196" s="5" t="s">
         <v>576</v>
       </c>
-      <c r="C196" s="5" t="s">
+      <c r="C196" s="6" t="s">
         <v>577</v>
       </c>
     </row>
     <row r="197" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A197" s="6" t="s">
+      <c r="A197" s="7" t="s">
         <v>578</v>
       </c>
-      <c r="B197" s="7" t="s">
+      <c r="B197" s="8" t="s">
         <v>579</v>
       </c>
-      <c r="C197" s="8" t="s">
+      <c r="C197" s="9" t="s">
         <v>580</v>
       </c>
     </row>
     <row r="198" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A198" s="3" t="s">
+      <c r="A198" s="4" t="s">
         <v>581</v>
       </c>
-      <c r="B198" s="4" t="s">
+      <c r="B198" s="5" t="s">
         <v>582</v>
       </c>
-      <c r="C198" s="5" t="s">
+      <c r="C198" s="6" t="s">
         <v>583</v>
       </c>
     </row>
     <row r="199" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A199" s="6" t="s">
+      <c r="A199" s="7" t="s">
         <v>584</v>
       </c>
-      <c r="B199" s="7" t="s">
+      <c r="B199" s="8" t="s">
         <v>585</v>
       </c>
-      <c r="C199" s="8" t="s">
+      <c r="C199" s="9" t="s">
         <v>586</v>
       </c>
     </row>
     <row r="200" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A200" s="3" t="s">
+      <c r="A200" s="4" t="s">
         <v>587</v>
       </c>
-      <c r="B200" s="4" t="s">
+      <c r="B200" s="5" t="s">
         <v>588</v>
       </c>
-      <c r="C200" s="5" t="s">
+      <c r="C200" s="6" t="s">
         <v>589</v>
       </c>
     </row>
     <row r="201" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A201" s="6" t="s">
+      <c r="A201" s="7" t="s">
         <v>590</v>
       </c>
-      <c r="B201" s="7" t="s">
+      <c r="B201" s="8" t="s">
         <v>591</v>
       </c>
-      <c r="C201" s="8" t="s">
+      <c r="C201" s="9" t="s">
         <v>592</v>
       </c>
     </row>
     <row r="202" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A202" s="3" t="s">
+      <c r="A202" s="4" t="s">
         <v>593</v>
       </c>
-      <c r="B202" s="4" t="s">
+      <c r="B202" s="5" t="s">
         <v>594</v>
       </c>
-      <c r="C202" s="5" t="s">
+      <c r="C202" s="6" t="s">
         <v>595</v>
       </c>
     </row>
     <row r="203" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A203" s="6" t="s">
+      <c r="A203" s="7" t="s">
         <v>596</v>
       </c>
-      <c r="B203" s="7" t="s">
+      <c r="B203" s="8" t="s">
         <v>597</v>
       </c>
-      <c r="C203" s="8" t="s">
+      <c r="C203" s="9" t="s">
         <v>598</v>
       </c>
     </row>
     <row r="204" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A204" s="3" t="s">
+      <c r="A204" s="4" t="s">
         <v>599</v>
       </c>
-      <c r="B204" s="4" t="s">
+      <c r="B204" s="5" t="s">
         <v>600</v>
       </c>
-      <c r="C204" s="5" t="s">
+      <c r="C204" s="6" t="s">
         <v>601</v>
       </c>
     </row>
     <row r="205" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A205" s="6" t="s">
+      <c r="A205" s="7" t="s">
         <v>602</v>
       </c>
-      <c r="B205" s="7" t="s">
+      <c r="B205" s="8" t="s">
         <v>603</v>
       </c>
-      <c r="C205" s="8" t="s">
+      <c r="C205" s="9" t="s">
         <v>604</v>
       </c>
     </row>
     <row r="206" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A206" s="3" t="s">
+      <c r="A206" s="4" t="s">
         <v>605</v>
       </c>
-      <c r="B206" s="4" t="s">
+      <c r="B206" s="5" t="s">
         <v>606</v>
       </c>
-      <c r="C206" s="5" t="s">
+      <c r="C206" s="6" t="s">
         <v>607</v>
       </c>
     </row>
     <row r="207" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A207" s="6" t="s">
+      <c r="A207" s="7" t="s">
         <v>608</v>
       </c>
-      <c r="B207" s="7" t="s">
+      <c r="B207" s="8" t="s">
         <v>609</v>
       </c>
-      <c r="C207" s="8" t="s">
+      <c r="C207" s="9" t="s">
         <v>610</v>
       </c>
     </row>
     <row r="208" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A208" s="6" t="s">
+      <c r="A208" s="7" t="s">
         <v>611</v>
       </c>
-      <c r="B208" s="7" t="s">
+      <c r="B208" s="8" t="s">
         <v>612</v>
       </c>
-      <c r="C208" s="8" t="s">
+      <c r="C208" s="9" t="s">
         <v>613</v>
       </c>
     </row>
     <row r="209" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A209" s="3" t="s">
+      <c r="A209" s="4" t="s">
         <v>614</v>
       </c>
-      <c r="B209" s="4" t="s">
+      <c r="B209" s="5" t="s">
         <v>615</v>
       </c>
-      <c r="C209" s="5" t="s">
+      <c r="C209" s="6" t="s">
         <v>616</v>
       </c>
     </row>
     <row r="210" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A210" s="6" t="s">
+      <c r="A210" s="7" t="s">
         <v>617</v>
       </c>
-      <c r="B210" s="7" t="s">
+      <c r="B210" s="8" t="s">
         <v>618</v>
       </c>
-      <c r="C210" s="8" t="s">
+      <c r="C210" s="9" t="s">
         <v>619</v>
       </c>
     </row>
     <row r="211" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A211" s="3" t="s">
+      <c r="A211" s="4" t="s">
         <v>620</v>
       </c>
-      <c r="B211" s="4" t="s">
+      <c r="B211" s="5" t="s">
         <v>621</v>
       </c>
-      <c r="C211" s="5" t="s">
+      <c r="C211" s="6" t="s">
         <v>622</v>
       </c>
     </row>
     <row r="212" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A212" s="6" t="s">
+      <c r="A212" s="7" t="s">
         <v>623</v>
       </c>
-      <c r="B212" s="7" t="s">
+      <c r="B212" s="8" t="s">
         <v>624</v>
       </c>
-      <c r="C212" s="8" t="s">
+      <c r="C212" s="9" t="s">
         <v>625</v>
       </c>
     </row>
     <row r="213" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A213" s="3" t="s">
+      <c r="A213" s="4" t="s">
         <v>626</v>
       </c>
-      <c r="B213" s="4" t="s">
+      <c r="B213" s="5" t="s">
         <v>627</v>
       </c>
-      <c r="C213" s="5" t="s">
+      <c r="C213" s="6" t="s">
         <v>628</v>
       </c>
     </row>
     <row r="214" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A214" s="6" t="s">
+      <c r="A214" s="7" t="s">
         <v>629</v>
       </c>
-      <c r="B214" s="7" t="s">
+      <c r="B214" s="8" t="s">
         <v>630</v>
       </c>
-      <c r="C214" s="8" t="s">
+      <c r="C214" s="9" t="s">
         <v>631</v>
       </c>
     </row>
     <row r="215" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A215" s="3" t="s">
+      <c r="A215" s="4" t="s">
         <v>632</v>
       </c>
-      <c r="B215" s="4" t="s">
+      <c r="B215" s="5" t="s">
         <v>633</v>
       </c>
-      <c r="C215" s="5" t="s">
+      <c r="C215" s="6" t="s">
         <v>634</v>
       </c>
     </row>
     <row r="216" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A216" s="6" t="s">
+      <c r="A216" s="7" t="s">
         <v>635</v>
       </c>
-      <c r="B216" s="7" t="s">
+      <c r="B216" s="8" t="s">
         <v>636</v>
       </c>
-      <c r="C216" s="8" t="s">
+      <c r="C216" s="9" t="s">
         <v>637</v>
       </c>
     </row>
     <row r="217" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A217" s="3" t="s">
+      <c r="A217" s="4" t="s">
         <v>638</v>
       </c>
-      <c r="B217" s="4" t="s">
+      <c r="B217" s="5" t="s">
         <v>639</v>
       </c>
-      <c r="C217" s="5" t="s">
+      <c r="C217" s="6" t="s">
         <v>640</v>
       </c>
     </row>
     <row r="218" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A218" s="6" t="s">
+      <c r="A218" s="7" t="s">
         <v>641</v>
       </c>
-      <c r="B218" s="7" t="s">
+      <c r="B218" s="8" t="s">
         <v>642</v>
       </c>
-      <c r="C218" s="8" t="s">
+      <c r="C218" s="9" t="s">
         <v>643</v>
       </c>
     </row>
     <row r="219" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A219" s="3" t="s">
+      <c r="A219" s="4" t="s">
         <v>644</v>
       </c>
-      <c r="B219" s="4" t="s">
+      <c r="B219" s="5" t="s">
         <v>645</v>
       </c>
-      <c r="C219" s="5" t="s">
+      <c r="C219" s="6" t="s">
         <v>646</v>
       </c>
     </row>
     <row r="220" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A220" s="6" t="s">
+      <c r="A220" s="7" t="s">
         <v>647</v>
       </c>
-      <c r="B220" s="7" t="s">
+      <c r="B220" s="8" t="s">
         <v>648</v>
       </c>
-      <c r="C220" s="8" t="s">
+      <c r="C220" s="9" t="s">
         <v>649</v>
       </c>
     </row>
     <row r="221" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A221" s="3" t="s">
+      <c r="A221" s="4" t="s">
         <v>650</v>
       </c>
-      <c r="B221" s="4" t="s">
+      <c r="B221" s="5" t="s">
         <v>651</v>
       </c>
-      <c r="C221" s="5" t="s">
+      <c r="C221" s="6" t="s">
         <v>652</v>
       </c>
     </row>
     <row r="222" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A222" s="6" t="s">
+      <c r="A222" s="7" t="s">
         <v>653</v>
       </c>
-      <c r="B222" s="7" t="s">
+      <c r="B222" s="8" t="s">
         <v>654</v>
       </c>
-      <c r="C222" s="8" t="s">
+      <c r="C222" s="9" t="s">
         <v>655</v>
       </c>
     </row>
     <row r="223" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A223" s="3" t="s">
+      <c r="A223" s="4" t="s">
         <v>656</v>
       </c>
-      <c r="B223" s="4"/>
-      <c r="C223" s="5" t="s">
+      <c r="B223" s="5"/>
+      <c r="C223" s="6" t="s">
         <v>657</v>
       </c>
     </row>
     <row r="224" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A224" s="6" t="s">
+      <c r="A224" s="7" t="s">
         <v>658</v>
       </c>
-      <c r="B224" s="7" t="s">
+      <c r="B224" s="8" t="s">
         <v>659</v>
       </c>
-      <c r="C224" s="8" t="s">
+      <c r="C224" s="9" t="s">
         <v>660</v>
       </c>
     </row>
     <row r="225" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A225" s="3" t="s">
+      <c r="A225" s="4" t="s">
         <v>661</v>
       </c>
-      <c r="B225" s="4" t="s">
+      <c r="B225" s="5" t="s">
         <v>662</v>
       </c>
-      <c r="C225" s="5" t="s">
+      <c r="C225" s="6" t="s">
         <v>663</v>
       </c>
     </row>
     <row r="226" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A226" s="6" t="s">
+      <c r="A226" s="7" t="s">
         <v>664</v>
       </c>
-      <c r="B226" s="7" t="s">
+      <c r="B226" s="8" t="s">
         <v>665</v>
       </c>
-      <c r="C226" s="8" t="s">
+      <c r="C226" s="9" t="s">
         <v>666</v>
       </c>
     </row>
     <row r="227" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A227" s="6" t="s">
+      <c r="A227" s="7" t="s">
         <v>667</v>
       </c>
-      <c r="B227" s="7" t="s">
+      <c r="B227" s="8" t="s">
         <v>668</v>
       </c>
-      <c r="C227" s="5" t="s">
+      <c r="C227" s="6" t="s">
         <v>669</v>
       </c>
     </row>
     <row r="228" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A228" s="3" t="s">
+      <c r="A228" s="4" t="s">
         <v>670</v>
       </c>
-      <c r="B228" s="4" t="s">
+      <c r="B228" s="5" t="s">
         <v>671</v>
       </c>
-      <c r="C228" s="5" t="s">
+      <c r="C228" s="6" t="s">
         <v>672</v>
       </c>
     </row>
     <row r="229" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A229" s="6" t="s">
+      <c r="A229" s="7" t="s">
         <v>673</v>
       </c>
-      <c r="B229" s="7" t="s">
+      <c r="B229" s="8" t="s">
         <v>674</v>
       </c>
-      <c r="C229" s="8" t="s">
+      <c r="C229" s="9" t="s">
         <v>675</v>
       </c>
     </row>
     <row r="230" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A230" s="3" t="s">
+      <c r="A230" s="4" t="s">
         <v>676</v>
       </c>
-      <c r="B230" s="4" t="s">
+      <c r="B230" s="5" t="s">
         <v>677</v>
       </c>
-      <c r="C230" s="5" t="s">
+      <c r="C230" s="6" t="s">
         <v>678</v>
       </c>
     </row>
     <row r="231" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A231" s="6" t="s">
+      <c r="A231" s="7" t="s">
         <v>679</v>
       </c>
-      <c r="B231" s="7" t="s">
+      <c r="B231" s="8" t="s">
         <v>680</v>
       </c>
-      <c r="C231" s="8" t="s">
+      <c r="C231" s="9" t="s">
         <v>681</v>
       </c>
     </row>
     <row r="232" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A232" s="3" t="s">
+      <c r="A232" s="4" t="s">
         <v>682</v>
       </c>
-      <c r="B232" s="4" t="s">
+      <c r="B232" s="5" t="s">
         <v>683</v>
       </c>
-      <c r="C232" s="5" t="s">
+      <c r="C232" s="6" t="s">
         <v>684</v>
       </c>
     </row>
     <row r="233" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A233" s="6" t="s">
+      <c r="A233" s="7" t="s">
         <v>685</v>
       </c>
-      <c r="B233" s="7" t="s">
+      <c r="B233" s="8" t="s">
         <v>686</v>
       </c>
-      <c r="C233" s="8" t="s">
+      <c r="C233" s="9" t="s">
         <v>687</v>
       </c>
     </row>
     <row r="234" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A234" s="3" t="s">
+      <c r="A234" s="4" t="s">
         <v>688</v>
       </c>
-      <c r="B234" s="4" t="s">
+      <c r="B234" s="5" t="s">
         <v>689</v>
       </c>
-      <c r="C234" s="5" t="s">
+      <c r="C234" s="6" t="s">
         <v>690</v>
       </c>
     </row>
     <row r="235" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A235" s="6" t="s">
+      <c r="A235" s="7" t="s">
         <v>691</v>
       </c>
-      <c r="B235" s="7" t="s">
+      <c r="B235" s="8" t="s">
         <v>692</v>
       </c>
-      <c r="C235" s="8" t="s">
+      <c r="C235" s="9" t="s">
         <v>693</v>
       </c>
     </row>
     <row r="236" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A236" s="3" t="s">
+      <c r="A236" s="4" t="s">
         <v>694</v>
       </c>
-      <c r="B236" s="4" t="s">
+      <c r="B236" s="5" t="s">
         <v>695</v>
       </c>
-      <c r="C236" s="5" t="s">
+      <c r="C236" s="6" t="s">
         <v>696</v>
       </c>
     </row>
     <row r="237" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A237" s="6" t="s">
+      <c r="A237" s="7" t="s">
         <v>697</v>
       </c>
-      <c r="B237" s="7" t="s">
+      <c r="B237" s="8" t="s">
         <v>698</v>
       </c>
-      <c r="C237" s="8" t="s">
+      <c r="C237" s="9" t="s">
         <v>699</v>
       </c>
     </row>
     <row r="238" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A238" s="3" t="s">
+      <c r="A238" s="4" t="s">
         <v>700</v>
       </c>
-      <c r="B238" s="4" t="s">
+      <c r="B238" s="5" t="s">
         <v>701</v>
       </c>
-      <c r="C238" s="5" t="s">
+      <c r="C238" s="6" t="s">
         <v>702</v>
       </c>
     </row>
     <row r="239" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A239" s="6" t="s">
+      <c r="A239" s="7" t="s">
         <v>703</v>
       </c>
-      <c r="B239" s="7" t="s">
+      <c r="B239" s="8" t="s">
         <v>704</v>
       </c>
-      <c r="C239" s="8" t="s">
+      <c r="C239" s="9" t="s">
         <v>705</v>
       </c>
     </row>
     <row r="240" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A240" s="3" t="s">
+      <c r="A240" s="4" t="s">
         <v>706</v>
       </c>
-      <c r="B240" s="4" t="s">
+      <c r="B240" s="5" t="s">
         <v>707</v>
       </c>
-      <c r="C240" s="5" t="s">
+      <c r="C240" s="6" t="s">
         <v>708</v>
       </c>
     </row>
     <row r="241" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A241" s="6" t="s">
+      <c r="A241" s="7" t="s">
         <v>709</v>
       </c>
-      <c r="B241" s="7" t="s">
+      <c r="B241" s="8" t="s">
         <v>710</v>
       </c>
-      <c r="C241" s="8" t="s">
+      <c r="C241" s="9" t="s">
         <v>711</v>
       </c>
     </row>
     <row r="242" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A242" s="3" t="s">
+      <c r="A242" s="4" t="s">
         <v>712</v>
       </c>
-      <c r="B242" s="4" t="s">
+      <c r="B242" s="5" t="s">
         <v>713</v>
       </c>
-      <c r="C242" s="5" t="s">
+      <c r="C242" s="6" t="s">
         <v>714</v>
       </c>
     </row>
     <row r="243" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A243" s="6" t="s">
+      <c r="A243" s="7" t="s">
         <v>715</v>
       </c>
-      <c r="B243" s="7" t="s">
+      <c r="B243" s="8" t="s">
         <v>716</v>
       </c>
-      <c r="C243" s="8" t="s">
+      <c r="C243" s="9" t="s">
         <v>717</v>
       </c>
     </row>
     <row r="244" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A244" s="3" t="s">
+      <c r="A244" s="4" t="s">
         <v>718</v>
       </c>
-      <c r="B244" s="4" t="s">
+      <c r="B244" s="5" t="s">
         <v>719</v>
       </c>
-      <c r="C244" s="5" t="s">
+      <c r="C244" s="6" t="s">
         <v>720</v>
       </c>
     </row>
     <row r="245" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A245" s="6" t="s">
+      <c r="A245" s="7" t="s">
         <v>721</v>
       </c>
-      <c r="B245" s="7" t="s">
+      <c r="B245" s="8" t="s">
         <v>722</v>
       </c>
-      <c r="C245" s="8" t="s">
+      <c r="C245" s="9" t="s">
         <v>723</v>
       </c>
     </row>
     <row r="246" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A246" s="3" t="s">
+      <c r="A246" s="4" t="s">
         <v>724</v>
       </c>
-      <c r="B246" s="4" t="s">
+      <c r="B246" s="5" t="s">
         <v>725</v>
       </c>
-      <c r="C246" s="5" t="s">
+      <c r="C246" s="6" t="s">
         <v>726</v>
       </c>
     </row>
     <row r="247" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A247" s="6" t="s">
+      <c r="A247" s="7" t="s">
         <v>727</v>
       </c>
-      <c r="B247" s="7" t="s">
+      <c r="B247" s="8" t="s">
         <v>728</v>
       </c>
-      <c r="C247" s="8" t="s">
+      <c r="C247" s="9" t="s">
         <v>729</v>
       </c>
     </row>
     <row r="248" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A248" s="3" t="s">
+      <c r="A248" s="4" t="s">
         <v>730</v>
       </c>
-      <c r="B248" s="4" t="s">
+      <c r="B248" s="5" t="s">
         <v>731</v>
       </c>
-      <c r="C248" s="5" t="s">
+      <c r="C248" s="6" t="s">
         <v>732</v>
       </c>
     </row>
     <row r="249" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A249" s="6" t="s">
+      <c r="A249" s="7" t="s">
         <v>733</v>
       </c>
-      <c r="B249" s="7" t="s">
+      <c r="B249" s="8" t="s">
         <v>734</v>
       </c>
-      <c r="C249" s="8" t="s">
+      <c r="C249" s="9" t="s">
         <v>735</v>
       </c>
     </row>
     <row r="250" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A250" s="3" t="s">
+      <c r="A250" s="4" t="s">
         <v>736</v>
       </c>
-      <c r="B250" s="4" t="s">
+      <c r="B250" s="5" t="s">
         <v>737</v>
       </c>
-      <c r="C250" s="5" t="s">
+      <c r="C250" s="6" t="s">
         <v>738</v>
       </c>
     </row>
     <row r="251" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A251" s="6" t="s">
+      <c r="A251" s="7" t="s">
         <v>739</v>
       </c>
-      <c r="B251" s="7" t="s">
+      <c r="B251" s="8" t="s">
         <v>740</v>
       </c>
-      <c r="C251" s="8" t="s">
+      <c r="C251" s="9" t="s">
         <v>741</v>
       </c>
     </row>
     <row r="252" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A252" s="3" t="s">
+      <c r="A252" s="4" t="s">
         <v>742</v>
       </c>
-      <c r="B252" s="4" t="s">
+      <c r="B252" s="5" t="s">
         <v>743</v>
       </c>
-      <c r="C252" s="5" t="s">
+      <c r="C252" s="6" t="s">
         <v>744</v>
       </c>
     </row>
     <row r="253" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A253" s="6" t="s">
+      <c r="A253" s="7" t="s">
         <v>745</v>
       </c>
-      <c r="B253" s="7" t="s">
+      <c r="B253" s="8" t="s">
         <v>746</v>
       </c>
-      <c r="C253" s="8" t="s">
+      <c r="C253" s="9" t="s">
         <v>747</v>
       </c>
     </row>
     <row r="254" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A254" s="3" t="s">
+      <c r="A254" s="4" t="s">
         <v>748</v>
       </c>
-      <c r="B254" s="4" t="s">
+      <c r="B254" s="5" t="s">
         <v>749</v>
       </c>
-      <c r="C254" s="5" t="s">
+      <c r="C254" s="6" t="s">
         <v>750</v>
       </c>
     </row>
     <row r="255" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A255" s="6" t="s">
+      <c r="A255" s="7" t="s">
         <v>751</v>
       </c>
-      <c r="B255" s="7" t="s">
+      <c r="B255" s="8" t="s">
         <v>752</v>
       </c>
-      <c r="C255" s="8" t="s">
+      <c r="C255" s="9" t="s">
         <v>753</v>
       </c>
     </row>
     <row r="256" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A256" s="3" t="s">
+      <c r="A256" s="4" t="s">
         <v>754</v>
       </c>
-      <c r="B256" s="4" t="s">
+      <c r="B256" s="5" t="s">
         <v>755</v>
       </c>
-      <c r="C256" s="5" t="s">
+      <c r="C256" s="6" t="s">
         <v>756</v>
       </c>
     </row>
     <row r="257" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A257" s="6" t="s">
+      <c r="A257" s="7" t="s">
         <v>757</v>
       </c>
-      <c r="B257" s="7" t="s">
+      <c r="B257" s="8" t="s">
         <v>758</v>
       </c>
-      <c r="C257" s="8" t="s">
+      <c r="C257" s="9" t="s">
         <v>759</v>
       </c>
     </row>
     <row r="258" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A258" s="3" t="s">
+      <c r="A258" s="4" t="s">
         <v>760</v>
       </c>
-      <c r="B258" s="4" t="s">
+      <c r="B258" s="5" t="s">
         <v>761</v>
       </c>
-      <c r="C258" s="5" t="s">
+      <c r="C258" s="6" t="s">
         <v>762</v>
       </c>
     </row>
     <row r="259" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A259" s="6" t="s">
+      <c r="A259" s="7" t="s">
         <v>763</v>
       </c>
-      <c r="B259" s="7" t="s">
+      <c r="B259" s="8" t="s">
         <v>764</v>
       </c>
-      <c r="C259" s="8" t="s">
+      <c r="C259" s="9" t="s">
         <v>765</v>
       </c>
     </row>
     <row r="260" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A260" s="3" t="s">
+      <c r="A260" s="4" t="s">
         <v>766</v>
       </c>
-      <c r="B260" s="4" t="s">
+      <c r="B260" s="5" t="s">
         <v>767</v>
       </c>
-      <c r="C260" s="5" t="s">
+      <c r="C260" s="6" t="s">
         <v>768</v>
       </c>
     </row>
     <row r="261" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A261" s="6" t="s">
+      <c r="A261" s="7" t="s">
         <v>769</v>
       </c>
-      <c r="B261" s="7" t="s">
+      <c r="B261" s="8" t="s">
         <v>770</v>
       </c>
-      <c r="C261" s="8" t="s">
+      <c r="C261" s="9" t="s">
         <v>771</v>
       </c>
     </row>
     <row r="262" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A262" s="3" t="s">
+      <c r="A262" s="4" t="s">
         <v>772</v>
       </c>
-      <c r="B262" s="4" t="s">
+      <c r="B262" s="5" t="s">
         <v>773</v>
       </c>
-      <c r="C262" s="5" t="s">
+      <c r="C262" s="6" t="s">
         <v>774</v>
       </c>
     </row>
     <row r="263" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A263" s="6" t="s">
+      <c r="A263" s="7" t="s">
         <v>775</v>
       </c>
-      <c r="B263" s="7" t="s">
+      <c r="B263" s="8" t="s">
         <v>776</v>
       </c>
-      <c r="C263" s="8" t="s">
+      <c r="C263" s="9" t="s">
         <v>777</v>
       </c>
     </row>
     <row r="264" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A264" s="3" t="s">
+      <c r="A264" s="4" t="s">
         <v>778</v>
       </c>
-      <c r="B264" s="4" t="s">
+      <c r="B264" s="5" t="s">
         <v>779</v>
       </c>
-      <c r="C264" s="5" t="s">
+      <c r="C264" s="6" t="s">
         <v>780</v>
       </c>
     </row>
     <row r="265" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A265" s="6" t="s">
+      <c r="A265" s="7" t="s">
         <v>781</v>
       </c>
-      <c r="B265" s="7" t="s">
+      <c r="B265" s="8" t="s">
         <v>782</v>
       </c>
-      <c r="C265" s="8" t="s">
+      <c r="C265" s="9" t="s">
         <v>783</v>
       </c>
     </row>
     <row r="266" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A266" s="3" t="s">
+      <c r="A266" s="4" t="s">
         <v>784</v>
       </c>
-      <c r="B266" s="4" t="s">
+      <c r="B266" s="5" t="s">
         <v>785</v>
       </c>
-      <c r="C266" s="5" t="s">
+      <c r="C266" s="6" t="s">
         <v>786</v>
       </c>
     </row>
     <row r="267" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A267" s="6" t="s">
+      <c r="A267" s="7" t="s">
         <v>787</v>
       </c>
-      <c r="B267" s="7" t="s">
+      <c r="B267" s="8" t="s">
         <v>788</v>
       </c>
-      <c r="C267" s="8" t="s">
+      <c r="C267" s="9" t="s">
         <v>789</v>
       </c>
     </row>
     <row r="268" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A268" s="3" t="s">
+      <c r="A268" s="4" t="s">
         <v>790</v>
       </c>
-      <c r="B268" s="4" t="s">
+      <c r="B268" s="5" t="s">
         <v>791</v>
       </c>
-      <c r="C268" s="5" t="s">
+      <c r="C268" s="6" t="s">
         <v>792</v>
       </c>
     </row>
     <row r="269" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A269" s="6" t="s">
+      <c r="A269" s="7" t="s">
         <v>793</v>
       </c>
-      <c r="B269" s="7" t="s">
+      <c r="B269" s="8" t="s">
         <v>794</v>
       </c>
-      <c r="C269" s="8" t="s">
+      <c r="C269" s="9" t="s">
         <v>795</v>
       </c>
     </row>
     <row r="270" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A270" s="3" t="s">
+      <c r="A270" s="4" t="s">
         <v>796</v>
       </c>
-      <c r="B270" s="4" t="s">
+      <c r="B270" s="5" t="s">
         <v>797</v>
       </c>
-      <c r="C270" s="5" t="s">
+      <c r="C270" s="6" t="s">
         <v>798</v>
       </c>
     </row>
     <row r="271" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A271" s="6" t="s">
+      <c r="A271" s="7" t="s">
         <v>799</v>
       </c>
-      <c r="B271" s="7" t="s">
+      <c r="B271" s="8" t="s">
         <v>800</v>
       </c>
-      <c r="C271" s="8" t="s">
+      <c r="C271" s="9" t="s">
         <v>801</v>
       </c>
     </row>
     <row r="272" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A272" s="3" t="s">
+      <c r="A272" s="4" t="s">
         <v>802</v>
       </c>
-      <c r="B272" s="4" t="s">
+      <c r="B272" s="5" t="s">
         <v>803</v>
       </c>
-      <c r="C272" s="5" t="s">
+      <c r="C272" s="6" t="s">
         <v>804</v>
       </c>
     </row>
     <row r="273" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A273" s="3" t="s">
+      <c r="A273" s="4" t="s">
         <v>805</v>
       </c>
-      <c r="B273" s="4" t="s">
+      <c r="B273" s="5" t="s">
         <v>806</v>
       </c>
-      <c r="C273" s="5"/>
+      <c r="C273" s="6"/>
     </row>
     <row r="274" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A274" s="6" t="s">
+      <c r="A274" s="7" t="s">
         <v>807</v>
       </c>
-      <c r="B274" s="7" t="s">
+      <c r="B274" s="8" t="s">
         <v>808</v>
       </c>
-      <c r="C274" s="8" t="s">
+      <c r="C274" s="9" t="s">
         <v>809</v>
       </c>
     </row>
     <row r="275" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A275" s="3" t="s">
+      <c r="A275" s="4" t="s">
         <v>810</v>
       </c>
-      <c r="B275" s="4" t="s">
+      <c r="B275" s="5" t="s">
         <v>811</v>
       </c>
-      <c r="C275" s="5" t="s">
+      <c r="C275" s="6" t="s">
         <v>812</v>
       </c>
     </row>
     <row r="276" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A276" s="6" t="s">
+      <c r="A276" s="7" t="s">
         <v>813</v>
       </c>
-      <c r="B276" s="7" t="s">
+      <c r="B276" s="8" t="s">
         <v>814</v>
       </c>
-      <c r="C276" s="8" t="s">
+      <c r="C276" s="9" t="s">
         <v>815</v>
       </c>
     </row>
     <row r="277" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A277" s="3" t="s">
+      <c r="A277" s="4" t="s">
         <v>816</v>
       </c>
-      <c r="B277" s="4" t="s">
+      <c r="B277" s="5" t="s">
         <v>817</v>
       </c>
-      <c r="C277" s="5" t="s">
+      <c r="C277" s="6" t="s">
         <v>818</v>
       </c>
     </row>
     <row r="278" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A278" s="6" t="s">
+      <c r="A278" s="7" t="s">
         <v>819</v>
       </c>
-      <c r="B278" s="7" t="s">
+      <c r="B278" s="8" t="s">
         <v>820</v>
       </c>
-      <c r="C278" s="8" t="s">
+      <c r="C278" s="9" t="s">
         <v>821</v>
       </c>
     </row>
     <row r="279" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A279" s="3" t="s">
+      <c r="A279" s="4" t="s">
         <v>822</v>
       </c>
-      <c r="B279" s="4" t="s">
+      <c r="B279" s="5" t="s">
         <v>823</v>
       </c>
-      <c r="C279" s="5" t="s">
+      <c r="C279" s="6" t="s">
         <v>824</v>
       </c>
     </row>
     <row r="280" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A280" s="6" t="s">
+      <c r="A280" s="7" t="s">
         <v>825</v>
       </c>
-      <c r="B280" s="7" t="s">
+      <c r="B280" s="8" t="s">
         <v>826</v>
       </c>
-      <c r="C280" s="8" t="s">
+      <c r="C280" s="9" t="s">
         <v>827</v>
       </c>
     </row>
     <row r="281" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A281" s="3" t="s">
+      <c r="A281" s="4" t="s">
         <v>828</v>
       </c>
-      <c r="B281" s="4" t="s">
+      <c r="B281" s="5" t="s">
         <v>829</v>
       </c>
-      <c r="C281" s="5" t="s">
+      <c r="C281" s="6" t="s">
         <v>830</v>
       </c>
     </row>
     <row r="282" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A282" s="6" t="s">
+      <c r="A282" s="7" t="s">
         <v>831</v>
       </c>
-      <c r="B282" s="7" t="s">
+      <c r="B282" s="8" t="s">
         <v>832</v>
       </c>
-      <c r="C282" s="8" t="s">
+      <c r="C282" s="9" t="s">
         <v>833</v>
       </c>
     </row>
     <row r="283" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A283" s="3" t="s">
+      <c r="A283" s="4" t="s">
         <v>834</v>
       </c>
-      <c r="B283" s="4" t="s">
+      <c r="B283" s="5" t="s">
         <v>835</v>
       </c>
-      <c r="C283" s="5" t="s">
+      <c r="C283" s="6" t="s">
         <v>836</v>
       </c>
     </row>
     <row r="284" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A284" s="6" t="s">
+      <c r="A284" s="7" t="s">
         <v>837</v>
       </c>
-      <c r="B284" s="7" t="s">
+      <c r="B284" s="8" t="s">
         <v>838</v>
       </c>
-      <c r="C284" s="8" t="s">
+      <c r="C284" s="9" t="s">
         <v>839</v>
       </c>
     </row>
     <row r="285" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A285" s="3" t="s">
+      <c r="A285" s="4" t="s">
         <v>840</v>
       </c>
-      <c r="B285" s="4" t="s">
+      <c r="B285" s="5" t="s">
         <v>841</v>
       </c>
-      <c r="C285" s="5" t="s">
+      <c r="C285" s="6" t="s">
         <v>842</v>
       </c>
     </row>
     <row r="286" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A286" s="6" t="s">
+      <c r="A286" s="7" t="s">
         <v>843</v>
       </c>
-      <c r="B286" s="7" t="s">
+      <c r="B286" s="8" t="s">
         <v>844</v>
       </c>
-      <c r="C286" s="8" t="s">
+      <c r="C286" s="9" t="s">
         <v>845</v>
       </c>
     </row>
     <row r="287" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A287" s="3" t="s">
+      <c r="A287" s="4" t="s">
         <v>846</v>
       </c>
-      <c r="B287" s="4" t="s">
+      <c r="B287" s="5" t="s">
         <v>847</v>
       </c>
-      <c r="C287" s="5" t="s">
+      <c r="C287" s="6" t="s">
         <v>848</v>
       </c>
     </row>
     <row r="288" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A288" s="6" t="s">
+      <c r="A288" s="7" t="s">
         <v>849</v>
       </c>
-      <c r="B288" s="7" t="s">
+      <c r="B288" s="8" t="s">
         <v>850</v>
       </c>
-      <c r="C288" s="8" t="s">
+      <c r="C288" s="9" t="s">
         <v>851</v>
       </c>
     </row>
     <row r="289" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A289" s="3" t="s">
+      <c r="A289" s="4" t="s">
         <v>852</v>
       </c>
-      <c r="B289" s="4" t="s">
+      <c r="B289" s="5" t="s">
         <v>853</v>
       </c>
-      <c r="C289" s="5" t="s">
+      <c r="C289" s="6" t="s">
         <v>854</v>
       </c>
     </row>
     <row r="290" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A290" s="6" t="s">
+      <c r="A290" s="7" t="s">
         <v>855</v>
       </c>
-      <c r="B290" s="7" t="s">
+      <c r="B290" s="8" t="s">
         <v>856</v>
       </c>
-      <c r="C290" s="8" t="s">
+      <c r="C290" s="9" t="s">
         <v>857</v>
       </c>
     </row>
     <row r="291" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A291" s="6" t="s">
+      <c r="A291" s="7" t="s">
         <v>858</v>
       </c>
-      <c r="B291" s="7" t="s">
+      <c r="B291" s="8" t="s">
         <v>859</v>
       </c>
-      <c r="C291" s="5" t="s">
+      <c r="C291" s="6" t="s">
         <v>860</v>
       </c>
     </row>
     <row r="292" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A292" s="3" t="s">
+      <c r="A292" s="4" t="s">
         <v>861</v>
       </c>
-      <c r="B292" s="4" t="s">
+      <c r="B292" s="5" t="s">
         <v>862</v>
       </c>
-      <c r="C292" s="5" t="s">
+      <c r="C292" s="6" t="s">
         <v>863</v>
       </c>
     </row>
     <row r="293" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A293" s="6" t="s">
+      <c r="A293" s="7" t="s">
         <v>864</v>
       </c>
-      <c r="B293" s="7" t="s">
+      <c r="B293" s="8" t="s">
         <v>865</v>
       </c>
-      <c r="C293" s="8" t="s">
+      <c r="C293" s="9" t="s">
         <v>866</v>
       </c>
     </row>
     <row r="294" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A294" s="3" t="s">
+      <c r="A294" s="4" t="s">
         <v>867</v>
       </c>
-      <c r="B294" s="4" t="s">
+      <c r="B294" s="5" t="s">
         <v>868</v>
       </c>
-      <c r="C294" s="5" t="s">
+      <c r="C294" s="6" t="s">
         <v>869</v>
       </c>
     </row>
     <row r="295" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A295" s="6" t="s">
+      <c r="A295" s="7" t="s">
         <v>870</v>
       </c>
-      <c r="B295" s="7" t="s">
+      <c r="B295" s="8" t="s">
         <v>871</v>
       </c>
-      <c r="C295" s="8" t="s">
+      <c r="C295" s="9" t="s">
         <v>872</v>
       </c>
     </row>
     <row r="296" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A296" s="3" t="s">
+      <c r="A296" s="4" t="s">
         <v>873</v>
       </c>
-      <c r="B296" s="4" t="s">
+      <c r="B296" s="5" t="s">
         <v>874</v>
       </c>
-      <c r="C296" s="5" t="s">
+      <c r="C296" s="6" t="s">
         <v>875</v>
       </c>
     </row>
     <row r="297" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A297" s="6" t="s">
+      <c r="A297" s="7" t="s">
         <v>876</v>
       </c>
-      <c r="B297" s="7" t="s">
+      <c r="B297" s="8" t="s">
         <v>877</v>
       </c>
-      <c r="C297" s="8" t="s">
+      <c r="C297" s="9" t="s">
         <v>878</v>
       </c>
     </row>
     <row r="298" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A298" s="3" t="s">
+      <c r="A298" s="4" t="s">
         <v>879</v>
       </c>
-      <c r="B298" s="4" t="s">
+      <c r="B298" s="5" t="s">
         <v>880</v>
       </c>
-      <c r="C298" s="5" t="s">
+      <c r="C298" s="6" t="s">
         <v>881</v>
       </c>
     </row>
     <row r="299" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A299" s="6" t="s">
+      <c r="A299" s="7" t="s">
         <v>882</v>
       </c>
-      <c r="B299" s="7" t="s">
+      <c r="B299" s="8" t="s">
         <v>883</v>
       </c>
-      <c r="C299" s="8" t="s">
+      <c r="C299" s="9" t="s">
         <v>884</v>
       </c>
     </row>
     <row r="300" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A300" s="3" t="s">
+      <c r="A300" s="4" t="s">
         <v>885</v>
       </c>
-      <c r="B300" s="4" t="s">
+      <c r="B300" s="5" t="s">
         <v>886</v>
       </c>
-      <c r="C300" s="5" t="s">
+      <c r="C300" s="6" t="s">
         <v>887</v>
       </c>
     </row>
     <row r="301" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A301" s="6" t="s">
+      <c r="A301" s="7" t="s">
         <v>888</v>
       </c>
-      <c r="B301" s="7" t="s">
+      <c r="B301" s="8" t="s">
         <v>889</v>
       </c>
-      <c r="C301" s="8" t="s">
+      <c r="C301" s="9" t="s">
         <v>890</v>
       </c>
     </row>
     <row r="302" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A302" s="3" t="s">
+      <c r="A302" s="4" t="s">
         <v>891</v>
       </c>
-      <c r="B302" s="4" t="s">
+      <c r="B302" s="5" t="s">
         <v>892</v>
       </c>
-      <c r="C302" s="5" t="s">
+      <c r="C302" s="6" t="s">
         <v>893</v>
       </c>
     </row>
     <row r="303" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A303" s="6" t="s">
+      <c r="A303" s="7" t="s">
         <v>894</v>
       </c>
-      <c r="B303" s="7" t="s">
+      <c r="B303" s="8" t="s">
         <v>895</v>
       </c>
-      <c r="C303" s="8" t="s">
+      <c r="C303" s="9" t="s">
         <v>896</v>
       </c>
     </row>
     <row r="304" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A304" s="3" t="s">
+      <c r="A304" s="4" t="s">
         <v>897</v>
       </c>
-      <c r="B304" s="4" t="s">
+      <c r="B304" s="5" t="s">
         <v>898</v>
       </c>
-      <c r="C304" s="5" t="s">
+      <c r="C304" s="6" t="s">
         <v>899</v>
       </c>
     </row>
     <row r="305" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A305" s="6" t="s">
+      <c r="A305" s="7" t="s">
         <v>900</v>
       </c>
-      <c r="B305" s="7" t="s">
+      <c r="B305" s="8" t="s">
         <v>901</v>
       </c>
-      <c r="C305" s="8" t="s">
+      <c r="C305" s="9" t="s">
         <v>902</v>
       </c>
     </row>
     <row r="306" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A306" s="3" t="s">
+      <c r="A306" s="4" t="s">
         <v>903</v>
       </c>
-      <c r="B306" s="4" t="s">
+      <c r="B306" s="5" t="s">
         <v>904</v>
       </c>
-      <c r="C306" s="5" t="s">
+      <c r="C306" s="6" t="s">
         <v>905</v>
       </c>
     </row>
     <row r="307" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A307" s="6" t="s">
+      <c r="A307" s="7" t="s">
         <v>906</v>
       </c>
-      <c r="B307" s="7" t="s">
+      <c r="B307" s="8" t="s">
         <v>907</v>
       </c>
-      <c r="C307" s="8" t="s">
+      <c r="C307" s="9" t="s">
         <v>908</v>
       </c>
     </row>
     <row r="308" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A308" s="3" t="s">
+      <c r="A308" s="4" t="s">
         <v>909</v>
       </c>
-      <c r="B308" s="4" t="s">
+      <c r="B308" s="5" t="s">
         <v>910</v>
       </c>
-      <c r="C308" s="5" t="s">
+      <c r="C308" s="6" t="s">
         <v>911</v>
       </c>
     </row>
     <row r="309" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A309" s="6" t="s">
+      <c r="A309" s="7" t="s">
         <v>912</v>
       </c>
-      <c r="B309" s="7" t="s">
+      <c r="B309" s="8" t="s">
         <v>913</v>
       </c>
-      <c r="C309" s="8" t="s">
+      <c r="C309" s="9" t="s">
         <v>914</v>
       </c>
     </row>
     <row r="310" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A310" s="3" t="s">
+      <c r="A310" s="4" t="s">
         <v>915</v>
       </c>
-      <c r="B310" s="4" t="s">
+      <c r="B310" s="5" t="s">
         <v>916</v>
       </c>
-      <c r="C310" s="5" t="s">
+      <c r="C310" s="6" t="s">
         <v>917</v>
       </c>
     </row>
     <row r="311" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A311" s="6" t="s">
+      <c r="A311" s="7" t="s">
         <v>918</v>
       </c>
-      <c r="B311" s="7"/>
-      <c r="C311" s="8" t="s">
+      <c r="B311" s="8"/>
+      <c r="C311" s="9" t="s">
         <v>919</v>
       </c>
     </row>
     <row r="312" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A312" s="3" t="s">
+      <c r="A312" s="4" t="s">
         <v>920</v>
       </c>
-      <c r="B312" s="4" t="s">
+      <c r="B312" s="5" t="s">
         <v>921</v>
       </c>
-      <c r="C312" s="5" t="s">
+      <c r="C312" s="6" t="s">
         <v>922</v>
       </c>
     </row>
     <row r="313" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A313" s="6" t="s">
+      <c r="A313" s="7" t="s">
         <v>923</v>
       </c>
-      <c r="B313" s="7" t="s">
+      <c r="B313" s="8" t="s">
         <v>924</v>
       </c>
-      <c r="C313" s="8" t="s">
+      <c r="C313" s="9" t="s">
         <v>925</v>
       </c>
     </row>
     <row r="314" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A314" s="3" t="s">
+      <c r="A314" s="4" t="s">
         <v>926</v>
       </c>
-      <c r="B314" s="4" t="s">
+      <c r="B314" s="5" t="s">
         <v>927</v>
       </c>
-      <c r="C314" s="5" t="s">
+      <c r="C314" s="6" t="s">
         <v>928</v>
       </c>
     </row>
     <row r="315" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A315" s="6" t="s">
+      <c r="A315" s="7" t="s">
         <v>929</v>
       </c>
-      <c r="B315" s="7" t="s">
+      <c r="B315" s="8" t="s">
         <v>930</v>
       </c>
-      <c r="C315" s="8" t="s">
+      <c r="C315" s="9" t="s">
         <v>931</v>
       </c>
     </row>
     <row r="316" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A316" s="3" t="s">
+      <c r="A316" s="4" t="s">
         <v>932</v>
       </c>
-      <c r="B316" s="4" t="s">
+      <c r="B316" s="5" t="s">
         <v>933</v>
       </c>
-      <c r="C316" s="5" t="s">
+      <c r="C316" s="6" t="s">
         <v>934</v>
       </c>
     </row>
     <row r="317" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A317" s="6" t="s">
+      <c r="A317" s="7" t="s">
         <v>935</v>
       </c>
-      <c r="B317" s="7" t="s">
+      <c r="B317" s="8" t="s">
         <v>936</v>
       </c>
-      <c r="C317" s="8" t="s">
+      <c r="C317" s="9" t="s">
         <v>937</v>
       </c>
     </row>
     <row r="318" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A318" s="3" t="s">
+      <c r="A318" s="4" t="s">
         <v>938</v>
       </c>
-      <c r="B318" s="4" t="s">
+      <c r="B318" s="5" t="s">
         <v>939</v>
       </c>
-      <c r="C318" s="5" t="s">
+      <c r="C318" s="6" t="s">
         <v>940</v>
       </c>
     </row>
     <row r="319" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A319" s="6" t="s">
+      <c r="A319" s="7" t="s">
         <v>941</v>
       </c>
-      <c r="B319" s="7" t="s">
+      <c r="B319" s="8" t="s">
         <v>942</v>
       </c>
-      <c r="C319" s="8" t="s">
+      <c r="C319" s="9" t="s">
         <v>943</v>
       </c>
     </row>
     <row r="320" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A320" s="3" t="s">
+      <c r="A320" s="4" t="s">
         <v>944</v>
       </c>
-      <c r="B320" s="4" t="s">
+      <c r="B320" s="5" t="s">
         <v>945</v>
       </c>
-      <c r="C320" s="5" t="s">
+      <c r="C320" s="6" t="s">
         <v>946</v>
       </c>
     </row>
     <row r="321" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A321" s="6" t="s">
+      <c r="A321" s="7" t="s">
         <v>947</v>
       </c>
-      <c r="B321" s="7" t="s">
+      <c r="B321" s="8" t="s">
         <v>948</v>
       </c>
-      <c r="C321" s="8" t="s">
+      <c r="C321" s="9" t="s">
         <v>949</v>
       </c>
     </row>
     <row r="322" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A322" s="3" t="s">
+      <c r="A322" s="4" t="s">
         <v>950</v>
       </c>
-      <c r="B322" s="4" t="s">
+      <c r="B322" s="5" t="s">
         <v>951</v>
       </c>
-      <c r="C322" s="5" t="s">
+      <c r="C322" s="6" t="s">
         <v>952</v>
       </c>
     </row>
     <row r="323" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A323" s="6" t="s">
+      <c r="A323" s="7" t="s">
         <v>953</v>
       </c>
-      <c r="B323" s="7" t="s">
+      <c r="B323" s="8" t="s">
         <v>954</v>
       </c>
-      <c r="C323" s="8" t="s">
+      <c r="C323" s="9" t="s">
         <v>955</v>
       </c>
     </row>
     <row r="324" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A324" s="3" t="s">
+      <c r="A324" s="4" t="s">
         <v>956</v>
       </c>
-      <c r="B324" s="4" t="s">
+      <c r="B324" s="5" t="s">
         <v>957</v>
       </c>
-      <c r="C324" s="5" t="s">
+      <c r="C324" s="6" t="s">
         <v>958</v>
       </c>
     </row>
     <row r="325" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A325" s="6" t="s">
+      <c r="A325" s="7" t="s">
         <v>959</v>
       </c>
-      <c r="B325" s="7" t="s">
+      <c r="B325" s="8" t="s">
         <v>960</v>
       </c>
-      <c r="C325" s="8" t="s">
+      <c r="C325" s="9" t="s">
         <v>961</v>
       </c>
     </row>
     <row r="326" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A326" s="3" t="s">
+      <c r="A326" s="4" t="s">
         <v>962</v>
       </c>
-      <c r="B326" s="4" t="s">
+      <c r="B326" s="5" t="s">
         <v>963</v>
       </c>
-      <c r="C326" s="5" t="s">
+      <c r="C326" s="6" t="s">
         <v>964</v>
       </c>
     </row>
     <row r="327" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A327" s="6" t="s">
+      <c r="A327" s="7" t="s">
         <v>965</v>
       </c>
-      <c r="B327" s="7" t="s">
+      <c r="B327" s="8" t="s">
         <v>966</v>
       </c>
-      <c r="C327" s="8" t="s">
+      <c r="C327" s="9" t="s">
         <v>967</v>
       </c>
     </row>
     <row r="328" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A328" s="3" t="s">
+      <c r="A328" s="4" t="s">
         <v>968</v>
       </c>
-      <c r="B328" s="4" t="s">
+      <c r="B328" s="5" t="s">
         <v>969</v>
       </c>
-      <c r="C328" s="5" t="s">
+      <c r="C328" s="6" t="s">
         <v>970</v>
       </c>
     </row>
     <row r="329" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A329" s="6" t="s">
+      <c r="A329" s="7" t="s">
         <v>971</v>
       </c>
-      <c r="B329" s="7" t="s">
+      <c r="B329" s="8" t="s">
         <v>972</v>
       </c>
-      <c r="C329" s="8" t="s">
+      <c r="C329" s="9" t="s">
         <v>973</v>
       </c>
     </row>
     <row r="330" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A330" s="3" t="s">
+      <c r="A330" s="4" t="s">
         <v>974</v>
       </c>
-      <c r="B330" s="4" t="s">
+      <c r="B330" s="5" t="s">
         <v>975</v>
       </c>
-      <c r="C330" s="5" t="s">
+      <c r="C330" s="6" t="s">
         <v>976</v>
       </c>
     </row>
     <row r="331" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A331" s="6" t="s">
+      <c r="A331" s="7" t="s">
         <v>977</v>
       </c>
-      <c r="B331" s="7"/>
-      <c r="C331" s="8" t="s">
+      <c r="B331" s="8"/>
+      <c r="C331" s="9" t="s">
         <v>978</v>
       </c>
     </row>
     <row r="332" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A332" s="3" t="s">
+      <c r="A332" s="4" t="s">
         <v>979</v>
       </c>
-      <c r="B332" s="4"/>
-      <c r="C332" s="5" t="s">
+      <c r="B332" s="5"/>
+      <c r="C332" s="6" t="s">
         <v>980</v>
       </c>
     </row>
     <row r="333" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A333" s="6" t="s">
+      <c r="A333" s="7" t="s">
         <v>981</v>
       </c>
-      <c r="B333" s="7"/>
-      <c r="C333" s="8" t="s">
+      <c r="B333" s="8"/>
+      <c r="C333" s="9" t="s">
         <v>982</v>
       </c>
     </row>
     <row r="334" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A334" s="10" t="s">
+      <c r="A334" s="11" t="s">
         <v>983</v>
       </c>
-      <c r="B334" s="4"/>
-      <c r="C334" s="5" t="s">
+      <c r="B334" s="5"/>
+      <c r="C334" s="6" t="s">
         <v>984</v>
       </c>
     </row>
     <row r="335" customFormat="false" ht="24.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A335" s="6" t="s">
+      <c r="A335" s="7" t="s">
         <v>985</v>
       </c>
-      <c r="B335" s="7"/>
-      <c r="C335" s="8" t="s">
+      <c r="B335" s="8"/>
+      <c r="C335" s="9" t="s">
         <v>986</v>
+      </c>
+    </row>
+    <row r="336" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A336" s="4" t="s">
+        <v>987</v>
+      </c>
+      <c r="B336" s="5" t="s">
+        <v>988</v>
+      </c>
+      <c r="C336" s="6" t="s">
+        <v>989</v>
       </c>
     </row>
   </sheetData>
@@ -9346,6 +9398,9 @@
       </filters>
     </filterColumn>
   </autoFilter>
+  <hyperlinks>
+    <hyperlink ref="B336" r:id="rId2" display="T-TRIM@95"/>
+  </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -9353,7 +9408,7 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
-  <drawing r:id="rId2"/>
+  <drawing r:id="rId3"/>
 </worksheet>
 </file>
 
@@ -9365,348 +9420,348 @@
   <dimension ref="A1:I29"/>
   <sheetFormatPr defaultColWidth="8.6171875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="11" width="16.72"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="11" width="21.58"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="11" width="17.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="11" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="11" width="14.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="61.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="12" width="16.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="12" width="21.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="12" width="17.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="12" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="12" width="14.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="61.57"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="12" t="s">
-        <v>987</v>
-      </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
+      <c r="A1" s="13" t="s">
+        <v>990</v>
+      </c>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="14" t="s">
-        <v>988</v>
-      </c>
-      <c r="B2" s="15" t="s">
-        <v>989</v>
-      </c>
-      <c r="C2" s="15" t="s">
+      <c r="A2" s="15" t="s">
+        <v>991</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>992</v>
+      </c>
+      <c r="C2" s="16" t="s">
+        <v>993</v>
+      </c>
+      <c r="D2" s="16" t="s">
+        <v>994</v>
+      </c>
+      <c r="E2" s="16" t="s">
+        <v>995</v>
+      </c>
+      <c r="F2" s="16" t="s">
+        <v>996</v>
+      </c>
+      <c r="G2" s="17" t="s">
+        <v>997</v>
+      </c>
+      <c r="H2" s="16" t="s">
+        <v>998</v>
+      </c>
+      <c r="I2" s="15"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="15"/>
+      <c r="B3" s="16"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
+      <c r="H3" s="16"/>
+      <c r="I3" s="15"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="15"/>
+      <c r="B4" s="16"/>
+      <c r="C4" s="16"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="16"/>
+      <c r="H4" s="16"/>
+      <c r="I4" s="15"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="15"/>
+      <c r="B5" s="16"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="18"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="16"/>
+      <c r="H5" s="16"/>
+      <c r="I5" s="15"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="15"/>
+      <c r="B6" s="16"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="16"/>
+      <c r="H6" s="16"/>
+      <c r="I6" s="15"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="15"/>
+      <c r="B7" s="16"/>
+      <c r="C7" s="16"/>
+      <c r="D7" s="16"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="16"/>
+      <c r="G7" s="16"/>
+      <c r="H7" s="16"/>
+      <c r="I7" s="15"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="15"/>
+      <c r="B8" s="16"/>
+      <c r="C8" s="16"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="16"/>
+      <c r="I8" s="15"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="15"/>
+      <c r="B9" s="16"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="16"/>
+      <c r="H9" s="16"/>
+      <c r="I9" s="15"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="15"/>
+      <c r="B10" s="16"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="16"/>
+      <c r="E10" s="16"/>
+      <c r="F10" s="16"/>
+      <c r="G10" s="16"/>
+      <c r="H10" s="16"/>
+      <c r="I10" s="15"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="15"/>
+      <c r="B11" s="16"/>
+      <c r="C11" s="16"/>
+      <c r="D11" s="16"/>
+      <c r="E11" s="16"/>
+      <c r="F11" s="16"/>
+      <c r="G11" s="16"/>
+      <c r="H11" s="16"/>
+      <c r="I11" s="15"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="15"/>
+      <c r="B12" s="16"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="16"/>
+      <c r="H12" s="16"/>
+      <c r="I12" s="15"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="15"/>
+      <c r="B13" s="16"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="16"/>
+      <c r="G13" s="16"/>
+      <c r="H13" s="16"/>
+      <c r="I13" s="15"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="15"/>
+      <c r="B14" s="16"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="16"/>
+      <c r="F14" s="16"/>
+      <c r="G14" s="16"/>
+      <c r="H14" s="16"/>
+      <c r="I14" s="15"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="12" t="s">
         <v>990</v>
       </c>
-      <c r="D2" s="15" t="s">
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="15" t="s">
         <v>991</v>
       </c>
-      <c r="E2" s="15" t="s">
+      <c r="B17" s="16" t="s">
         <v>992</v>
       </c>
-      <c r="F2" s="15" t="s">
+      <c r="C17" s="16" t="s">
         <v>993</v>
       </c>
-      <c r="G2" s="16" t="s">
+      <c r="D17" s="16" t="s">
         <v>994</v>
       </c>
-      <c r="H2" s="15" t="s">
+      <c r="E17" s="16" t="s">
         <v>995</v>
       </c>
-      <c r="I2" s="14"/>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="14"/>
-      <c r="B3" s="15"/>
-      <c r="C3" s="15"/>
-      <c r="D3" s="15"/>
-      <c r="E3" s="15"/>
-      <c r="F3" s="15"/>
-      <c r="G3" s="15"/>
-      <c r="H3" s="15"/>
-      <c r="I3" s="14"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="14"/>
-      <c r="B4" s="15"/>
-      <c r="C4" s="15"/>
-      <c r="D4" s="15"/>
-      <c r="E4" s="15"/>
-      <c r="F4" s="15"/>
-      <c r="G4" s="15"/>
-      <c r="H4" s="15"/>
-      <c r="I4" s="14"/>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="14"/>
-      <c r="B5" s="15"/>
-      <c r="C5" s="15"/>
-      <c r="D5" s="15"/>
-      <c r="E5" s="17"/>
-      <c r="F5" s="15"/>
-      <c r="G5" s="15"/>
-      <c r="H5" s="15"/>
-      <c r="I5" s="14"/>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="14"/>
-      <c r="B6" s="15"/>
-      <c r="C6" s="15"/>
-      <c r="D6" s="15"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="15"/>
-      <c r="G6" s="15"/>
-      <c r="H6" s="15"/>
-      <c r="I6" s="14"/>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="14"/>
-      <c r="B7" s="15"/>
-      <c r="C7" s="15"/>
-      <c r="D7" s="15"/>
-      <c r="E7" s="17"/>
-      <c r="F7" s="15"/>
-      <c r="G7" s="15"/>
-      <c r="H7" s="15"/>
-      <c r="I7" s="14"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="14"/>
-      <c r="B8" s="15"/>
-      <c r="C8" s="15"/>
-      <c r="D8" s="15"/>
-      <c r="E8" s="15"/>
-      <c r="F8" s="15"/>
-      <c r="G8" s="15"/>
-      <c r="H8" s="15"/>
-      <c r="I8" s="14"/>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="14"/>
-      <c r="B9" s="15"/>
-      <c r="C9" s="15"/>
-      <c r="D9" s="15"/>
-      <c r="E9" s="15"/>
-      <c r="F9" s="15"/>
-      <c r="G9" s="15"/>
-      <c r="H9" s="15"/>
-      <c r="I9" s="14"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="14"/>
-      <c r="B10" s="15"/>
-      <c r="C10" s="15"/>
-      <c r="D10" s="15"/>
-      <c r="E10" s="15"/>
-      <c r="F10" s="15"/>
-      <c r="G10" s="15"/>
-      <c r="H10" s="15"/>
-      <c r="I10" s="14"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="14"/>
-      <c r="B11" s="15"/>
-      <c r="C11" s="15"/>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="15"/>
-      <c r="G11" s="15"/>
-      <c r="H11" s="15"/>
-      <c r="I11" s="14"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="14"/>
-      <c r="B12" s="15"/>
-      <c r="C12" s="15"/>
-      <c r="D12" s="15"/>
-      <c r="E12" s="15"/>
-      <c r="F12" s="15"/>
-      <c r="G12" s="15"/>
-      <c r="H12" s="15"/>
-      <c r="I12" s="14"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="14"/>
-      <c r="B13" s="15"/>
-      <c r="C13" s="15"/>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="15"/>
-      <c r="G13" s="15"/>
-      <c r="H13" s="15"/>
-      <c r="I13" s="14"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="14"/>
-      <c r="B14" s="15"/>
-      <c r="C14" s="15"/>
-      <c r="D14" s="15"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="15"/>
-      <c r="G14" s="15"/>
-      <c r="H14" s="15"/>
-      <c r="I14" s="14"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="11" t="s">
-        <v>987</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="14" t="s">
-        <v>988</v>
-      </c>
-      <c r="B17" s="15" t="s">
-        <v>989</v>
-      </c>
-      <c r="C17" s="15" t="s">
-        <v>990</v>
-      </c>
-      <c r="D17" s="15" t="s">
-        <v>991</v>
-      </c>
-      <c r="E17" s="15" t="s">
-        <v>992</v>
-      </c>
-      <c r="F17" s="15" t="s">
-        <v>993</v>
-      </c>
-      <c r="G17" s="16" t="s">
-        <v>994</v>
-      </c>
-      <c r="H17" s="15" t="s">
-        <v>995</v>
-      </c>
-      <c r="I17" s="14"/>
+      <c r="F17" s="16" t="s">
+        <v>996</v>
+      </c>
+      <c r="G17" s="17" t="s">
+        <v>997</v>
+      </c>
+      <c r="H17" s="16" t="s">
+        <v>998</v>
+      </c>
+      <c r="I17" s="15"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="14"/>
-      <c r="B18" s="15"/>
-      <c r="C18" s="15"/>
-      <c r="D18" s="15"/>
-      <c r="E18" s="15"/>
-      <c r="F18" s="15"/>
-      <c r="G18" s="15"/>
-      <c r="H18" s="15"/>
-      <c r="I18" s="14"/>
+      <c r="A18" s="15"/>
+      <c r="B18" s="16"/>
+      <c r="C18" s="16"/>
+      <c r="D18" s="16"/>
+      <c r="E18" s="16"/>
+      <c r="F18" s="16"/>
+      <c r="G18" s="16"/>
+      <c r="H18" s="16"/>
+      <c r="I18" s="15"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="14"/>
-      <c r="B19" s="15"/>
-      <c r="C19" s="15"/>
-      <c r="D19" s="15"/>
-      <c r="E19" s="15"/>
-      <c r="F19" s="15"/>
-      <c r="G19" s="15"/>
-      <c r="H19" s="15"/>
-      <c r="I19" s="14"/>
+      <c r="A19" s="15"/>
+      <c r="B19" s="16"/>
+      <c r="C19" s="16"/>
+      <c r="D19" s="16"/>
+      <c r="E19" s="16"/>
+      <c r="F19" s="16"/>
+      <c r="G19" s="16"/>
+      <c r="H19" s="16"/>
+      <c r="I19" s="15"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="14"/>
-      <c r="B20" s="15"/>
-      <c r="C20" s="15"/>
-      <c r="D20" s="15"/>
-      <c r="E20" s="15"/>
-      <c r="F20" s="15"/>
-      <c r="G20" s="15"/>
-      <c r="H20" s="15"/>
-      <c r="I20" s="14"/>
+      <c r="A20" s="15"/>
+      <c r="B20" s="16"/>
+      <c r="C20" s="16"/>
+      <c r="D20" s="16"/>
+      <c r="E20" s="16"/>
+      <c r="F20" s="16"/>
+      <c r="G20" s="16"/>
+      <c r="H20" s="16"/>
+      <c r="I20" s="15"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="14"/>
-      <c r="B21" s="15"/>
-      <c r="C21" s="15"/>
-      <c r="D21" s="15"/>
-      <c r="E21" s="15"/>
-      <c r="F21" s="15"/>
-      <c r="G21" s="15"/>
-      <c r="H21" s="15"/>
-      <c r="I21" s="14"/>
+      <c r="A21" s="15"/>
+      <c r="B21" s="16"/>
+      <c r="C21" s="16"/>
+      <c r="D21" s="16"/>
+      <c r="E21" s="16"/>
+      <c r="F21" s="16"/>
+      <c r="G21" s="16"/>
+      <c r="H21" s="16"/>
+      <c r="I21" s="15"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="14"/>
-      <c r="B22" s="15"/>
-      <c r="C22" s="15"/>
-      <c r="D22" s="15"/>
-      <c r="E22" s="15"/>
-      <c r="F22" s="15"/>
-      <c r="G22" s="15"/>
-      <c r="H22" s="15"/>
-      <c r="I22" s="14"/>
+      <c r="A22" s="15"/>
+      <c r="B22" s="16"/>
+      <c r="C22" s="16"/>
+      <c r="D22" s="16"/>
+      <c r="E22" s="16"/>
+      <c r="F22" s="16"/>
+      <c r="G22" s="16"/>
+      <c r="H22" s="16"/>
+      <c r="I22" s="15"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="14"/>
-      <c r="B23" s="15"/>
-      <c r="C23" s="15"/>
-      <c r="D23" s="15"/>
-      <c r="E23" s="15"/>
-      <c r="F23" s="15"/>
-      <c r="G23" s="15"/>
-      <c r="H23" s="15"/>
-      <c r="I23" s="14"/>
+      <c r="A23" s="15"/>
+      <c r="B23" s="16"/>
+      <c r="C23" s="16"/>
+      <c r="D23" s="16"/>
+      <c r="E23" s="16"/>
+      <c r="F23" s="16"/>
+      <c r="G23" s="16"/>
+      <c r="H23" s="16"/>
+      <c r="I23" s="15"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="14"/>
-      <c r="B24" s="15"/>
-      <c r="C24" s="15"/>
-      <c r="D24" s="15"/>
-      <c r="E24" s="15"/>
-      <c r="F24" s="15"/>
-      <c r="G24" s="15"/>
-      <c r="H24" s="15"/>
-      <c r="I24" s="14"/>
+      <c r="A24" s="15"/>
+      <c r="B24" s="16"/>
+      <c r="C24" s="16"/>
+      <c r="D24" s="16"/>
+      <c r="E24" s="16"/>
+      <c r="F24" s="16"/>
+      <c r="G24" s="16"/>
+      <c r="H24" s="16"/>
+      <c r="I24" s="15"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="14"/>
-      <c r="B25" s="15"/>
-      <c r="C25" s="15"/>
-      <c r="D25" s="15"/>
-      <c r="E25" s="15"/>
-      <c r="F25" s="15"/>
-      <c r="G25" s="15"/>
-      <c r="H25" s="15"/>
-      <c r="I25" s="14"/>
+      <c r="A25" s="15"/>
+      <c r="B25" s="16"/>
+      <c r="C25" s="16"/>
+      <c r="D25" s="16"/>
+      <c r="E25" s="16"/>
+      <c r="F25" s="16"/>
+      <c r="G25" s="16"/>
+      <c r="H25" s="16"/>
+      <c r="I25" s="15"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="14"/>
-      <c r="B26" s="15"/>
-      <c r="C26" s="15"/>
-      <c r="D26" s="15"/>
-      <c r="E26" s="15"/>
-      <c r="F26" s="15"/>
-      <c r="G26" s="15"/>
-      <c r="H26" s="15"/>
-      <c r="I26" s="14"/>
+      <c r="A26" s="15"/>
+      <c r="B26" s="16"/>
+      <c r="C26" s="16"/>
+      <c r="D26" s="16"/>
+      <c r="E26" s="16"/>
+      <c r="F26" s="16"/>
+      <c r="G26" s="16"/>
+      <c r="H26" s="16"/>
+      <c r="I26" s="15"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="14"/>
-      <c r="B27" s="15"/>
-      <c r="C27" s="15"/>
-      <c r="D27" s="15"/>
-      <c r="E27" s="15"/>
-      <c r="F27" s="15"/>
-      <c r="G27" s="15"/>
-      <c r="H27" s="15"/>
-      <c r="I27" s="14"/>
+      <c r="A27" s="15"/>
+      <c r="B27" s="16"/>
+      <c r="C27" s="16"/>
+      <c r="D27" s="16"/>
+      <c r="E27" s="16"/>
+      <c r="F27" s="16"/>
+      <c r="G27" s="16"/>
+      <c r="H27" s="16"/>
+      <c r="I27" s="15"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="14"/>
-      <c r="B28" s="15"/>
-      <c r="C28" s="15"/>
-      <c r="D28" s="15"/>
-      <c r="E28" s="15"/>
-      <c r="F28" s="15"/>
-      <c r="G28" s="15"/>
-      <c r="H28" s="15"/>
-      <c r="I28" s="14"/>
+      <c r="A28" s="15"/>
+      <c r="B28" s="16"/>
+      <c r="C28" s="16"/>
+      <c r="D28" s="16"/>
+      <c r="E28" s="16"/>
+      <c r="F28" s="16"/>
+      <c r="G28" s="16"/>
+      <c r="H28" s="16"/>
+      <c r="I28" s="15"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="14"/>
-      <c r="B29" s="15"/>
-      <c r="C29" s="15"/>
-      <c r="D29" s="15"/>
-      <c r="E29" s="15"/>
-      <c r="F29" s="15"/>
-      <c r="G29" s="15"/>
-      <c r="H29" s="15"/>
-      <c r="I29" s="14"/>
+      <c r="A29" s="15"/>
+      <c r="B29" s="16"/>
+      <c r="C29" s="16"/>
+      <c r="D29" s="16"/>
+      <c r="E29" s="16"/>
+      <c r="F29" s="16"/>
+      <c r="G29" s="16"/>
+      <c r="H29" s="16"/>
+      <c r="I29" s="15"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -9727,860 +9782,860 @@
   <dimension ref="A1:J33"/>
   <sheetFormatPr defaultColWidth="8.6171875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="19.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="11.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="34"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="6" min="6" style="18" width="8.62"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="19" width="19"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="19" width="17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="11.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="51.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="19.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="11.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="34"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="6" min="6" style="19" width="8.62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="20" width="19"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="20" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="11.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="51.57"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F1" s="20"/>
+      <c r="F1" s="21"/>
     </row>
     <row r="2" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="14" t="s">
-        <v>996</v>
-      </c>
-      <c r="B2" s="14" t="s">
-        <v>997</v>
-      </c>
-      <c r="C2" s="14" t="s">
-        <v>998</v>
-      </c>
-      <c r="D2" s="14" t="s">
+      <c r="A2" s="15" t="s">
         <v>999</v>
       </c>
-      <c r="E2" s="21" t="s">
+      <c r="B2" s="15" t="s">
         <v>1000</v>
       </c>
-      <c r="F2" s="22" t="s">
+      <c r="C2" s="15" t="s">
         <v>1001</v>
       </c>
-      <c r="G2" s="23" t="s">
+      <c r="D2" s="15" t="s">
         <v>1002</v>
       </c>
-      <c r="H2" s="23" t="s">
+      <c r="E2" s="22" t="s">
         <v>1003</v>
       </c>
-      <c r="I2" s="14" t="s">
+      <c r="F2" s="23" t="s">
         <v>1004</v>
       </c>
-      <c r="J2" s="14" t="s">
+      <c r="G2" s="24" t="s">
         <v>1005</v>
       </c>
-    </row>
-    <row r="3" s="28" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="24" t="s">
+      <c r="H2" s="24" t="s">
         <v>1006</v>
       </c>
-      <c r="B3" s="24" t="s">
+      <c r="I2" s="15" t="s">
         <v>1007</v>
       </c>
-      <c r="C3" s="25" t="s">
+      <c r="J2" s="15" t="s">
         <v>1008</v>
       </c>
-      <c r="D3" s="26" t="s">
+    </row>
+    <row r="3" s="29" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="25" t="s">
         <v>1009</v>
       </c>
-      <c r="E3" s="24" t="n">
+      <c r="B3" s="25" t="s">
+        <v>1010</v>
+      </c>
+      <c r="C3" s="26" t="s">
+        <v>1011</v>
+      </c>
+      <c r="D3" s="27" t="s">
+        <v>1012</v>
+      </c>
+      <c r="E3" s="25" t="n">
         <v>25</v>
       </c>
-      <c r="F3" s="27" t="n">
+      <c r="F3" s="28" t="n">
         <v>-36</v>
       </c>
-      <c r="G3" s="25"/>
-      <c r="H3" s="25"/>
-      <c r="I3" s="24" t="s">
-        <v>1010</v>
-      </c>
-      <c r="J3" s="24" t="s">
-        <v>1011</v>
-      </c>
-    </row>
-    <row r="4" s="28" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="24" t="s">
-        <v>1012</v>
-      </c>
-      <c r="B4" s="24"/>
-      <c r="C4" s="25" t="s">
+      <c r="G3" s="26"/>
+      <c r="H3" s="26"/>
+      <c r="I3" s="25" t="s">
         <v>1013</v>
       </c>
-      <c r="D4" s="24" t="s">
+      <c r="J3" s="25" t="s">
         <v>1014</v>
       </c>
-      <c r="E4" s="24" t="n">
+    </row>
+    <row r="4" s="29" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="25" t="s">
+        <v>1015</v>
+      </c>
+      <c r="B4" s="25"/>
+      <c r="C4" s="26" t="s">
+        <v>1016</v>
+      </c>
+      <c r="D4" s="25" t="s">
+        <v>1017</v>
+      </c>
+      <c r="E4" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="F4" s="27" t="n">
+      <c r="F4" s="28" t="n">
         <v>-46</v>
       </c>
-      <c r="G4" s="25"/>
-      <c r="H4" s="25"/>
-      <c r="I4" s="24" t="s">
-        <v>1015</v>
-      </c>
-      <c r="J4" s="24" t="s">
-        <v>1016</v>
-      </c>
-    </row>
-    <row r="5" s="28" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="24" t="s">
-        <v>1017</v>
-      </c>
-      <c r="B5" s="24"/>
-      <c r="C5" s="25" t="s">
+      <c r="G4" s="26"/>
+      <c r="H4" s="26"/>
+      <c r="I4" s="25" t="s">
         <v>1018</v>
       </c>
-      <c r="D5" s="24" t="s">
+      <c r="J4" s="25" t="s">
         <v>1019</v>
       </c>
-      <c r="E5" s="24" t="n">
+    </row>
+    <row r="5" s="29" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="25" t="s">
+        <v>1020</v>
+      </c>
+      <c r="B5" s="25"/>
+      <c r="C5" s="26" t="s">
+        <v>1021</v>
+      </c>
+      <c r="D5" s="25" t="s">
+        <v>1022</v>
+      </c>
+      <c r="E5" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="F5" s="27" t="n">
+      <c r="F5" s="28" t="n">
         <v>-46</v>
       </c>
-      <c r="G5" s="25"/>
-      <c r="H5" s="25"/>
-      <c r="I5" s="24" t="s">
-        <v>1015</v>
-      </c>
-      <c r="J5" s="24" t="s">
-        <v>1016</v>
-      </c>
-    </row>
-    <row r="6" s="28" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="26" t="s">
-        <v>1020</v>
-      </c>
-      <c r="B6" s="24" t="s">
-        <v>1021</v>
-      </c>
-      <c r="C6" s="25" t="s">
-        <v>1022</v>
-      </c>
-      <c r="D6" s="26" t="s">
+      <c r="G5" s="26"/>
+      <c r="H5" s="26"/>
+      <c r="I5" s="25" t="s">
+        <v>1018</v>
+      </c>
+      <c r="J5" s="25" t="s">
+        <v>1019</v>
+      </c>
+    </row>
+    <row r="6" s="29" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="27" t="s">
         <v>1023</v>
       </c>
-      <c r="E6" s="24" t="n">
+      <c r="B6" s="25" t="s">
+        <v>1024</v>
+      </c>
+      <c r="C6" s="26" t="s">
+        <v>1025</v>
+      </c>
+      <c r="D6" s="27" t="s">
+        <v>1026</v>
+      </c>
+      <c r="E6" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="F6" s="27" t="n">
+      <c r="F6" s="28" t="n">
         <v>-88</v>
       </c>
-      <c r="G6" s="25"/>
-      <c r="H6" s="29"/>
-      <c r="I6" s="24" t="s">
-        <v>1015</v>
-      </c>
-      <c r="J6" s="24" t="s">
-        <v>1016</v>
-      </c>
-    </row>
-    <row r="7" s="28" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="24" t="s">
-        <v>1024</v>
-      </c>
-      <c r="B7" s="24"/>
-      <c r="C7" s="25" t="s">
-        <v>1025</v>
-      </c>
-      <c r="D7" s="24" t="s">
-        <v>1026</v>
-      </c>
-      <c r="E7" s="24" t="n">
+      <c r="G6" s="26"/>
+      <c r="H6" s="30"/>
+      <c r="I6" s="25" t="s">
+        <v>1018</v>
+      </c>
+      <c r="J6" s="25" t="s">
+        <v>1019</v>
+      </c>
+    </row>
+    <row r="7" s="29" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="25" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B7" s="25"/>
+      <c r="C7" s="26" t="s">
+        <v>1028</v>
+      </c>
+      <c r="D7" s="25" t="s">
+        <v>1029</v>
+      </c>
+      <c r="E7" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="F7" s="27" t="n">
+      <c r="F7" s="28" t="n">
         <v>-33</v>
       </c>
-      <c r="G7" s="25"/>
-      <c r="H7" s="25"/>
-      <c r="I7" s="24" t="s">
-        <v>1027</v>
-      </c>
-      <c r="J7" s="24" t="s">
-        <v>1028</v>
-      </c>
-    </row>
-    <row r="8" s="28" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="24" t="s">
-        <v>1029</v>
-      </c>
-      <c r="B8" s="24"/>
-      <c r="C8" s="25" t="s">
+      <c r="G7" s="26"/>
+      <c r="H7" s="26"/>
+      <c r="I7" s="25" t="s">
         <v>1030</v>
       </c>
-      <c r="D8" s="26" t="s">
+      <c r="J7" s="25" t="s">
         <v>1031</v>
       </c>
-      <c r="E8" s="24" t="n">
+    </row>
+    <row r="8" s="29" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="25" t="s">
+        <v>1032</v>
+      </c>
+      <c r="B8" s="25"/>
+      <c r="C8" s="26" t="s">
+        <v>1033</v>
+      </c>
+      <c r="D8" s="27" t="s">
+        <v>1034</v>
+      </c>
+      <c r="E8" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="F8" s="27" t="n">
+      <c r="F8" s="28" t="n">
         <v>-53</v>
       </c>
-      <c r="G8" s="25"/>
-      <c r="H8" s="25"/>
-      <c r="I8" s="24" t="s">
-        <v>1027</v>
-      </c>
-      <c r="J8" s="24" t="s">
-        <v>1028</v>
-      </c>
-    </row>
-    <row r="9" s="28" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="24" t="s">
-        <v>1032</v>
-      </c>
-      <c r="B9" s="24"/>
-      <c r="C9" s="25" t="s">
-        <v>1033</v>
-      </c>
-      <c r="D9" s="24" t="s">
-        <v>1034</v>
-      </c>
-      <c r="E9" s="24" t="n">
+      <c r="G8" s="26"/>
+      <c r="H8" s="26"/>
+      <c r="I8" s="25" t="s">
+        <v>1030</v>
+      </c>
+      <c r="J8" s="25" t="s">
+        <v>1031</v>
+      </c>
+    </row>
+    <row r="9" s="29" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="25" t="s">
+        <v>1035</v>
+      </c>
+      <c r="B9" s="25"/>
+      <c r="C9" s="26" t="s">
+        <v>1036</v>
+      </c>
+      <c r="D9" s="25" t="s">
+        <v>1037</v>
+      </c>
+      <c r="E9" s="25" t="n">
         <v>38</v>
       </c>
-      <c r="F9" s="27" t="n">
+      <c r="F9" s="28" t="n">
         <v>-50</v>
       </c>
-      <c r="G9" s="25"/>
-      <c r="H9" s="25"/>
-      <c r="I9" s="24" t="s">
-        <v>1027</v>
-      </c>
-      <c r="J9" s="24" t="s">
-        <v>1028</v>
-      </c>
-    </row>
-    <row r="10" s="28" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="24" t="s">
-        <v>1035</v>
-      </c>
-      <c r="B10" s="24"/>
-      <c r="C10" s="25" t="s">
-        <v>1036</v>
-      </c>
-      <c r="D10" s="24" t="s">
-        <v>1037</v>
-      </c>
-      <c r="E10" s="24" t="n">
+      <c r="G9" s="26"/>
+      <c r="H9" s="26"/>
+      <c r="I9" s="25" t="s">
+        <v>1030</v>
+      </c>
+      <c r="J9" s="25" t="s">
+        <v>1031</v>
+      </c>
+    </row>
+    <row r="10" s="29" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="25" t="s">
+        <v>1038</v>
+      </c>
+      <c r="B10" s="25"/>
+      <c r="C10" s="26" t="s">
+        <v>1039</v>
+      </c>
+      <c r="D10" s="25" t="s">
+        <v>1040</v>
+      </c>
+      <c r="E10" s="25" t="n">
         <v>159</v>
       </c>
-      <c r="F10" s="27" t="n">
+      <c r="F10" s="28" t="n">
         <v>-181</v>
       </c>
-      <c r="G10" s="25"/>
-      <c r="H10" s="25"/>
-      <c r="I10" s="24" t="s">
-        <v>1027</v>
-      </c>
-      <c r="J10" s="24" t="s">
-        <v>1028</v>
-      </c>
-    </row>
-    <row r="11" s="28" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="24" t="s">
-        <v>1038</v>
-      </c>
-      <c r="B11" s="24" t="s">
-        <v>1039</v>
-      </c>
-      <c r="C11" s="25" t="s">
-        <v>1040</v>
-      </c>
-      <c r="D11" s="26" t="s">
+      <c r="G10" s="26"/>
+      <c r="H10" s="26"/>
+      <c r="I10" s="25" t="s">
+        <v>1030</v>
+      </c>
+      <c r="J10" s="25" t="s">
+        <v>1031</v>
+      </c>
+    </row>
+    <row r="11" s="29" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="25" t="s">
         <v>1041</v>
       </c>
-      <c r="E11" s="24" t="n">
+      <c r="B11" s="25" t="s">
+        <v>1042</v>
+      </c>
+      <c r="C11" s="26" t="s">
+        <v>1043</v>
+      </c>
+      <c r="D11" s="27" t="s">
+        <v>1044</v>
+      </c>
+      <c r="E11" s="25" t="n">
         <v>148</v>
       </c>
-      <c r="F11" s="27" t="n">
+      <c r="F11" s="28" t="n">
         <v>-226</v>
       </c>
-      <c r="G11" s="25"/>
-      <c r="H11" s="25"/>
-      <c r="I11" s="24" t="s">
-        <v>1027</v>
-      </c>
-      <c r="J11" s="24" t="s">
-        <v>1028</v>
-      </c>
-    </row>
-    <row r="12" s="28" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="24" t="s">
-        <v>1042</v>
-      </c>
-      <c r="B12" s="24"/>
-      <c r="C12" s="25"/>
-      <c r="D12" s="26"/>
-      <c r="E12" s="24"/>
-      <c r="F12" s="27"/>
-      <c r="G12" s="25"/>
-      <c r="H12" s="25"/>
-      <c r="I12" s="30" t="n">
+      <c r="G11" s="26"/>
+      <c r="H11" s="26"/>
+      <c r="I11" s="25" t="s">
+        <v>1030</v>
+      </c>
+      <c r="J11" s="25" t="s">
+        <v>1031</v>
+      </c>
+    </row>
+    <row r="12" s="29" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="25" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B12" s="25"/>
+      <c r="C12" s="26"/>
+      <c r="D12" s="27"/>
+      <c r="E12" s="25"/>
+      <c r="F12" s="28"/>
+      <c r="G12" s="26"/>
+      <c r="H12" s="26"/>
+      <c r="I12" s="31" t="n">
         <v>14481</v>
       </c>
-      <c r="J12" s="24" t="s">
-        <v>1028</v>
-      </c>
-    </row>
-    <row r="13" s="28" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="24" t="s">
-        <v>1043</v>
-      </c>
-      <c r="B13" s="24"/>
-      <c r="C13" s="25" t="s">
-        <v>1044</v>
-      </c>
-      <c r="D13" s="26" t="s">
-        <v>1045</v>
-      </c>
-      <c r="E13" s="24" t="n">
+      <c r="J12" s="25" t="s">
+        <v>1031</v>
+      </c>
+    </row>
+    <row r="13" s="29" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="25" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B13" s="25"/>
+      <c r="C13" s="26" t="s">
+        <v>1047</v>
+      </c>
+      <c r="D13" s="27" t="s">
+        <v>1048</v>
+      </c>
+      <c r="E13" s="25" t="n">
         <v>42</v>
       </c>
-      <c r="F13" s="27" t="n">
+      <c r="F13" s="28" t="n">
         <v>-26</v>
       </c>
-      <c r="G13" s="25"/>
-      <c r="H13" s="25"/>
-      <c r="I13" s="24" t="s">
-        <v>1046</v>
-      </c>
-      <c r="J13" s="24" t="s">
-        <v>1047</v>
-      </c>
-    </row>
-    <row r="14" s="28" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="24" t="s">
-        <v>1048</v>
-      </c>
-      <c r="B14" s="24"/>
-      <c r="C14" s="25" t="s">
+      <c r="G13" s="26"/>
+      <c r="H13" s="26"/>
+      <c r="I13" s="25" t="s">
         <v>1049</v>
       </c>
-      <c r="D14" s="24" t="s">
+      <c r="J13" s="25" t="s">
         <v>1050</v>
       </c>
-      <c r="E14" s="24" t="n">
+    </row>
+    <row r="14" s="29" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="25" t="s">
+        <v>1051</v>
+      </c>
+      <c r="B14" s="25"/>
+      <c r="C14" s="26" t="s">
+        <v>1052</v>
+      </c>
+      <c r="D14" s="25" t="s">
+        <v>1053</v>
+      </c>
+      <c r="E14" s="25" t="n">
         <v>112</v>
       </c>
-      <c r="F14" s="27" t="n">
+      <c r="F14" s="28" t="n">
         <v>-47</v>
       </c>
-      <c r="G14" s="25"/>
-      <c r="H14" s="25"/>
-      <c r="I14" s="24" t="s">
-        <v>1046</v>
-      </c>
-      <c r="J14" s="24" t="s">
-        <v>1047</v>
-      </c>
-    </row>
-    <row r="15" s="28" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="26" t="s">
-        <v>1051</v>
-      </c>
-      <c r="B15" s="24"/>
-      <c r="C15" s="25" t="s">
-        <v>1052</v>
-      </c>
-      <c r="D15" s="26" t="s">
-        <v>1053</v>
-      </c>
-      <c r="E15" s="24" t="n">
+      <c r="G14" s="26"/>
+      <c r="H14" s="26"/>
+      <c r="I14" s="25" t="s">
+        <v>1049</v>
+      </c>
+      <c r="J14" s="25" t="s">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="15" s="29" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="27" t="s">
+        <v>1054</v>
+      </c>
+      <c r="B15" s="25"/>
+      <c r="C15" s="26" t="s">
+        <v>1055</v>
+      </c>
+      <c r="D15" s="27" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E15" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="F15" s="27" t="n">
+      <c r="F15" s="28" t="n">
         <v>-100</v>
       </c>
-      <c r="G15" s="25"/>
-      <c r="H15" s="29"/>
-      <c r="I15" s="24" t="s">
-        <v>1046</v>
-      </c>
-      <c r="J15" s="24" t="s">
-        <v>1047</v>
-      </c>
-    </row>
-    <row r="16" s="28" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="24" t="s">
-        <v>1054</v>
-      </c>
-      <c r="B16" s="24" t="s">
-        <v>1055</v>
-      </c>
-      <c r="C16" s="25" t="s">
-        <v>1056</v>
-      </c>
-      <c r="D16" s="24" t="s">
+      <c r="G15" s="26"/>
+      <c r="H15" s="30"/>
+      <c r="I15" s="25" t="s">
+        <v>1049</v>
+      </c>
+      <c r="J15" s="25" t="s">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="16" s="29" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="25" t="s">
         <v>1057</v>
       </c>
-      <c r="E16" s="24" t="n">
+      <c r="B16" s="25" t="s">
+        <v>1058</v>
+      </c>
+      <c r="C16" s="26" t="s">
+        <v>1059</v>
+      </c>
+      <c r="D16" s="25" t="s">
+        <v>1060</v>
+      </c>
+      <c r="E16" s="25" t="n">
         <v>200</v>
       </c>
-      <c r="F16" s="27" t="n">
+      <c r="F16" s="28" t="n">
         <v>-84</v>
       </c>
-      <c r="G16" s="25"/>
-      <c r="H16" s="25"/>
-      <c r="I16" s="24" t="s">
-        <v>1058</v>
-      </c>
-      <c r="J16" s="24" t="s">
-        <v>1059</v>
+      <c r="G16" s="26"/>
+      <c r="H16" s="26"/>
+      <c r="I16" s="25" t="s">
+        <v>1061</v>
+      </c>
+      <c r="J16" s="25" t="s">
+        <v>1062</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="14" t="s">
-        <v>1060</v>
-      </c>
-      <c r="B17" s="14" t="s">
-        <v>1061</v>
-      </c>
-      <c r="C17" s="31" t="s">
-        <v>1062</v>
-      </c>
-      <c r="D17" s="32" t="s">
+      <c r="A17" s="15" t="s">
         <v>1063</v>
       </c>
-      <c r="E17" s="33" t="n">
+      <c r="B17" s="15" t="s">
+        <v>1064</v>
+      </c>
+      <c r="C17" s="32" t="s">
+        <v>1065</v>
+      </c>
+      <c r="D17" s="33" t="s">
+        <v>1066</v>
+      </c>
+      <c r="E17" s="34" t="n">
         <v>250</v>
       </c>
-      <c r="F17" s="34" t="n">
+      <c r="F17" s="35" t="n">
         <v>-116</v>
       </c>
-      <c r="G17" s="31"/>
-      <c r="H17" s="31"/>
-      <c r="I17" s="14" t="s">
-        <v>1064</v>
-      </c>
-      <c r="J17" s="14" t="s">
-        <v>1065</v>
-      </c>
-    </row>
-    <row r="18" s="28" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="24" t="s">
-        <v>1066</v>
-      </c>
-      <c r="B18" s="24"/>
-      <c r="C18" s="25" t="s">
+      <c r="G17" s="32"/>
+      <c r="H17" s="32"/>
+      <c r="I17" s="15" t="s">
         <v>1067</v>
       </c>
-      <c r="D18" s="24" t="s">
+      <c r="J17" s="15" t="s">
         <v>1068</v>
       </c>
-      <c r="E18" s="24" t="n">
+    </row>
+    <row r="18" s="29" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="25" t="s">
+        <v>1069</v>
+      </c>
+      <c r="B18" s="25"/>
+      <c r="C18" s="26" t="s">
+        <v>1070</v>
+      </c>
+      <c r="D18" s="25" t="s">
+        <v>1071</v>
+      </c>
+      <c r="E18" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="F18" s="27" t="n">
+      <c r="F18" s="28" t="n">
         <v>-2</v>
       </c>
-      <c r="G18" s="25"/>
-      <c r="H18" s="25"/>
-      <c r="I18" s="24" t="s">
-        <v>1069</v>
-      </c>
-      <c r="J18" s="24" t="s">
-        <v>1070</v>
-      </c>
-    </row>
-    <row r="19" s="28" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="24" t="s">
-        <v>1071</v>
-      </c>
-      <c r="B19" s="24"/>
-      <c r="C19" s="25" t="s">
+      <c r="G18" s="26"/>
+      <c r="H18" s="26"/>
+      <c r="I18" s="25" t="s">
         <v>1072</v>
       </c>
-      <c r="D19" s="24" t="s">
+      <c r="J18" s="25" t="s">
         <v>1073</v>
       </c>
-      <c r="E19" s="24" t="n">
+    </row>
+    <row r="19" s="29" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="25" t="s">
+        <v>1074</v>
+      </c>
+      <c r="B19" s="25"/>
+      <c r="C19" s="26" t="s">
+        <v>1075</v>
+      </c>
+      <c r="D19" s="25" t="s">
+        <v>1076</v>
+      </c>
+      <c r="E19" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="F19" s="27" t="n">
+      <c r="F19" s="28" t="n">
         <v>-35</v>
       </c>
-      <c r="G19" s="25"/>
-      <c r="H19" s="25"/>
-      <c r="I19" s="24" t="s">
-        <v>1069</v>
-      </c>
-      <c r="J19" s="24" t="s">
-        <v>1070</v>
-      </c>
-    </row>
-    <row r="20" s="28" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="24" t="s">
-        <v>1074</v>
-      </c>
-      <c r="B20" s="24"/>
-      <c r="C20" s="25" t="s">
-        <v>1075</v>
-      </c>
-      <c r="D20" s="24" t="s">
-        <v>1076</v>
-      </c>
-      <c r="E20" s="24" t="n">
+      <c r="G19" s="26"/>
+      <c r="H19" s="26"/>
+      <c r="I19" s="25" t="s">
+        <v>1072</v>
+      </c>
+      <c r="J19" s="25" t="s">
+        <v>1073</v>
+      </c>
+    </row>
+    <row r="20" s="29" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="25" t="s">
+        <v>1077</v>
+      </c>
+      <c r="B20" s="25"/>
+      <c r="C20" s="26" t="s">
+        <v>1078</v>
+      </c>
+      <c r="D20" s="25" t="s">
+        <v>1079</v>
+      </c>
+      <c r="E20" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="F20" s="27" t="n">
+      <c r="F20" s="28" t="n">
         <v>-7.6967</v>
       </c>
-      <c r="G20" s="25"/>
-      <c r="H20" s="25"/>
-      <c r="I20" s="24" t="s">
-        <v>1069</v>
-      </c>
-      <c r="J20" s="24" t="s">
-        <v>1070</v>
-      </c>
-    </row>
-    <row r="21" s="28" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="24" t="s">
-        <v>1077</v>
-      </c>
-      <c r="B21" s="24"/>
-      <c r="C21" s="25" t="s">
-        <v>1078</v>
-      </c>
-      <c r="D21" s="24" t="s">
-        <v>1079</v>
-      </c>
-      <c r="E21" s="24" t="n">
+      <c r="G20" s="26"/>
+      <c r="H20" s="26"/>
+      <c r="I20" s="25" t="s">
+        <v>1072</v>
+      </c>
+      <c r="J20" s="25" t="s">
+        <v>1073</v>
+      </c>
+    </row>
+    <row r="21" s="29" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="25" t="s">
+        <v>1080</v>
+      </c>
+      <c r="B21" s="25"/>
+      <c r="C21" s="26" t="s">
+        <v>1081</v>
+      </c>
+      <c r="D21" s="25" t="s">
+        <v>1082</v>
+      </c>
+      <c r="E21" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="F21" s="27" t="n">
+      <c r="F21" s="28" t="n">
         <v>-10</v>
       </c>
-      <c r="G21" s="25"/>
-      <c r="H21" s="25"/>
-      <c r="I21" s="24" t="s">
-        <v>1069</v>
-      </c>
-      <c r="J21" s="24" t="s">
-        <v>1070</v>
-      </c>
-    </row>
-    <row r="22" s="28" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="24" t="s">
-        <v>1080</v>
-      </c>
-      <c r="B22" s="24"/>
-      <c r="C22" s="25" t="s">
-        <v>1081</v>
-      </c>
-      <c r="D22" s="26" t="s">
-        <v>1082</v>
-      </c>
-      <c r="E22" s="24" t="n">
+      <c r="G21" s="26"/>
+      <c r="H21" s="26"/>
+      <c r="I21" s="25" t="s">
+        <v>1072</v>
+      </c>
+      <c r="J21" s="25" t="s">
+        <v>1073</v>
+      </c>
+    </row>
+    <row r="22" s="29" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="25" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B22" s="25"/>
+      <c r="C22" s="26" t="s">
+        <v>1084</v>
+      </c>
+      <c r="D22" s="27" t="s">
+        <v>1085</v>
+      </c>
+      <c r="E22" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="F22" s="27" t="n">
+      <c r="F22" s="28" t="n">
         <v>-44</v>
       </c>
-      <c r="G22" s="25"/>
-      <c r="H22" s="25"/>
-      <c r="I22" s="24" t="s">
-        <v>1069</v>
-      </c>
-      <c r="J22" s="24" t="s">
-        <v>1070</v>
-      </c>
-    </row>
-    <row r="23" s="28" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="26" t="s">
-        <v>1083</v>
-      </c>
-      <c r="B23" s="24" t="s">
-        <v>1084</v>
-      </c>
-      <c r="C23" s="25" t="s">
-        <v>1085</v>
-      </c>
-      <c r="D23" s="26" t="s">
+      <c r="G22" s="26"/>
+      <c r="H22" s="26"/>
+      <c r="I22" s="25" t="s">
+        <v>1072</v>
+      </c>
+      <c r="J22" s="25" t="s">
+        <v>1073</v>
+      </c>
+    </row>
+    <row r="23" s="29" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="27" t="s">
         <v>1086</v>
       </c>
-      <c r="E23" s="24" t="n">
+      <c r="B23" s="25" t="s">
+        <v>1087</v>
+      </c>
+      <c r="C23" s="26" t="s">
+        <v>1088</v>
+      </c>
+      <c r="D23" s="27" t="s">
+        <v>1089</v>
+      </c>
+      <c r="E23" s="25" t="n">
         <v>30</v>
       </c>
-      <c r="F23" s="27" t="n">
+      <c r="F23" s="28" t="n">
         <v>-24</v>
       </c>
-      <c r="G23" s="25"/>
-      <c r="H23" s="25"/>
-      <c r="I23" s="24" t="s">
-        <v>1087</v>
-      </c>
-      <c r="J23" s="24" t="s">
-        <v>1088</v>
-      </c>
-    </row>
-    <row r="24" s="28" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="24" t="s">
-        <v>1089</v>
-      </c>
-      <c r="B24" s="24" t="s">
+      <c r="G23" s="26"/>
+      <c r="H23" s="26"/>
+      <c r="I23" s="25" t="s">
         <v>1090</v>
       </c>
-      <c r="C24" s="25" t="s">
+      <c r="J23" s="25" t="s">
         <v>1091</v>
       </c>
-      <c r="D24" s="24" t="s">
+    </row>
+    <row r="24" s="29" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="25" t="s">
         <v>1092</v>
       </c>
-      <c r="E24" s="24" t="n">
+      <c r="B24" s="25" t="s">
+        <v>1093</v>
+      </c>
+      <c r="C24" s="26" t="s">
+        <v>1094</v>
+      </c>
+      <c r="D24" s="25" t="s">
+        <v>1095</v>
+      </c>
+      <c r="E24" s="25" t="n">
         <v>30</v>
       </c>
-      <c r="F24" s="27" t="n">
+      <c r="F24" s="28" t="n">
         <v>-20</v>
       </c>
-      <c r="G24" s="25"/>
-      <c r="H24" s="25"/>
-      <c r="I24" s="24" t="s">
-        <v>1087</v>
-      </c>
-      <c r="J24" s="24" t="s">
-        <v>1088</v>
-      </c>
-    </row>
-    <row r="25" s="28" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="26" t="s">
-        <v>1093</v>
-      </c>
-      <c r="B25" s="24"/>
-      <c r="C25" s="25" t="s">
-        <v>1094</v>
-      </c>
-      <c r="D25" s="26" t="s">
-        <v>1095</v>
-      </c>
-      <c r="E25" s="24" t="n">
+      <c r="G24" s="26"/>
+      <c r="H24" s="26"/>
+      <c r="I24" s="25" t="s">
+        <v>1090</v>
+      </c>
+      <c r="J24" s="25" t="s">
+        <v>1091</v>
+      </c>
+    </row>
+    <row r="25" s="29" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="27" t="s">
+        <v>1096</v>
+      </c>
+      <c r="B25" s="25"/>
+      <c r="C25" s="26" t="s">
+        <v>1097</v>
+      </c>
+      <c r="D25" s="27" t="s">
+        <v>1098</v>
+      </c>
+      <c r="E25" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="F25" s="27" t="n">
+      <c r="F25" s="28" t="n">
         <v>-44</v>
       </c>
-      <c r="G25" s="25"/>
-      <c r="H25" s="29"/>
-      <c r="I25" s="24" t="s">
-        <v>1096</v>
-      </c>
-      <c r="J25" s="24" t="s">
-        <v>1097</v>
-      </c>
-    </row>
-    <row r="26" s="28" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="24" t="s">
-        <v>1098</v>
-      </c>
-      <c r="B26" s="24"/>
-      <c r="C26" s="25" t="s">
+      <c r="G25" s="26"/>
+      <c r="H25" s="30"/>
+      <c r="I25" s="25" t="s">
         <v>1099</v>
       </c>
-      <c r="D26" s="24" t="s">
+      <c r="J25" s="25" t="s">
         <v>1100</v>
       </c>
-      <c r="E26" s="24" t="n">
+    </row>
+    <row r="26" s="29" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="25" t="s">
+        <v>1101</v>
+      </c>
+      <c r="B26" s="25"/>
+      <c r="C26" s="26" t="s">
+        <v>1102</v>
+      </c>
+      <c r="D26" s="25" t="s">
+        <v>1103</v>
+      </c>
+      <c r="E26" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="F26" s="27" t="n">
+      <c r="F26" s="28" t="n">
         <v>-14</v>
       </c>
-      <c r="G26" s="25"/>
-      <c r="H26" s="25"/>
-      <c r="I26" s="24" t="s">
-        <v>1101</v>
-      </c>
-      <c r="J26" s="24" t="s">
-        <v>1102</v>
-      </c>
-    </row>
-    <row r="27" s="28" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="24" t="s">
-        <v>1103</v>
-      </c>
-      <c r="B27" s="24" t="s">
+      <c r="G26" s="26"/>
+      <c r="H26" s="26"/>
+      <c r="I26" s="25" t="s">
         <v>1104</v>
       </c>
-      <c r="C27" s="25" t="s">
+      <c r="J26" s="25" t="s">
         <v>1105</v>
       </c>
-      <c r="D27" s="24" t="s">
+    </row>
+    <row r="27" s="29" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="25" t="s">
         <v>1106</v>
       </c>
-      <c r="E27" s="24" t="n">
+      <c r="B27" s="25" t="s">
+        <v>1107</v>
+      </c>
+      <c r="C27" s="26" t="s">
+        <v>1108</v>
+      </c>
+      <c r="D27" s="25" t="s">
+        <v>1109</v>
+      </c>
+      <c r="E27" s="25" t="n">
         <v>20</v>
       </c>
-      <c r="F27" s="27" t="n">
+      <c r="F27" s="28" t="n">
         <v>-58</v>
       </c>
-      <c r="G27" s="25"/>
-      <c r="H27" s="25"/>
-      <c r="I27" s="24" t="s">
-        <v>1101</v>
-      </c>
-      <c r="J27" s="24" t="s">
-        <v>1102</v>
-      </c>
-    </row>
-    <row r="28" s="28" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="24" t="s">
-        <v>1107</v>
-      </c>
-      <c r="B28" s="24"/>
-      <c r="C28" s="25" t="s">
-        <v>1108</v>
-      </c>
-      <c r="D28" s="26" t="s">
-        <v>1109</v>
-      </c>
-      <c r="E28" s="24" t="n">
+      <c r="G27" s="26"/>
+      <c r="H27" s="26"/>
+      <c r="I27" s="25" t="s">
+        <v>1104</v>
+      </c>
+      <c r="J27" s="25" t="s">
+        <v>1105</v>
+      </c>
+    </row>
+    <row r="28" s="29" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="25" t="s">
+        <v>1110</v>
+      </c>
+      <c r="B28" s="25"/>
+      <c r="C28" s="26" t="s">
+        <v>1111</v>
+      </c>
+      <c r="D28" s="27" t="s">
+        <v>1112</v>
+      </c>
+      <c r="E28" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="F28" s="27" t="n">
+      <c r="F28" s="28" t="n">
         <v>-200</v>
       </c>
-      <c r="G28" s="25"/>
-      <c r="H28" s="25"/>
-      <c r="I28" s="24" t="s">
-        <v>1110</v>
-      </c>
-      <c r="J28" s="24" t="s">
-        <v>1111</v>
-      </c>
-    </row>
-    <row r="29" s="28" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="24" t="s">
-        <v>1112</v>
-      </c>
-      <c r="B29" s="24" t="s">
+      <c r="G28" s="26"/>
+      <c r="H28" s="26"/>
+      <c r="I28" s="25" t="s">
         <v>1113</v>
       </c>
-      <c r="C29" s="25" t="s">
+      <c r="J28" s="25" t="s">
         <v>1114</v>
       </c>
-      <c r="D29" s="26" t="s">
+    </row>
+    <row r="29" s="29" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="25" t="s">
         <v>1115</v>
       </c>
-      <c r="E29" s="24" t="n">
+      <c r="B29" s="25" t="s">
+        <v>1116</v>
+      </c>
+      <c r="C29" s="26" t="s">
+        <v>1117</v>
+      </c>
+      <c r="D29" s="27" t="s">
+        <v>1118</v>
+      </c>
+      <c r="E29" s="25" t="n">
         <v>80</v>
       </c>
-      <c r="F29" s="27" t="n">
+      <c r="F29" s="28" t="n">
         <v>-42</v>
       </c>
-      <c r="G29" s="25"/>
-      <c r="H29" s="25"/>
-      <c r="I29" s="24" t="s">
-        <v>1116</v>
-      </c>
-      <c r="J29" s="24" t="s">
-        <v>1117</v>
-      </c>
-    </row>
-    <row r="30" s="28" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="24" t="s">
-        <v>1118</v>
-      </c>
-      <c r="B30" s="24"/>
-      <c r="C30" s="25" t="s">
+      <c r="G29" s="26"/>
+      <c r="H29" s="26"/>
+      <c r="I29" s="25" t="s">
         <v>1119</v>
       </c>
-      <c r="D30" s="24" t="s">
+      <c r="J29" s="25" t="s">
         <v>1120</v>
       </c>
-      <c r="E30" s="24" t="n">
+    </row>
+    <row r="30" s="29" customFormat="true" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="25" t="s">
+        <v>1121</v>
+      </c>
+      <c r="B30" s="25"/>
+      <c r="C30" s="26" t="s">
+        <v>1122</v>
+      </c>
+      <c r="D30" s="25" t="s">
+        <v>1123</v>
+      </c>
+      <c r="E30" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="F30" s="27" t="n">
+      <c r="F30" s="28" t="n">
         <v>-88</v>
       </c>
-      <c r="G30" s="25"/>
-      <c r="H30" s="25"/>
-      <c r="I30" s="24" t="s">
-        <v>1121</v>
-      </c>
-      <c r="J30" s="24" t="s">
-        <v>1122</v>
+      <c r="G30" s="26"/>
+      <c r="H30" s="26"/>
+      <c r="I30" s="25" t="s">
+        <v>1124</v>
+      </c>
+      <c r="J30" s="25" t="s">
+        <v>1125</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="14" t="s">
-        <v>1123</v>
-      </c>
-      <c r="B31" s="14"/>
-      <c r="C31" s="31" t="s">
-        <v>1124</v>
-      </c>
-      <c r="D31" s="32" t="s">
-        <v>1125</v>
-      </c>
-      <c r="E31" s="33" t="n">
+      <c r="A31" s="15" t="s">
+        <v>1126</v>
+      </c>
+      <c r="B31" s="15"/>
+      <c r="C31" s="32" t="s">
+        <v>1127</v>
+      </c>
+      <c r="D31" s="33" t="s">
+        <v>1128</v>
+      </c>
+      <c r="E31" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="F31" s="34" t="n">
+      <c r="F31" s="35" t="n">
         <v>-54</v>
       </c>
-      <c r="G31" s="31"/>
-      <c r="H31" s="31"/>
-      <c r="I31" s="14" t="s">
-        <v>1126</v>
-      </c>
-      <c r="J31" s="14" t="s">
-        <v>1127</v>
+      <c r="G31" s="32"/>
+      <c r="H31" s="32"/>
+      <c r="I31" s="15" t="s">
+        <v>1129</v>
+      </c>
+      <c r="J31" s="15" t="s">
+        <v>1130</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="14" t="s">
-        <v>1128</v>
-      </c>
-      <c r="B32" s="14" t="s">
+      <c r="A32" s="15" t="s">
+        <v>1131</v>
+      </c>
+      <c r="B32" s="15" t="s">
+        <v>1132</v>
+      </c>
+      <c r="C32" s="32" t="s">
+        <v>1133</v>
+      </c>
+      <c r="D32" s="33" t="s">
+        <v>1134</v>
+      </c>
+      <c r="E32" s="34" t="n">
+        <v>31</v>
+      </c>
+      <c r="F32" s="35" t="n">
+        <v>-22</v>
+      </c>
+      <c r="G32" s="32"/>
+      <c r="H32" s="32"/>
+      <c r="I32" s="15" t="s">
         <v>1129</v>
       </c>
-      <c r="C32" s="31" t="s">
+      <c r="J32" s="15" t="s">
         <v>1130</v>
       </c>
-      <c r="D32" s="32" t="s">
-        <v>1131</v>
-      </c>
-      <c r="E32" s="33" t="n">
-        <v>31</v>
-      </c>
-      <c r="F32" s="34" t="n">
-        <v>-22</v>
-      </c>
-      <c r="G32" s="31"/>
-      <c r="H32" s="31"/>
-      <c r="I32" s="14" t="s">
-        <v>1126</v>
-      </c>
-      <c r="J32" s="14" t="s">
-        <v>1127</v>
-      </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="14" t="s">
-        <v>1132</v>
-      </c>
-      <c r="B33" s="14"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="22"/>
-      <c r="G33" s="31"/>
-      <c r="H33" s="31"/>
-      <c r="I33" s="35" t="n">
+      <c r="A33" s="15" t="s">
+        <v>1135</v>
+      </c>
+      <c r="B33" s="15"/>
+      <c r="C33" s="15"/>
+      <c r="D33" s="15"/>
+      <c r="E33" s="15"/>
+      <c r="F33" s="23"/>
+      <c r="G33" s="32"/>
+      <c r="H33" s="32"/>
+      <c r="I33" s="36" t="n">
         <v>15031</v>
       </c>
-      <c r="J33" s="14" t="s">
-        <v>1133</v>
+      <c r="J33" s="15" t="s">
+        <v>1136</v>
       </c>
     </row>
   </sheetData>

--- a/Manifest Description Conversion.xlsx
+++ b/Manifest Description Conversion.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C341"/>
+  <dimension ref="A1:C342"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6085,13 +6085,18 @@
       <c r="C340" t="inlineStr"/>
     </row>
     <row r="341">
-      <c r="A341" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="A341" t="inlineStr"/>
       <c r="B341" t="inlineStr"/>
       <c r="C341" t="inlineStr"/>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr"/>
+      <c r="C342" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
